--- a/untitled folder/HSC_Physics_1st_Paper_Chapter_04_Newtonian_Mechanics.xlsx
+++ b/untitled folder/HSC_Physics_1st_Paper_Chapter_04_Newtonian_Mechanics.xlsx
@@ -1051,17 +1051,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>একটি অনুভূমিক মসৃণ মেঝেতে $M$ ভরের একটি ওয়েজ (wedge) রাখা আছে যার নতি কোণ $lpha$। ওয়েজের মসৃণ ঢালু তলে $m$ ভরের একটি ব্লক রাখা হলো। পুরো সংস্থাকে স্থির অবস্থা থেকে ছেড়ে দিলে অনুভূমিক মেঝে বরাবর ওয়েজের ত্বরণ $A$ এবং ওয়েজের সাপেক্ষে ব্লকের আপেক্ষিক ত্বরণ $a_r$ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি অনুভূমিক মসৃণ মেঝেতে $M$ ভরের একটি ওয়েজ (wedge) রাখা আছে যার নতি কোণ $\alpha$। ওয়েজের মসৃণ ঢালু তলে $m$ ভরের একটি ব্লক রাখা হলো। পুরো সংস্থাকে স্থির অবস্থা থেকে ছেড়ে দিলে অনুভূমিক মেঝে বরাবর ওয়েজের ত্বরণ $A$ এবং ওয়েজের সাপেক্ষে ব্লকের আপেক্ষিক ত্বরণ $a_r$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ব্লকের অনুভূমিক ত্বরণ $a_x = a_r \coslpha - A$ এবং উল্লম্ব নিম্নমুখী ত্বরণ $a_y = a_r \sinlpha$। ওয়েজের জন্য অনুভূমিক বলের সমীকরণ: $N\sinlpha = MA$। ব্লকের ক্ষেত্রে অভিলম্ব বরাবর সমীকরণ: $mg\coslpha - N = m a_{\perp} = m A\sinlpha \implies N = m(g\coslpha - A\sinlpha)$। এই $N$-এর মান ওয়েজের সমীকরণে বসিয়ে পাই: $m(g\coslpha - A\sinlpha)\sinlpha = MA \implies A(M + m\sin^2lpha) = mg\sinlpha\coslpha \implies A = rac{mg\sinlpha\coslpha}{M + m\sin^2lpha}$। ব্লকের স্পর্শক বরাবর সমীকরণ: $mg\sinlpha + m A\coslpha = m a_r \implies a_r = g\sinlpha + A\coslpha = rac{(M+m)g\sinlpha}{M + m\sin^2lpha}$।</t>
+          <t>ব্লকের অনুভূমিক ত্বরণ $a_x = a_r \coslpha - A$ এবং উল্লম্ব নিম্নমুখী ত্বরণ $a_y = a_r \sinlpha$। ওয়েজের জন্য অনুভূমিক বলের সমীকরণ: $N\sinlpha = MA$। ব্লকের ক্ষেত্রে অভিলম্ব বরাবর সমীকরণ: $mg\coslpha - N = m a_{\perp} = m A\sinlpha \implies N = m(g\coslpha - A\sinlpha)$। এই $N$-এর মান ওয়েজের সমীকরণে বসিয়ে পাই: $m(g\coslpha - A\sinlpha)\sinlpha = MA \implies A(M + m\sin^2\alpha) = mg\sinlpha\coslpha \implies A = \frac{mg\sinlpha\coslpha}{M + m\sin^2\alpha}$। ব্লকের স্পর্শক বরাবর সমীকরণ: $mg\sinlpha + m A\coslpha = m a_r \implies a_r = g\sinlpha + A\coslpha = \frac{(M+m)g\sinlpha}{M + m\sin^2\alpha}$।</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1112,8 +1107,8 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>সুতার মোট দৈর্ঘ্যের ওপর দ্বিতীয়বার ব্যবকলন করলে কনস্ট্রেইন্ট সম্পর্ক পাওয়া যায়: $2\ddot{x}_1 + 3\ddot{x}_2 = 0 \implies 2a_1 + 3a_2 = 0 \implies a_1 = -rac{3}{2}a_2$। ভার্চুয়াল ওয়ার্ক বা শক্তির সংরক্ষণ নীতি অনুসারে $T_1 a_1 + T_2 a_2 = 0 \implies T_1\left(-rac{3}{2}a_2-ight) + T_2 a_2 = 0 \implies T_2 = rac{3}{2}T_1$ অথবা পুলির টানের অনুপাত $rac{T_1}{T_2} = rac{2}{3}$। নিউটনের গতির সমীকরণ: $m_1 g - 2T = m_1 a_1$ এবং $m_2 g - 3T = m_2 a_2$। এগুলো সমাধান করে ত্বরণ $a_2 = rac{(3m_2 - 2m_1)g}{4m_1 + 9m_2}$ (বা অনুরূপ ভর বিন্যাস অনুযায়ী) এবং $a_1 = -rac{3}{2}a_2$।</t>
+          <t>সুতার মোট দৈর্ঘ্যের ওপর দ্বিতীয়বার ব্যবকলন করলে কনস্ট্রেইন্ট সম্পর্ক পাওয়া যায়: $2\ddot{x}_1 + 3\ddot{x}_2 = 0 \implies 2a_1 + 3a_2 = 0 \implies a_1 = -\frac{3}{2}a_2$। ভার্চুয়াল ওয়ার্ক বা শক্তির সংরক্ষণ নীতি অনুসারে $T_1 a_1 + T_2 a_2 = 0 \implies T_1\left(-\frac{3}{2}a_2+ight) + T_2 a_2 = 0 \implies T_2 = \frac{3}{2}T_1$ অথবা পুলির টানের অনুপাত $\frac{T_1}{T_2} = \frac{2}{3}$। নিউটনের গতির সমীকরণ: $m_1 g - 2T = m_1 a_1$ এবং $m_2 g - 3T = m_2 a_2$। এগুলো সমাধান করে ত্বরণ $a_2 = \frac{(3m_2 - 2m_1)g}{4m_1 + 9m_2}$ (বা অনুরূপ ভর বিন্যাস অনুযায়ী) এবং $a_1 = -\frac{3}{2}a_2$।</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1153,17 +1148,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>একটি ঘর্ষণহীন $	heta$ নতি কোণের হেলানো তল বরাবর একটি ট্রলি মুক্তভাবে পিছলে নামছে। ট্রলির ছাদ থেকে $L$ দৈর্ঘ্যের সুতায় একটি বব ঝুলিয়ে দেওয়া হলো। ট্রলির সাপেক্ষে দোলকটির সুতা উল্লম্বের সাথে বা হেলানো তলের অভিলম্বের সাথে কত কোণ তৈরি করে স্থির থাকবে?</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি ঘর্ষণহীন $\theta$ নতি কোণের হেলানো তল বরাবর একটি ট্রলি মুক্তভাবে পিছলে নামছে। ট্রলির ছাদ থেকে $L$ দৈর্ঘ্যের সুতায় একটি বব ঝুলিয়ে দেওয়া হলো। ট্রলির সাপেক্ষে দোলকটির সুতা উল্লম্বের সাথে বা হেলানো তলের অভিলম্বের সাথে কত কোণ তৈরি করে স্থির থাকবে?</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>হেলানো তল বরাবর ট্রলির নিম্নমুখী ত্বরণ $a = g\sin	heta$। ট্রলির রেফারেন্স ফ্রেমে ববের ওপর কার্যকর মহাকর্ষীয় ত্বরণ $ec{g}_{	ext{eff}} = ec{g} - ec{a}$। তলের সমান্তরাল উপাংশ: $g_{\parallel} = g\sin	heta - a = g\sin	heta - g\sin	heta = 0$। তলের অভিলম্ব উপাংশ: $g_{\perp} = g\cos	heta$ (তলের দিকে লম্বভাবে)। যেহেতু হেলানো তলের সমান্তরালে কোনো কার্যকর ত্বরণ নেই, তাই ববটি হেলানো তলের ঠিক অভিলম্ব বরাবর সুতা প্রসারিত করে স্থির থাকবে। অর্থাৎ সুতাটি হেলানো তলের অভিলম্বের সাথে $0^\circ$ কোণ করবে (বা উল্লম্বের সাথে $	heta$ কোণে থাকবে)।</t>
+          <t>হেলানো তল বরাবর ট্রলির নিম্নমুখী ত্বরণ $a = g\sin\theta$। ট্রলির রেফারেন্স ফ্রেমে ববের ওপর কার্যকর মহাকর্ষীয় ত্বরণ $ec{g}_{\text{eff}} = ec{g} - ec{a}$। তলের সমান্তরাল উপাংশ: $g_{\parallel} = g\sin\theta - a = g\sin\theta - g\sin\theta = 0$। তলের অভিলম্ব উপাংশ: $g_{\perp} = g\cos\theta$ (তলের দিকে লম্বভাবে)। যেহেতু হেলানো তলের সমান্তরালে কোনো কার্যকর ত্বরণ নেই, তাই ববটি হেলানো তলের ঠিক অভিলম্ব বরাবর সুতা প্রসারিত করে স্থির থাকবে। অর্থাৎ সুতাটি হেলানো তলের অভিলম্বের সাথে $0^\circ$ কোণ করবে (বা উল্লম্বের সাথে $\theta$ কোণে থাকবে)।</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1206,14 +1196,9 @@
           <t>$R$ ব্যাসার্ধের একটি মসৃণ স্থির অর্ধগোলকের শীর্ষবিন্দু থেকে সুষম রৈখিক ভর ঘনত্ব $\lambda$ বিশিষ্ট একটি নমনীয় দড়ি গোলকের পৃষ্ঠ ঘেঁষে ঝুলছে এবং এর শেষ প্রান্ত অনুভূমিক ব্যাসার্ধে স্পর্শ করেছে (চতুর্থাংশ বৃত্ত)। শীর্ষবিন্দুতে দড়িটিকে ধরে রাখতে প্রয়োজনীয় অনুভূমিক টান $T_0$ কত?</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>দড়ির একটি ক্ষুদ্রাংশ $d	heta$-এর ভর $dm = \lambda R d	heta$। উল্লম্বের সাথে কোণ $	heta$ হলে ওই অংশে স্পর্শকীয় ওজনের উপাংশ $dm g \sin	heta = \lambda R g \sin	heta d	heta$। পৃষ্ঠ মসৃণ হওয়ায় অভিলম্ব প্রতিক্রিয়া বল কোনো ঘর্ষণ তৈরি করে না। অতএব শীর্ষবিন্দুতে টান সমগ্র স্পর্শকীয় ওজনের সমাকলনের সমান: $T_0 = \int_0^{\pi/2} \lambda R g \sin	heta d	heta = \lambda R g [-\cos	heta]_0^{\pi/2} = \lambda R g (0 - (-1)) = \lambda R g$। যেহেতু মোট ভর $M = \lambda rac{\pi R}{2}$, সেহেতু টান $T_0 = rac{2}{\pi}Mg$।</t>
+          <t>দড়ির একটি ক্ষুদ্রাংশ $d\theta$-এর ভর $dm = \lambda R d\theta$। উল্লম্বের সাথে কোণ $\theta$ হলে ওই অংশে স্পর্শকীয় ওজনের উপাংশ $dm g \sin\theta = \lambda R g \sin\theta d\theta$। পৃষ্ঠ মসৃণ হওয়ায় অভিলম্ব প্রতিক্রিয়া বল কোনো ঘর্ষণ তৈরি করে না। অতএব শীর্ষবিন্দুতে টান সমগ্র স্পর্শকীয় ওজনের সমাকলনের সমান: $T_0 = \int_0^{\pi/2} \lambda R g \sin\theta d\theta = \lambda R g [-\cos\theta]_0^{\pi/2} = \lambda R g (0 - (-1)) = \lambda R g$। যেহেতু মোট ভর $M = \lambda \frac{\pi R}{2}$, সেহেতু টান $T_0 = \frac{2}{\pi}Mg$।</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1256,14 +1241,9 @@
           <t>একটি লিফট $a_0$ সমত্বরণে ওপরের দিকে উঠছে। লিফটের ভেতর স্প্রিং ধ্রুবক $k$-এর একটি স্প্রিং থেকে $m$ ভরের ব্লক ঝুলছে। সাম্যাবস্থায় স্প্রিংটির প্রসারণ কত হবে এবং সাম্যাবস্থা থেকে সামান্য টেনে ছেড়ে দিলে দোলনের পর্যায়কাল কি লিফটের ত্বরণের ওপর নির্ভর করবে?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>লিফটের অ-জড় প্রসঙ্গ কাঠামোতে ব্লকের ওপর ছদ্ম বল $m a_0$ নিচের দিকে কাজ করে। কার্যকর অভিকর্ষজ ত্বরণ $g_{	ext{eff}} = g + a_0$। সাম্যাবস্থায় বলের ভারসাম্য: $k x_0 = m g_{	ext{eff}} = m(g + a_0) \implies x_0 = rac{m(g + a_0)}{k}$। সাম্যাবস্থা থেকে সরণ $x$ ঘটালে স্প্রিং বল $F_{	ext{net}} = -k(x_0 + x) + m(g + a_0) = -kx$। অতএব গতির সমীকরণ $m \ddot{x} = -kx \implies \ddot{x} + rac{k}{m}x = 0$। পর্যায়কাল $T = 2\pi\sqrt{rac{m}{k}}$, যা লিফটের ত্বরণ $a_0$-এর ওপর সম্পূর্ণ স্বাধীন।</t>
+          <t>লিফটের অ-জড় প্রসঙ্গ কাঠামোতে ব্লকের ওপর ছদ্ম বল $m a_0$ নিচের দিকে কাজ করে। কার্যকর অভিকর্ষজ ত্বরণ $g_{\text{eff}} = g + a_0$। সাম্যাবস্থায় বলের ভারসাম্য: $k x_0 = m g_{\text{eff}} = m(g + a_0) \implies x_0 = \frac{m(g + a_0)}{k}$। সাম্যাবস্থা থেকে সরণ $x$ ঘটালে স্প্রিং বল $F_{\text{net}} = -k(x_0 + x) + m(g + a_0) = -kx$। অতএব গতির সমীকরণ $m \ddot{x} = -kx \implies \ddot{x} + \frac{k}{m}x = 0$। পর্যায়কাল $T = 2\pi\sqrt{\frac{m}{k}}$, যা লিফটের ত্বরণ $a_0$-এর ওপর সম্পূর্ণ স্বাধীন।</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1303,17 +1283,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>একটি উল্লম্ব মসৃণ তারের রিং যার ব্যাসার্ধ $R$, তার নিজস্ব উল্লম্ব ব্যাস বরাবর ধ্রুব কৌণিক বেগ $\omega$ নিয়ে ঘুরছে। রিংয়ের গায়ে লাগানো একটি পুঁতি রিংয়ের সর্বনিম্ন বিন্দু থেকে কত কৌণিক উচ্চতা $	heta$-তে সাম্যাবস্থায় অবস্থান করতে পারবে এবং এর জন্য $\omega$-এর সর্বনিম্ন শর্ত কী?</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি উল্লম্ব মসৃণ তারের রিং যার ব্যাসার্ধ $R$, তার নিজস্ব উল্লম্ব ব্যাস বরাবর ধ্রুব কৌণিক বেগ $\omega$ নিয়ে ঘুরছে। রিংয়ের গায়ে লাগানো একটি পুঁতি রিংয়ের সর্বনিম্ন বিন্দু থেকে কত কৌণিক উচ্চতা $\theta$-তে সাম্যাবস্থায় অবস্থান করতে পারবে এবং এর জন্য $\omega$-এর সর্বনিম্ন শর্ত কী?</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>উল্লম্বের সাথে পুঁতির অবস্থান কোণ $	heta$ হলে কেন্দ্র থেকে অনুভূমিক দূরত্ব $r = R\sin	heta$। পুঁতির ওপর প্রতিক্রিয়া বল $N$ কেন্দ্রের দিকে অভিমুখী। উল্লম্ব ভারসাম্য: $N\cos	heta = mg$। অনুভূমিক কেন্দ্রমুখী বল: $N\sin	heta = m\omega^2 r = m\omega^2 R\sin	heta$। দুটি সমীকরণ ভাগ করে পাই: $rac{N\sin	heta}{N\cos	heta} = rac{m\omega^2 R\sin	heta}{mg} \implies 	an	heta = rac{\omega^2 R}{g}\sin	heta$। এর একটি সমাধান $\sin	heta = 0 \implies 	heta = 0$ (সর্বনিম্ন বিন্দু)। অশূন্য সমাধানের জন্য: $rac{1}{\cos	heta} = rac{\omega^2 R}{g} \implies \cos	heta = rac{g}{\omega^2 R}$। যেহেতু $\cos	heta \le 1$, সেহেতু বাস্তব কোণ পাওয়ার শর্ত $\omega^2 R &gt; g \implies \omega &gt; \sqrt{rac{g}{R}}$।</t>
+          <t>উল্লম্বের সাথে পুঁতির অবস্থান কোণ $\theta$ হলে কেন্দ্র থেকে অনুভূমিক দূরত্ব $r = R\sin\theta$। পুঁতির ওপর প্রতিক্রিয়া বল $N$ কেন্দ্রের দিকে অভিমুখী। উল্লম্ব ভারসাম্য: $N\cos\theta = mg$। অনুভূমিক কেন্দ্রমুখী বল: $N\sin\theta = m\omega^2 r = m\omega^2 R\sin\theta$। দুটি সমীকরণ ভাগ করে পাই: $\frac{N\sin\theta}{N\cos\theta} = \frac{m\omega^2 R\sin\theta}{mg} \implies \tan\theta = \frac{\omega^2 R}{g}\sin\theta$। এর একটি সমাধান $\sin\theta = 0 \implies \theta = 0$ (সর্বনিম্ন বিন্দু)। অশূন্য সমাধানের জন্য: $\frac{1}{\cos\theta} = \frac{\omega^2 R}{g} \implies \cos\theta = \frac{g}{\omega^2 R}$। যেহেতু $\cos\theta \le 1$, সেহেতু বাস্তব কোণ পাওয়ার শর্ত $\omega^2 R &gt; g \implies \omega &gt; \sqrt{\frac{g}{R}}$।</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1353,17 +1328,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>একটি ফাঁপা সিলিন্ডারের মসৃণ অভ্যন্তরীণ অবতল তলে একটি ছোট কণা রাখা আছে। সিলিন্ডারটি অনুভূমিকভাবে সমত্বরণ $a$ নিয়ে ডানদিকে চললে কণাটি সিলিন্ডারের সর্বনিম্ন বিন্দু থেকে বামদিকে উল্লম্বের সাথে কত কোণ $	heta$ তৈরি করে স্থির থাকবে?</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি ফাঁপা সিলিন্ডারের মসৃণ অভ্যন্তরীণ অবতল তলে একটি ছোট কণা রাখা আছে। সিলিন্ডারটি অনুভূমিকভাবে সমত্বরণ $a$ নিয়ে ডানদিকে চললে কণাটি সিলিন্ডারের সর্বনিম্ন বিন্দু থেকে বামদিকে উল্লম্বের সাথে কত কোণ $\theta$ তৈরি করে স্থির থাকবে?</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>সিলিন্ডারের অভ্যন্তরীণ কাঠামোতে কণাটির ওপর অভিকর্ষজ বল $mg$ নিচের দিকে এবং ছদ্ম বল $ma$ বামদিকে ক্রিয়া করে। কার্যকর বল ভেক্টর উল্লম্বের সাথে কোণ উৎপন্ন করে $	an	heta = rac{F_{	ext{pseudo}}}{F_{	ext{grav}}} = rac{ma}{mg} = rac{a}{g}$। সিলিন্ডারের তল মসৃণ হওয়ায় অভিলম্ব প্রতিক্রিয়া বল $N$ এই লব্ধি বলের ঠিক বিপরীত দিকে ক্রিয়া করবে। সুতরাং কণাটি সর্বনিম্ন বিন্দু হতে পেছনের দিকে $	heta = 	an^{-1}\left(rac{a}{g}+          <t>সিলিন্ডারের অভ্যন্তরীণ কাঠামোতে কণাটির ওপর অভিকর্ষজ বল $mg$ নিচের দিকে এবং ছদ্ম বল $ma$ বামদিকে ক্রিয়া করে। কার্যকর বল ভেক্টর উল্লম্বের সাথে কোণ উৎপন্ন করে $\tan\theta = \frac{F_{\text{pseudo}}}{F_{\text{grav}}} = \frac{ma}{mg} = \frac{a}{g}$। সিলিন্ডারের তল মসৃণ হওয়ায় অভিলম্ব প্রতিক্রিয়া বল $N$ এই লব্ধি বলের ঠিক বিপরীত দিকে ক্রিয়া করবে। সুতরাং কণাটি সর্বনিম্ন বিন্দু হতে পেছনের দিকে $\theta = \tan^{-1}\left(\frac{a}{g} ight)$ কোণে সাম্যাবস্থায় স্থিতিশীল থাকবে।</t>
         </is>
       </c>
@@ -1404,17 +1374,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>একটি জটিল লিভার ও গিয়ার সংস্থায় ইনপুট প্রান্ত $x$ সরণ ঘটালে আউটপুট প্রান্ত $y = c x^2$ সরণ লাভ করে। ইনপুট প্রান্তে $F_{	ext{in}}$ ধ্রুব বল প্রয়োগ করলে $x = x_0$ বিন্দুতে আউটপুট প্রান্তে প্রাপ্ত বল $F_{	ext{out}}$ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি জটিল লিভার ও গিয়ার সংস্থায় ইনপুট প্রান্ত $x$ সরণ ঘটালে আউটপুট প্রান্ত $y = c x^2$ সরণ লাভ করে। ইনপুট প্রান্তে $F_{\text{in}}$ ধ্রুব বল প্রয়োগ করলে $x = x_0$ বিন্দুতে আউটপুট প্রান্তে প্রাপ্ত বল $F_{\text{out}}$ কত হবে?</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ভার্চুয়াল কাজের নীতি (Principle of Virtual Work) অনুসারে ঘর্ষণহীন ও আদর্শ লিভার সংস্থায় মোট ভার্চুয়াল কাজ শূন্য: $\delta W = F_{	ext{in}}\delta x - F_{	ext{out}}\delta y = 0 \implies F_{	ext{out}} = F_{	ext{in}}rac{\delta x}{\delta y} = F_{	ext{in}}rac{1}{rac{dy}{dx}}$। প্রদত্ত সম্পর্ক $y = c x^2 \implies rac{dy}{dx} = 2cx$। সুতরাং $x = x_0$ বিন্দুতে প্রাপ্ত আউটপুট বল $F_{	ext{out}} = rac{F_{	ext{in}}}{2cx_0}$।</t>
+          <t>ভার্চুয়াল কাজের নীতি (Principle of Virtual Work) অনুসারে ঘর্ষণহীন ও আদর্শ লিভার সংস্থায় মোট ভার্চুয়াল কাজ শূন্য: $\delta W = F_{\text{in}}\delta x - F_{\text{out}}\delta y = 0 \implies F_{\text{out}} = F_{\text{in}}\frac{\delta x}{\delta y} = F_{\text{in}}\frac{1}{\frac{dy}{dx}}$। প্রদত্ত সম্পর্ক $y = c x^2 \implies \frac{dy}{dx} = 2cx$। সুতরাং $x = x_0$ বিন্দুতে প্রাপ্ত আউটপুট বল $F_{\text{out}} = \frac{F_{\text{in}}}{2cx_0}$।</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1457,14 +1422,9 @@
           <t>একটি মসৃণ মেঝেতে $M_1$ ভরের একটি ব্লক রাখা। তার ওপর $M_2$ ভরের একটি ব্লক এবং তার ওপর $M_3$ ভরের ব্লক রাখা। ব্লকদ্বয়ের মধ্যকার ঘর্ষণ গুণাঙ্ক যথাক্রমে $\mu_1$ ($M_1$ ও $M_2$-এর মাঝে) এবং $\mu_2$ ($M_2$ ও $M_3$-এর মাঝে)। সর্বনিম্ন ব্লক $M_1$-এর ওপর অনুভূমিক বল $F$ প্রয়োগ করলে কোনো ব্লকের মাঝেই যেন পিছলানো না ঘটে তার জন্য $F$-এর সর্বোচ্চ মান কত?</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>যদি কেউ না পিছলায় তবে সংস্থার সামগ্রিক ত্বরণ $a = rac{F}{M_1 + M_2 + M_3}$। সবচেয়ে উপরের ব্লক $M_3$-কে এই ত্বরণে রাখার একমাত্র বল $M_2$ ও $M_3$-এর মধ্যকার ঘর্ষণ বল: $f_2 \le \mu_2 M_3 g \implies M_3 a \le \mu_2 M_3 g \implies a \le \mu_2 g$। আবার উপরের দুটি ব্লককে ($M_2 + M_3$) একসাথে টেনে রাখার জন্য $M_1$ ও $M_2$-এর মধ্যকার ঘর্ষণ বল: $f_1 \le \mu_1 (M_2 + M_3)g \implies (M_2 + M_3)a \le \mu_1 (M_2 + M_3)g \implies a \le \mu_1 g$। অতএব সংস্থার ত্বরণ $a_{\max} = \min(\mu_1 g, \mu_2 g)$। সুতরাং প্রযুক্ত সর্বোচ্চ বল $F_{\max} = (M_1 + M_2 + M_3)\min(\mu_1 g, \mu_2 g)$।</t>
+          <t>যদি কেউ না পিছলায় তবে সংস্থার সামগ্রিক ত্বরণ $a = \frac{F}{M_1 + M_2 + M_3}$। সবচেয়ে উপরের ব্লক $M_3$-কে এই ত্বরণে রাখার একমাত্র বল $M_2$ ও $M_3$-এর মধ্যকার ঘর্ষণ বল: $f_2 \le \mu_2 M_3 g \implies M_3 a \le \mu_2 M_3 g \implies a \le \mu_2 g$। আবার উপরের দুটি ব্লককে ($M_2 + M_3$) একসাথে টেনে রাখার জন্য $M_1$ ও $M_2$-এর মধ্যকার ঘর্ষণ বল: $f_1 \le \mu_1 (M_2 + M_3)g \implies (M_2 + M_3)a \le \mu_1 (M_2 + M_3)g \implies a \le \mu_1 g$। অতএব সংস্থার ত্বরণ $a_{\max} = \min(\mu_1 g, \mu_2 g)$। সুতরাং প্রযুক্ত সর্বোচ্চ বল $F_{\max} = (M_1 + M_2 + M_3)\min(\mu_1 g, \mu_2 g)$।</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1507,14 +1467,9 @@
           <t>একটি অনুভূমিক মসৃণ সোজা রড তার এক প্রান্তগামী উল্লম্ব অক্ষের সাপেক্ষে ধ্রুব কৌণিক বেগ $\omega$ নিয়ে ঘুরছে। রডের ভেতর পরানো $m$ ভরের একটি ছোট আংটি অক্ষ থেকে $r_0$ আদি দূরত্বে স্থির অবস্থা থেকে যাত্রা করে। আংটিটির অক্ষ থেকে দূরত্বের বৃদ্ধি এবং রড কর্তৃক আংটির ওপর প্রযুক্ত অনুভূমিক বল নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>রডের সাপেক্ষে আংটির রেডিয়াল ত্বরণ $\ddot{r} = \omega^2 r$। এর সমাধান $r(t) = r_0 \cosh(\omega t)$ এবং রেডিয়াল বেগ $\dot{r} = r_0 \omega \sinh(\omega t)$। রড মসৃণ হওয়ায় রড কর্তৃক বল কেবল লম্ব বা ট্রান্সভার্স (স্পর্শকীয়) দিকে প্রযুক্ত হয়। রডের সাপেক্ষে করিওলিস বল কাজ করে $F_{	ext{cor}} = 2m\omega\dot{r}$। রডের অক্ষীয় জড় কাঠামোতে স্পর্শকীয় ত্বরণ $a_	heta = rlpha + 2\dot{r}\omega = 0 + 2\omega \dot{r} = 2\omega^2 r_0 \sinh(\omega t)$। অতএব রড কর্তৃক আংটির ওপর প্রযুক্ত বল $N = m a_	heta = 2m\omega^2 r_0 \sinh(\omega t)$।</t>
+          <t>রডের সাপেক্ষে আংটির রেডিয়াল ত্বরণ $\ddot{r} = \omega^2 r$। এর সমাধান $r(t) = r_0 \cosh(\omega t)$ এবং রেডিয়াল বেগ $\dot{r} = r_0 \omega \sinh(\omega t)$। রড মসৃণ হওয়ায় রড কর্তৃক বল কেবল লম্ব বা ট্রান্সভার্স (স্পর্শকীয়) দিকে প্রযুক্ত হয়। রডের সাপেক্ষে করিওলিস বল কাজ করে $F_{\text{cor}} = 2m\omega\dot{r}$। রডের অক্ষীয় জড় কাঠামোতে স্পর্শকীয় ত্বরণ $a_\theta = rlpha + 2\dot{r}\omega = 0 + 2\omega \dot{r} = 2\omega^2 r_0 \sinh(\omega t)$। অতএব রড কর্তৃক আংটির ওপর প্রযুক্ত বল $N = m a_\theta = 2m\omega^2 r_0 \sinh(\omega t)$।</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1554,18 +1509,13 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>$m$ ভরের একটি ব্লক $v_0$ দ্রুতি নিয়ে একটি অরৈখিক শক্ত স্প্রিংয়ের সাথে ধাক্কা খায় যার বল অপেক্ষক $F(x) = -(kx + eta x^3)$ (যেখানে $k, eta &gt; 0$)। স্প্রিংটির সর্বোচ্চ সংকোচন $x_m$ নির্ণয়ের জন্য বীজগণিতীয় সমীকরণটি গঠন কর এবং $eta x_m^2 \ll k$ হলে প্রথম ক্রমের আসন্ন মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>$m$ ভরের একটি ব্লক $v_0$ দ্রুতি নিয়ে একটি অরৈখিক শক্ত স্প্রিংয়ের সাথে ধাক্কা খায় যার বল অপেক্ষক $F(x) = -(kx + \beta x^3)$ (যেখানে $k, \beta &gt; 0$)। স্প্রিংটির সর্বোচ্চ সংকোচন $x_m$ নির্ণয়ের জন্য বীজগণিতীয় সমীকরণটি গঠন কর এবং $\beta x_m^2 \ll k$ হলে প্রথম ক্রমের আসন্ন মান নির্ণয় কর।</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>কাজ-শক্তি উপপাদ্য অনুসারে ব্লকের আদি গতিশক্তি স্প্রিংয়ের বিভব শক্তিতে রূপান্তরিত হয়: $\Delta K = -W \implies rac{1}{2}m v_0^2 = \int_0^{x_m} (kx + eta x^3)dx = rac{1}{2}k x_m^2 + rac{1}{4}eta x_m^4$। উভয় পাশে ৪ দ্বারা গুণ করলে $eta x_m^4 + 2k x_m^2 - 2m v_0^2 = 0$। $x_m^2$-এর দ্বিঘাত সমীকরণ সমাধান করে: $x_m^2 = rac{-2k + \sqrt{4k^2 + 8eta m v_0^2}}{2eta} = rac{k}{eta}\left(\sqrt{1 + rac{2eta m v_0^2}{k^2}} - 1-ight)$। প্রথম ক্রমের দ্বিপদী বিস্তারে $\sqrt{1+y} pprox 1 + rac{y}{2} - rac{y^2}{8}$, ফলে $x_m pprox \sqrt{rac{m v_0^2}{k}}\left(1 - rac{eta m v_0^2}{4k^2}+          <t>কাজ-শক্তি উপপাদ্য অনুসারে ব্লকের আদি গতিশক্তি স্প্রিংয়ের বিভব শক্তিতে রূপান্তরিত হয়: $\Delta K = -W \implies \frac{1}{2}m v_0^2 = \int_0^{x_m} (kx + \beta x^3)dx = \frac{1}{2}k x_m^2 + \frac{1}{4}\beta x_m^4$। উভয় পাশে ৪ দ্বারা গুণ করলে $\beta x_m^4 + 2k x_m^2 - 2m v_0^2 = 0$। $x_m^2$-এর দ্বিঘাত সমীকরণ সমাধান করে: $x_m^2 = \frac{-2k + \sqrt{4k^2 + 8\beta m v_0^2}}{2eta} = \frac{k}{eta}\left(\sqrt{1 + \frac{2\beta m v_0^2}{k^2}} - 1+ight)$। প্রথম ক্রমের দ্বিপদী বিস্তারে $\sqrt{1+y} pprox 1 + \frac{y}{2} - \frac{y^2}{8}$, ফলে $x_m pprox \sqrt{\frac{m v_0^2}{k}}\left(1 - \frac{\beta m v_0^2}{4k^2} ight)$।</t>
         </is>
       </c>
@@ -1609,14 +1559,9 @@
           <t>একটি মসৃণ অনুভূমিক সমতলে $m_1$ ও $m_2$ ভরের দুটি ব্লক একটি $k$ স্প্রিং ধ্রুবকের হালকা স্প্রিং দ্বারা সংযুক্ত। ব্লক দুটিকে সাম্যাবস্থা থেকে $x_0$ পরিমাণ টেনে ছেড়ে দেওয়া হলো। ভরকেন্দ্রের সাপেক্ষে প্রতিটি ব্লকের দোলনের বিস্তার এবং পর্যায়কাল নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>সংস্থার ওপর কোনো বাহ্যিক বল নেই, ফলে ভরকেন্দ্র সর্বদা স্থির থাকবে। সংস্থার কার্যকর বা হ্রাসকৃত ভর (Reduced Mass) $\mu = rac{m_1 m_2}{m_1 + m_2}$। ভরকেন্দ্রের সাপেক্ষে কার্যকর স্প্রিং ধ্রুবক অপরিবর্তিত থাকে, ফলে দোলনের কৌণিক কম্পাঙ্ক $\omega = \sqrt{rac{k}{\mu}} = \sqrt{rac{k(m_1 + m_2)}{m_1 m_2}}$ এবং পর্যায়কাল $T = 2\pi\sqrt{rac{m_1 m_2}{k(m_1 + m_2)}}$। আদি প্রসারণ $x_0 = x_1 + x_2$ এবং ভরকেন্দ্র স্থিরতার শর্ত $m_1 x_1 = m_2 x_2$। সুতরাং $m_1$ ব্লকের বিস্তার $A_1 = rac{m_2}{m_1 + m_2} x_0$ এবং $m_2$ ব্লকের বিস্তার $A_2 = rac{m_1}{m_1 + m_2} x_0$।</t>
+          <t>সংস্থার ওপর কোনো বাহ্যিক বল নেই, ফলে ভরকেন্দ্র সর্বদা স্থির থাকবে। সংস্থার কার্যকর বা হ্রাসকৃত ভর (Reduced Mass) $\mu = \frac{m_1 m_2}{m_1 + m_2}$। ভরকেন্দ্রের সাপেক্ষে কার্যকর স্প্রিং ধ্রুবক অপরিবর্তিত থাকে, ফলে দোলনের কৌণিক কম্পাঙ্ক $\omega = \sqrt{\frac{k}{\mu}} = \sqrt{\frac{k(m_1 + m_2)}{m_1 m_2}}$ এবং পর্যায়কাল $T = 2\pi\sqrt{\frac{m_1 m_2}{k(m_1 + m_2)}}$। আদি প্রসারণ $x_0 = x_1 + x_2$ এবং ভরকেন্দ্র স্থিরতার শর্ত $m_1 x_1 = m_2 x_2$। সুতরাং $m_1$ ব্লকের বিস্তার $A_1 = \frac{m_2}{m_1 + m_2} x_0$ এবং $m_2$ ব্লকের বিস্তার $A_2 = \frac{m_1}{m_1 + m_2} x_0$।</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1659,14 +1604,9 @@
           <t>একটি উল্লম্ব স্প্রিংয়ের উপরের প্রান্তে $M$ ভরের একটি পাটাতন দৃঢ়ভাবে আটকানো যার ওপর $m$ ভরের একটি বস্তু রাখা। সংস্থাটি $A$ বিস্তার নিয়ে উল্লম্ব সরল ছন্দিত স্পন্দনে দুলছে। দোলনের কোন বিন্দুতে বস্তুটি পাটাতন থেকে বিচ্ছিন্ন হওয়ার উপক্রম হবে এবং এর জন্য প্রয়োজনীয় ন্যূনতম বিস্তার $A_{\min}$ কত?</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>বস্তুটির ওপর ক্রিয়াশীল বল হলো অভিলম্ব প্রতিক্রিয়া বল $N$ এবং ওজন $mg$। যখন পাটাতনটি সর্বোচ্চ বিন্দুতে থাকে, তখন তার নিম্নমুখী ত্বরণ সর্বোচ্চ হয়: $a_{\max} = \omega^2 A$। বস্তুটির গতির সমীকরণ: $mg - N = m a \implies N = m(g - \omega^2 A)$। পাটাতন থেকে বিচ্ছিন্ন হওয়ার শর্ত $N = 0 \implies g - \omega^2 A = 0 \implies A_{\min} = rac{g}{\omega^2} = rac{(M+m)g}{k}$। অতএব সর্বোচ্চ বিন্দুতে বিচ্ছিন্নতা ঘটবে যদি বিস্তার $A \ge rac{(M+m)g}{k}$ হয়।</t>
+          <t>বস্তুটির ওপর ক্রিয়াশীল বল হলো অভিলম্ব প্রতিক্রিয়া বল $N$ এবং ওজন $mg$। যখন পাটাতনটি সর্বোচ্চ বিন্দুতে থাকে, তখন তার নিম্নমুখী ত্বরণ সর্বোচ্চ হয়: $a_{\max} = \omega^2 A$। বস্তুটির গতির সমীকরণ: $mg - N = m a \implies N = m(g - \omega^2 A)$। পাটাতন থেকে বিচ্ছিন্ন হওয়ার শর্ত $N = 0 \implies g - \omega^2 A = 0 \implies A_{\min} = \frac{g}{\omega^2} = \frac{(M+m)g}{k}$। অতএব সর্বোচ্চ বিন্দুতে বিচ্ছিন্নতা ঘটবে যদি বিস্তার $A \ge \frac{(M+m)g}{k}$ হয়।</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1706,19 +1646,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>স্থির অবস্থায় থাকা $m$ ভরের একটি বস্তুর ওপর সময়ভিত্তিক পরিবর্তনশীল বল $F(t) = lpha t$ প্রয়োগ করা হলো ($lpha$ একটি ধ্রুবক)। বল প্রয়োগের ফলে বস্তুটির গতিশক্তি কখন প্রযুক্ত ক্ষমতার সমানুপাতিক হবে এবং $t$ সময় পর বস্তুটির গতিশক্তি কত হবে?</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>স্থির অবস্থায় থাকা $m$ ভরের একটি বস্তুর ওপর সময়ভিত্তিক পরিবর্তনশীল বল $F(t) = \alpha t$ প্রয়োগ করা হলো ($\alpha$ একটি ধ্রুবক)। বল প্রয়োগের ফলে বস্তুটির গতিশক্তি কখন প্রযুক্ত ক্ষমতার সমানুপাতিক হবে এবং $t$ সময় পর বস্তুটির গতিশক্তি কত হবে?</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>নিউটনের দ্বিতীয় সূত্র: $m rac{dv}{dt} = lpha t \implies dv = rac{lpha}{m} t dt \implies v(t) = rac{lpha t^2}{2m}$। গতিশক্তি $K(t) = rac{1}{2}m v^2 = rac{1}{2}m \left(rac{lpha t^2}{2m}-ight)^2 = rac{lpha^2 t^4}{8m}$। প্রযুক্ত ক্ষমতা $P(t) = F(t)v(t) = (lpha t)\left(rac{lpha t^2}{2m}-ight) = rac{lpha^2 t^3}{2m}$। গতিশক্তি ও ক্ষমতার অনুপাত $rac{K(t)}{P(t)} = rac{rac{lpha^2 t^4}{8m}}{rac{lpha^2 t^3}{2m}} = rac{t}{4}$। অতএব গতিশক্তি সময়ের সকল মানেই $K = rac{t}{4}P$ মেনে চলে।</t>
+          <t>নিউটনের দ্বিতীয় সূত্র: $m \frac{dv}{dt} = \alpha t \implies dv = \frac{\alpha}{m} t dt \implies v(t) = \frac{\alpha t^2}{2m}$। গতিশক্তি $K(t) = \frac{1}{2}m v^2 = \frac{1}{2}m \left(\frac{\alpha t^2}{2m}+ight)^2 = \frac{\alpha^2 t^4}{8m}$। প্রযুক্ত ক্ষমতা $P(t) = F(t)v(t) = (\alpha t)\left(\frac{\alpha t^2}{2m}+ight) = \frac{\alpha^2 t^3}{2m}$। গতিশক্তি ও ক্ষমতার অনুপাত $\frac{K(t)}{P(t)} = \frac{\frac{\alpha^2 t^4}{8m}}{\frac{\alpha^2 t^3}{2m}} = \frac{t}{4}$। অতএব গতিশক্তি সময়ের সকল মানেই $K = \frac{t}{4}P$ মেনে চলে।</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1761,15 +1696,10 @@
           <t>একটি কণার ওপর ক্রিয়াশীল এক-মাত্রিক সংরক্ষণশীল বল $F(x) = -a x + b x^2$ ($a, b &gt; 0$)। কণাটির সম্ভাব্য সাম্যাবস্থাগুলি চিহ্নিত কর এবং তাদের স্থিতিশীলতা (Stability) নির্ধারণ কর।</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>সাম্যাবস্থার শর্ত $F(x) = 0 \implies -ax + bx^2 = 0 \implies x(-a + bx) = 0$। সুতরাং দুটি সাম্যাবস্থা রয়েছে: $x = 0$ এবং $x = rac{a}{b}$। বিভব শক্তি $U(x) = -\int F(x)dx = rac{1}{2}ax^2 - rac{1}{3}bx^3$। দ্বিতীয় অন্তরক $rac{d^2 U}{dx^2} = -rac{dF}{dx} = -(-a + 2bx) = a - 2bx$। (১) $x = 0$ বিন্দুতে $\left.rac{d^2 U}{dx^2}-ight|_0 = a &gt; 0$, যা বিভব শক্তির স্থানীয় ন্যূনতম মান নির্দেশ করে; ফলে $x = 0$ একটি স্থিতিশীল (Stable) সাম্যাবস্থা। (২) $x = rac{a}{b}$ বিন্দুতে $\left.rac{d^2 U}{dx^2}+          <t>সাম্যাবস্থার শর্ত $F(x) = 0 \implies -ax + bx^2 = 0 \implies x(-a + bx) = 0$। সুতরাং দুটি সাম্যাবস্থা রয়েছে: $x = 0$ এবং $x = \frac{a}{b}$। বিভব শক্তি $U(x) = -\int F(x)dx = \frac{1}{2}ax^2 - \frac{1}{3}bx^3$। দ্বিতীয় অন্তরক $\frac{d^2 U}{dx^2} = -\frac{dF}{dx} = -(-a + 2bx) = a - 2bx$। (১) $x = 0$ বিন্দুতে $\left.\frac{d^2 U}{dx^2}+ight|_0 = a &gt; 0$, যা বিভব শক্তির স্থানীয় ন্যূনতম মান নির্দেশ করে; ফলে $x = 0$ একটি স্থিতিশীল (Stable) সাম্যাবস্থা। (২) $x = \frac{a}{b}$ বিন্দুতে $\left.\frac{d^2 U}{dx^2} ight|_{a/b} = a - 2b(a/b) = -a &lt; 0$, যা স্থানীয় সর্বোচ্চ মান নির্দেশ করে; ফলে এটি একটি অস্থিতিশীল (Unstable) সাম্যাবস্থা।</t>
         </is>
       </c>
@@ -1810,21 +1740,16 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>একটি কণার ওপর প্রযুক্ত বল সময়ের সাথে সাইনুসয়ডাল আকারে পরিবর্তিত হয়: $F(t) = F_0 \sin\left(rac{\pi t}{T}+          <t>একটি কণার ওপর প্রযুক্ত বল সময়ের সাথে সাইনুসয়ডাল আকারে পরিবর্তিত হয়: $F(t) = F_0 \sin\left(\frac{\pi t}{T} ight)$ ($0 \le t \le T$ সময়ের জন্য)। এই ঘাত বলের কারণে $m$ ভরের স্থির কণার চূড়ান্ত ভরবেগ এবং গড় বল নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ঘাত বা ভরবেগের পরিবর্তন হলো বলের সময়ভিত্তিক সমাকলন: $J = \Delta p = \int_0^T F(t)dt = \int_0^T F_0 \sin\left(rac{\pi t}{T}-ight)dt = F_0 \left[ -rac{T}{\pi}\cos\left(rac{\pi t}{T}+          <t>ঘাত বা ভরবেগের পরিবর্তন হলো বলের সময়ভিত্তিক সমাকলন: $J = \Delta p = \int_0^T F(t)dt = \int_0^T F_0 \sin\left(\frac{\pi t}{T}+ight)dt = F_0 \left[ -\frac{T}{\pi}\cos\left(\frac{\pi t}{T} ight) -ight]_0^T = F_0 rac{T}{\pi}(-\cos\pi + \cos 0) = rac{2F_0 T}{\pi}$। অতএব কণার চূড়ান্ত ভরবেগ $p_f = rac{2F_0 T}{\pi}$ এবং চূড়ান্ত বেগ $v_f = rac{2F_0 T}{\pi m}$। গড় বল $ar{F} = rac{J}{T} = rac{2}{\pi}F_0 pprox 0.637 F_0$।</t>
+ight]_0^T = F_0 \frac{T}{\pi}(-\cos\pi + \cos 0) = \frac{2F_0 T}{\pi}$। অতএব কণার চূড়ান্ত ভরবেগ $p_f = \frac{2F_0 T}{\pi}$ এবং চূড়ান্ত বেগ $v_f = \frac{2F_0 T}{\pi m}$। গড় বল $ar{F} = \frac{J}{T} = \frac{2}{\pi}F_0 pprox 0.637 F_0$।</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1867,18 +1792,13 @@
           <t>একটি মসৃণ টেবিলে রাখা $m$ ভরের একটি ব্লক $v_0$ বেগে গতিশীল হয়ে একটি দেয়ালের সাথে যুক্ত $k$ স্প্রিং ধ্রুবকের স্প্রিংয়ে আঘাত করে। যদি স্প্রিংটির নিজস্ব ভর $m_s$ অগ্রাহ্য না করা যায়, তবে স্প্রিংটির সর্বোচ্চ সংকোচনের মান কীভাবে পরিবর্তিত হবে?</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>যখন স্প্রিংয়ের মুক্ত প্রান্ত $x$ সংকুচিত হয় এবং এর বেগ $v$ হয়, তখন স্প্রিংয়ের প্রতিটি অংশের বেগ সুষমভাবে $0$ থেকে $v$ পর্যন্ত বণ্টিত থাকে। স্প্রিংয়ের ক্ষুদ্রাংশ $dy$-এর বেগ $v(y) = rac{y}{L}v$। স্প্রিংয়ের নিজস্ব গতিশক্তি $K_s = \int_0^L rac{1}{2}\left(rac{m_s}{L}dy-ight)\left(rac{y}{L}v-ight)^2 = rac{1}{6}m_s v^2$। অতএব ব্লকের সাথে স্প্রিংয়ের কার্যকর গতিশক্তি $K_{	ext{eff}} = rac{1}{2}\left(m + rac{m_s}{3}-ight)v^2$। শক্তির সংরক্ষণশীলতায় সর্বোচ্চ সংকোচনে $v=0$ এবং সমস্ত শক্তি স্প্রিংয়ের স্থিতি শক্তিতে জমা হয়: $rac{1}{2}\left(m + rac{m_s}{3}-ight)v_0^2 = rac{1}{2}k x_{\max}^2 \implies x_{\max} = v_0\sqrt{rac{m + m_s/3}{k}}$।</t>
+          <t>যখন স্প্রিংয়ের মুক্ত প্রান্ত $x$ সংকুচিত হয় এবং এর বেগ $v$ হয়, তখন স্প্রিংয়ের প্রতিটি অংশের বেগ সুষমভাবে $0$ থেকে $v$ পর্যন্ত বণ্টিত থাকে। স্প্রিংয়ের ক্ষুদ্রাংশ $dy$-এর বেগ $v(y) = \frac{y}{L}v$। স্প্রিংয়ের নিজস্ব গতিশক্তি $K_s = \int_0^L \frac{1}{2}\left(\frac{m_s}{L}dy+ight)\left(\frac{y}{L}v+ight)^2 = \frac{1}{6}m_s v^2$। অতএব ব্লকের সাথে স্প্রিংয়ের কার্যকর গতিশক্তি $K_{\text{eff}} = \frac{1}{2}\left(m + \frac{m_s}{3}+ight)v^2$। শক্তির সংরক্ষণশীলতায় সর্বোচ্চ সংকোচনে $v=0$ এবং সমস্ত শক্তি স্প্রিংয়ের স্থিতি শক্তিতে জমা হয়: $\frac{1}{2}\left(m + \frac{m_s}{3}+ight)v_0^2 = \frac{1}{2}k x_{\max}^2 \implies x_{\max} = v_0\sqrt{\frac{m + m_s/3}{k}}$।</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1918,19 +1838,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>একটি কণার ওপর একটি কেন্দ্রীয় বিকর্ষণ বল $F(r) = rac{k}{r^3}$ ক্রিয়াশীল ($k &gt; 0$)। কণাটি অসীম দূরত্ব থেকে ইমপ্যাক্ট প্যারামিটার $b$ এবং আদি বেগ $v_0$ নিয়ে নিক্ষিপ্ত হলে কণাটির নিকটতম দূরত্ব $r_{\min}$ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি কণার ওপর একটি কেন্দ্রীয় বিকর্ষণ বল $F(r) = \frac{k}{r^3}$ ক্রিয়াশীল ($k &gt; 0$)। কণাটি অসীম দূরত্ব থেকে ইমপ্যাক্ট প্যারামিটার $b$ এবং আদি বেগ $v_0$ নিয়ে নিক্ষিপ্ত হলে কণাটির নিকটতম দূরত্ব $r_{\min}$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>কৌণিক ভরবেগ সংরক্ষণশীলতা: $L = m v_0 b = m r_{\min} v_{\max} \implies v_{\max} = rac{v_0 b}{r_{\min}}$। শক্তির সংরক্ষণশীলতা: বিভব শক্তি $U(r) = -\int_\infty^r \left(-rac{k}{r^3}-ight)dr = rac{k}{2r^2}$। অসীমে মোট শক্তি $E = rac{1}{2}m v_0^2$। নিকটতম দূরত্বে রেডিয়াল বেগ শূন্য: $rac{1}{2}m v_0^2 = rac{1}{2}m v_{\max}^2 + rac{k}{2r_{\min}^2} = rac{1}{2}m \left(rac{v_0 b}{r_{\min}}-ight)^2 + rac{k}{2r_{\min}^2} = rac{m v_0^2 b^2 + k}{2 r_{\min}^2}$। উভয় পাশে $rac{1}{2}$ কেটে পাই: $m v_0^2 r_{\min}^2 = m v_0^2 b^2 + k \implies r_{\min}^2 = b^2 + rac{k}{m v_0^2} \implies r_{\min} = \sqrt{b^2 + rac{k}{m v_0^2}}$।</t>
+          <t>কৌণিক ভরবেগ সংরক্ষণশীলতা: $L = m v_0 b = m r_{\min} v_{\max} \implies v_{\max} = \frac{v_0 b}{r_{\min}}$। শক্তির সংরক্ষণশীলতা: বিভব শক্তি $U(r) = -\int_\infty^r \left(-\frac{k}{r^3}+ight)dr = \frac{k}{2r^2}$। অসীমে মোট শক্তি $E = \frac{1}{2}m v_0^2$। নিকটতম দূরত্বে রেডিয়াল বেগ শূন্য: $\frac{1}{2}m v_0^2 = \frac{1}{2}m v_{\max}^2 + \frac{k}{2r_{\min}^2} = \frac{1}{2}m \left(\frac{v_0 b}{r_{\min}}+ight)^2 + \frac{k}{2r_{\min}^2} = \frac{m v_0^2 b^2 + k}{2 r_{\min}^2}$। উভয় পাশে $\frac{1}{2}$ কেটে পাই: $m v_0^2 r_{\min}^2 = m v_0^2 b^2 + k \implies r_{\min}^2 = b^2 + \frac{k}{m v_0^2} \implies r_{\min} = \sqrt{b^2 + \frac{k}{m v_0^2}}$।</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1973,15 +1888,10 @@
           <t>$M$ ভরের একটি মসৃণ ট্রলির মেঝেতে $k$ স্প্রিং ধ্রুবকের স্প্রিং দ্বারা $m$ ভরের একটি ব্লক যুক্ত। ট্রলিটি অনুভূমিক মসৃণ মেঝেতে মুক্তভাবে চলতে পারে। সংস্থাকে স্প্রিং প্রসারিত অবস্থায় ছেড়ে দিলে স্পন্দনের পর্যায়কাল কত হবে?</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ট্রলি ও ব্লকের ওপর অনুভূমিক বরাবর কোনো বাহ্যিক বল নেই। ট্রলির সরণ $X$ এবং ব্লকের সরণ $x$ হলে ভরকেন্দ্রের স্থায়িত্ব থেকে $M X + m x = 0 \implies X = -rac{m}{M}x$। স্প্রিংয়ের মোট সংকোচন বা প্রসারণ $\Delta L = x - X = x\left(1 + rac{m}{M}-ight) = rac{M+m}{M}x$। ব্লকের ওপর প্রযুক্ত স্প্রিং বল $F = -k \Delta L = -krac{M+m}{M}x$। অতএব ব্লকের গতির সমীকরণ $m \ddot{x} = -rac{k(M+m)}{M}x \implies \ddot{x} + rac{k(M+m)}{M m}x = 0$। কৌণিক কম্পাঙ্ক $\omega = \sqrt{rac{k}{\mu}}$ যেখানে $\mu = rac{M m}{M + m}$। পর্যায়কাল $T = 2\pi\sqrt{rac{M m}{k(M+m)}}$।</t>
+          <t>ট্রলি ও ব্লকের ওপর অনুভূমিক বরাবর কোনো বাহ্যিক বল নেই। ট্রলির সরণ $X$ এবং ব্লকের সরণ $x$ হলে ভরকেন্দ্রের স্থায়িত্ব থেকে $M X + m x = 0 \implies X = -\frac{m}{M}x$। স্প্রিংয়ের মোট সংকোচন বা প্রসারণ $\Delta L = x - X = x\left(1 + \frac{m}{M}+ight) = \frac{M+m}{M}x$। ব্লকের ওপর প্রযুক্ত স্প্রিং বল $F = -k \Delta L = -krac{M+m}{M}x$। অতএব ব্লকের গতির সমীকরণ $m \ddot{x} = -\frac{k(M+m)}{M}x \implies \ddot{x} + \frac{k(M+m)}{M m}x = 0$। কৌণিক কম্পাঙ্ক $\omega = \sqrt{\frac{k}{\mu}}$ যেখানে $\mu = \frac{M m}{M + m}$। পর্যায়কাল $T = 2\pi\sqrt{\frac{M m}{k(M+m)}}$।</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2025,21 +1935,16 @@
 ho$ ঘনত্বের একটি তরলে আংশিক নিমজ্জিত অবস্থায় ভাসছে। সিলিন্ডারটিকে সাম্যাবস্থা থেকে সামান্য $x_0$ পরিমাণ নিচের দিকে চেপে ছেড়ে দিলে এর গতির প্রকৃতি কী হবে এবং পর্যায়কাল নির্ণয় কর?</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>সাম্যাবস্থায় ওজনের সমান প্লবতা বল ক্রিয়া করে: $M g = A h -ho g$। সাম্যাবস্থা থেকে আরও $x$ পরিমাণ নিমজ্জিত করলে অতিরিক্ত ঊর্ধ্বমুখী প্লবতা বল (প্রত্যয়নী বল) $F_{	ext{net}} = -A -ho g x$। নিউটনের গতির সমীকরণ: $M rac{d^2 x}{dt^2} = -A -ho g x \implies rac{d^2 x}{dt^2} + \left(rac{A+ho g$। সাম্যাবস্থা থেকে আরও $x$ পরিমাণ নিমজ্জিত করলে অতিরিক্ত ঊর্ধ্বমুখী প্লবতা বল (প্রত্যয়নী বল) $F_{\text{net}} = -A +ho g x$। নিউটনের গতির সমীকরণ: $M \frac{d^2 x}{dt^2} = -A +ho g x \implies \frac{d^2 x}{dt^2} + \left(\frac{A ho g}{M}-ight)x = 0$। এটি একটি সরল ছন্দিত স্পন্দন নির্দেশ করে যার কার্যকর বল ধ্রুবক $k_{	ext{eff}} = A -ho g$। সুতরাং দোলনের পর্যায়কাল $T = 2\pi\sqrt{rac{M}{A-ho g}} = 2\pi\sqrt{rac{h}{g}}$, যেখানে $h$ হলো সাম্যাবস্থায় নিমজ্জিত অংশের গভীরতা।</t>
+ight)x = 0$। এটি একটি সরল ছন্দিত স্পন্দন নির্দেশ করে যার কার্যকর বল ধ্রুবক $k_{\text{eff}} = A +ho g$। সুতরাং দোলনের পর্যায়কাল $T = 2\pi\sqrt{\frac{M}{A+ho g}} = 2\pi\sqrt{\frac{h}{g}}$, যেখানে $h$ হলো সাম্যাবস্থায় নিমজ্জিত অংশের গভীরতা।</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2082,15 +1987,10 @@
           <t>একটি মসৃণ অনুভূমিক মেঝের ওপর $M$ ভরের ব্লক রাখা। তার ওপর $m$ ভরের একটি ব্লক রাখা যার সাথে $M$-এর স্থৈতিক ও গতীয় ঘর্ষণ গুণাঙ্ক যথাক্রমে $\mu_s$ ও $\mu_k$। উপরের ব্লক $m$-এর ওপর অনুভূমিক বল $F$ প্রয়োগ করা হলে $F$-এর কোন মানের জন্য পিছলানো শুরু হবে এবং পিছলানোর পর ব্লক দুটির আলাদা ত্বরণ কত হবে?</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>উভয় ব্লক একসাথে চলার জন্য সর্বোচ্চ ত্বরণ প্রদান করে নিচের ব্লকের ওপর ক্রিয়াশীল ঘর্ষণ বল: $f_{\max} = \mu_s mg = M a_{\max} \implies a_{\max} = rac{\mu_s mg}{M}$। উভয় ব্লকের ওপর প্রযুক্ত মোট বল $F = (M+m)a \implies F_{	ext{slip}} = (M+m)rac{\mu_s mg}{M} = \mu_s mg\left(1 + rac{m}{M}-ight)$। যদি $F &gt; F_{	ext{slip}}$ হয়, তবে পিছলানো ঘটবে। পিছলানোর পর গতীয় ঘর্ষণ বল $f_k = \mu_k mg$। ফলে উপরের ব্লকের ত্বরণ $a_m = rac{F - \mu_k mg}{m}$ এবং নিচের ব্লকের ত্বরণ $a_M = rac{\mu_k mg}{M}$।</t>
+          <t>উভয় ব্লক একসাথে চলার জন্য সর্বোচ্চ ত্বরণ প্রদান করে নিচের ব্লকের ওপর ক্রিয়াশীল ঘর্ষণ বল: $f_{\max} = \mu_s mg = M a_{\max} \implies a_{\max} = \frac{\mu_s mg}{M}$। উভয় ব্লকের ওপর প্রযুক্ত মোট বল $F = (M+m)a \implies F_{\text{slip}} = (M+m)\frac{\mu_s mg}{M} = \mu_s mg\left(1 + \frac{m}{M}+ight)$। যদি $F &gt; F_{\text{slip}}$ হয়, তবে পিছলানো ঘটবে। পিছলানোর পর গতীয় ঘর্ষণ বল $f_k = \mu_k mg$। ফলে উপরের ব্লকের ত্বরণ $a_m = \frac{F - \mu_k mg}{m}$ এবং নিচের ব্লকের ত্বরণ $a_M = \frac{\mu_k mg}{M}$।</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2130,17 +2030,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>আগের ব্যবস্থায় বল $F$ যদি উপরের ব্লকে না দিয়ে নিচের ব্লক $M$-এর ওপর প্রয়োগ করা হয়, তবে পিছলানো শুরুর ক্রান্তিক বল $F'_{	ext{slip}}$ কত হবে এবং $F &gt; F'_{	ext{slip}}$ অবস্থায় ব্লকদ্বয়ের ত্বরণ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>আগের ব্যবস্থায় বল $F$ যদি উপরের ব্লকে না দিয়ে নিচের ব্লক $M$-এর ওপর প্রয়োগ করা হয়, তবে পিছলানো শুরুর ক্রান্তিক বল $F'_{\text{slip}}$ কত হবে এবং $F &gt; F'_{\text{slip}}$ অবস্থায় ব্লকদ্বয়ের ত্বরণ কত হবে?</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>নিচের ব্লকে বল দিলে উপরের ব্লককে গতিশীল করার একমাত্র বল ঘর্ষণ বল: $f \le \mu_s mg \implies m a \le \mu_s mg \implies a_{\max} = \mu_s g$। সংস্থা একসাথে চলার সর্বোচ্চ ত্বরণ $\mu_s g$। অতএব ক্রান্তিক বল $F'_{	ext{slip}} = (M+m)a_{\max} = \mu_s (M+m)g$। বল এর চেয়ে বেশি হলে পিছলানো ঘটবে। তখন উপরের ব্লকের ত্বরণ ধ্রুব থাকবে: $a_m = rac{f_k}{m} = \mu_k g$। নিচের ব্লকের ত্বরণ হবে $a_M = rac{F - \mu_k mg}{M}$।</t>
+          <t>নিচের ব্লকে বল দিলে উপরের ব্লককে গতিশীল করার একমাত্র বল ঘর্ষণ বল: $f \le \mu_s mg \implies m a \le \mu_s mg \implies a_{\max} = \mu_s g$। সংস্থা একসাথে চলার সর্বোচ্চ ত্বরণ $\mu_s g$। অতএব ক্রান্তিক বল $F'_{\text{slip}} = (M+m)a_{\max} = \mu_s (M+m)g$। বল এর চেয়ে বেশি হলে পিছলানো ঘটবে। তখন উপরের ব্লকের ত্বরণ ধ্রুব থাকবে: $a_m = \frac{f_k}{m} = \mu_k g$। নিচের ব্লকের ত্বরণ হবে $a_M = \frac{F - \mu_k mg}{M}$।</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2181,7 +2076,7 @@
       <c r="G24" t="inlineStr">
         <is>
           <t>##PRESET:incline(30,10,true)[size:medium]##
-$	heta$ নতি কোণের একটি অমসৃণ হেলানো তলে $m$ ভরের একটি ব্লক রাখা যার স্থৈতিক ঘর্ষণ গুণাঙ্ক $\mu$ ($	an	heta &gt; \mu$)। ব্লকটিকে তলের ওপর স্থির রাখতে তলের সমান্তরালে প্রয়োগযোগ্য সর্বনিম্ন বল $F_{\min}$ এবং সর্বোচ্চ বল $F_{\max}$ নির্ণয় কর।</t>
+$\theta$ নতি কোণের একটি অমসৃণ হেলানো তলে $m$ ভরের একটি ব্লক রাখা যার স্থৈতিক ঘর্ষণ গুণাঙ্ক $\mu$ ($\tan\theta &gt; \mu$)। ব্লকটিকে তলের ওপর স্থির রাখতে তলের সমান্তরালে প্রয়োগযোগ্য সর্বনিম্ন বল $F_{\min}$ এবং সর্বোচ্চ বল $F_{\max}$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2191,7 +2086,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>যেহেতু $	an	heta &gt; \mu$, তাই বল প্রয়োগ না করলে ব্লকটি নিজে থেকেই নিচের দিকে পিছলে পড়বে। (১) ব্লকটিকে নিচে নামা থেকে আটকাতে সর্বনিম্ন বল: ঘর্ষণ বল ওপরের দিকে কাজ করবে ($f = \mu mg\cos	heta$)। বলের ভারসাম্য: $F_{\min} + \mu mg\cos	heta = mg\sin	heta \implies F_{\min} = mg(\sin	heta - \mu\cos	heta)$। (২) ব্লকটিকে ওপরের দিকে গতিশীল করার ঠিক পূর্ব মুহূর্তে ঘর্ষণ বল নিচের দিকে কাজ করবে ($f = \mu mg\cos	heta$)। বলের ভারসাম্য: $F_{\max} - \mu mg\cos	heta = mg\sin	heta \implies F_{\max} = mg(\sin	heta + \mu\cos	heta)$।</t>
+          <t>যেহেতু $\tan\theta &gt; \mu$, তাই বল প্রয়োগ না করলে ব্লকটি নিজে থেকেই নিচের দিকে পিছলে পড়বে। (১) ব্লকটিকে নিচে নামা থেকে আটকাতে সর্বনিম্ন বল: ঘর্ষণ বল ওপরের দিকে কাজ করবে ($f = \mu mg\cos\theta$)। বলের ভারসাম্য: $F_{\min} + \mu mg\cos\theta = mg\sin\theta \implies F_{\min} = mg(\sin\theta - \mu\cos\theta)$। (২) ব্লকটিকে ওপরের দিকে গতিশীল করার ঠিক পূর্ব মুহূর্তে ঘর্ষণ বল নিচের দিকে কাজ করবে ($f = \mu mg\cos\theta$)। বলের ভারসাম্য: $F_{\max} - \mu mg\cos\theta = mg\sin\theta \implies F_{\max} = mg(\sin\theta + \mu\cos\theta)$।</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2234,14 +2129,9 @@
           <t>$R$ ব্যাসার্ধের একটি ফাঁপা উল্লম্ব সিলিন্ডার তার অক্ষের সাপেক্ষে $\omega$ কৌণিক বেগে ঘুরছে। সিলিন্ডারের অভ্যন্তরীণ উল্লম্ব দেয়ালে একটি ব্লককে চেপে ধরে সিলিন্ডার ঘোরানো হলো। ব্লক ও দেয়ালের মধ্যবর্তী স্থৈতিক ঘর্ষণ গুণাঙ্ক $\mu$ হলে, ব্লকটি যাতে নিচে না পড়ে তার জন্য $\omega$-এর ন্যূনতম মান কত?</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>সিলিন্ডারের অভ্যন্তরীণ দেয়াল কর্তৃক ব্লকের ওপর অনুভূমিক অভিলম্ব বল কেন্দ্রমুখী বল যোগায়: $N = m\omega^2 R$। উল্লম্ব বরাবর ব্লকের ওজন $mg$ নিচের দিকে কাজ করে এবং স্থৈতিক ঘর্ষণ বল $f_s$ ওপরের দিকে কাজ করে। পিছলে না পড়ার শর্ত: $f_{s,\max} \ge mg \implies \mu N \ge mg \implies \mu(m\omega^2 R) \ge mg \implies \omega^2 \ge rac{g}{\mu R} \implies \omega_{\min} = \sqrt{rac{g}{\mu R}}$।</t>
+          <t>সিলিন্ডারের অভ্যন্তরীণ দেয়াল কর্তৃক ব্লকের ওপর অনুভূমিক অভিলম্ব বল কেন্দ্রমুখী বল যোগায়: $N = m\omega^2 R$। উল্লম্ব বরাবর ব্লকের ওজন $mg$ নিচের দিকে কাজ করে এবং স্থৈতিক ঘর্ষণ বল $f_s$ ওপরের দিকে কাজ করে। পিছলে না পড়ার শর্ত: $f_{s,\max} \ge mg \implies \mu N \ge mg \implies \mu(m\omega^2 R) \ge mg \implies \omega^2 \ge \frac{g}{\mu R} \implies \omega_{\min} = \sqrt{\frac{g}{\mu R}}$।</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2284,14 +2174,9 @@
           <t>একটি অমসৃণ অনুভূমিক সমতলে $m$ ভরের একটি ব্লক $v_x$ বেগে ধনাত্মক $x$-অক্ষ বরাবর চলছে। হঠাৎ ব্লকটির ওপর $y$-অক্ষ বরাবর একটি ধ্রুব বল $F_y$ প্রয়োগ করা হলো। গতীয় ঘর্ষণ গুণাঙ্ক $\mu$ হলে, ঘর্ষণ বলের উপাংশসমূহ কীভাবে গতিপথকে প্রভাবিত করবে?</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>যে কোনো মুহূর্তে ব্লকের বেগ ভেক্টর $ec{v} = v_x \hat{i} + v_y \hat{j}$ এবং দ্রুতি $v = \sqrt{v_x^2 + v_y^2}$। গতীয় ঘর্ষণ বল সর্বদা তাৎক্ষণিক বেগ ভেক্টরের ঠিক বিপরীত দিকে কাজ করে: $ec{f}_k = -\mu mg rac{ec{v}}{v} = -\mu mg rac{v_x\hat{i} + v_y\hat{j}}{\sqrt{v_x^2 + v_y^2}}$। ব্যবকলনীয় সমীকরণ: $m rac{dv_x}{dt} = -\mu mg rac{v_x}{\sqrt{v_x^2 + v_y^2}}$ এবং $m rac{dv_y}{dt} = F_y - \mu mg rac{v_y}{\sqrt{v_x^2 + v_y^2}}$। এটি স্পষ্ট করে যে $y$-অক্ষে প্রযুক্ত বল $v_y$ বাড়িয়ে দিলে তা স্বয়ংক্রিয়ভাবে $x$-অক্ষের ঘর্ষণ উপাংশ কমিয়ে দেয়, ফলে $x$-অক্ষের বেগ হ্রাসের হার কমে যায়।</t>
+          <t>যে কোনো মুহূর্তে ব্লকের বেগ ভেক্টর $ec{v} = v_x \hat{i} + v_y \hat{j}$ এবং দ্রুতি $v = \sqrt{v_x^2 + v_y^2}$। গতীয় ঘর্ষণ বল সর্বদা তাৎক্ষণিক বেগ ভেক্টরের ঠিক বিপরীত দিকে কাজ করে: $ec{f}_k = -\mu mg \frac{ec{v}}{v} = -\mu mg \frac{v_x\hat{i} + v_y\hat{j}}{\sqrt{v_x^2 + v_y^2}}$। ব্যবকলনীয় সমীকরণ: $m \frac{dv_x}{dt} = -\mu mg \frac{v_x}{\sqrt{v_x^2 + v_y^2}}$ এবং $m \frac{dv_y}{dt} = F_y - \mu mg \frac{v_y}{\sqrt{v_x^2 + v_y^2}}$। এটি স্পষ্ট করে যে $y$-অক্ষে প্রযুক্ত বল $v_y$ বাড়িয়ে দিলে তা স্বয়ংক্রিয়ভাবে $x$-অক্ষের ঘর্ষণ উপাংশ কমিয়ে দেয়, ফলে $x$-অক্ষের বেগ হ্রাসের হার কমে যায়।</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2331,18 +2216,13 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>একটি স্থির রুক্ষ অনুভূমিক সিলিন্ডারের ওপর দিয়ে একটি দড়ি জড়ানো আছে যার সংস্পর্শ কোণ $eta$ (রেডিয়ানে)। দড়ি ও সিলিন্ডারের মধ্যকার ঘর্ষণ গুণাঙ্ক $\mu$। দড়ির এক প্রান্তে $T_1$ টান প্রয়োগ করে অপর প্রান্তে সর্বোচ্চ কত টান $T_2$ সাম্যাবস্থায় ধরে রাখা সম্ভব?</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি স্থির রুক্ষ অনুভূমিক সিলিন্ডারের ওপর দিয়ে একটি দড়ি জড়ানো আছে যার সংস্পর্শ কোণ $\beta$ (রেডিয়ানে)। দড়ি ও সিলিন্ডারের মধ্যকার ঘর্ষণ গুণাঙ্ক $\mu$। দড়ির এক প্রান্তে $T_1$ টান প্রয়োগ করে অপর প্রান্তে সর্বোচ্চ কত টান $T_2$ সাম্যাবস্থায় ধরে রাখা সম্ভব?</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>সিলিন্ডারের স্পর্শ কোণের ক্ষুদ্রাংশ $d	heta$-এর জন্য ভারসাম্য বিবেচনা করি: অভিলম্ব বল $dN = T d	heta$। ঘর্ষণ বল $df = \mu dN = \mu T d	heta$। টানের পরিবর্তন $dT = df = \mu T d	heta \implies rac{dT}{T} = \mu d	heta$। উভয় পাশে সমাকলন করি: $\int_{T_1}^{T_2} rac{dT}{T} = \mu \int_0^eta d	heta \implies \ln\left(rac{T_2}{T_1}-ight) = \mu eta \implies T_2 = T_1 e^{\mueta}$। এটি ক্যাপস্টান সমীকরণ নামে পরিচিত।</t>
+          <t>সিলিন্ডারের স্পর্শ কোণের ক্ষুদ্রাংশ $d\theta$-এর জন্য ভারসাম্য বিবেচনা করি: অভিলম্ব বল $dN = T d\theta$। ঘর্ষণ বল $df = \mu dN = \mu T d\theta$। টানের পরিবর্তন $dT = df = \mu T d\theta \implies \frac{dT}{T} = \mu d\theta$। উভয় পাশে সমাকলন করি: $\int_{T_1}^{T_2} \frac{dT}{T} = \mu \int_0^\beta d\theta \implies \ln\left(\frac{T_2}{T_1}+ight) = \mu \beta \implies T_2 = T_1 e^{\mueta}$। এটি ক্যাপস্টান সমীকরণ নামে পরিচিত।</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2385,15 +2265,10 @@
           <t>$a$ বাহুবিশিষ্ট একটি সুষম ঘনক $\mu$ ঘর্ষণ গুণাঙ্কের একটি অনুভূমিক তলে রাখা আছে। ঘনকটির শীর্ষপ্রান্তে অনুভূমিক বল $F$ প্রয়োগ করা হলে ঘনকটি আগে পিছলে যাবে নাকি উল্টে যাবে?</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ঘনকটির ভর $m$, কেন্দ্র হতে শীর্ষের দূরত্ব $a/2$। (১) পিছলানোর শর্ত: প্রযুক্ত বল সর্বোচ্চ স্থৈতিক ঘর্ষণের চেয়ে বেশি হতে হবে: $F &gt; F_{	ext{slip}} = \mu mg$। (২) উল্টে যাওয়ার (Tipping) শর্ত: সামনের নিচের কোণার সাপেক্ষে উল্টে যাওয়ার টর্ক বিবেচনা করি। ওজনের প্রত্যয়নী টর্ক $	au_g = mg \left(rac{a}{2}-ight)$। উল্টে দেওয়ার টর্ক $	au_F = F a$। উল্টে যাওয়ার জন্য $	au_F &gt; 	au_g \implies F a &gt; mgrac{a}{2} \implies F &gt; F_{	ext{tip}} = rac{1}{2}mg$। অতএব, যদি $\mu &lt; rac{1}{2}$ হয়, তবে $F_{	ext{slip}} &lt; F_{	ext{tip}}$, অর্থাৎ ঘনকটি উল্টে যাওয়ার আগেই পিছলে যাবে। আর যদি $\mu &gt; rac{1}{2}$ হয়, তবে $F_{	ext{tip}} &lt; F_{	ext{slip}}$, অর্থাৎ পিছলানোর আগেই ঘনকটি উল্টে যাবে।</t>
+          <t>ঘনকটির ভর $m$, কেন্দ্র হতে শীর্ষের দূরত্ব $a/2$। (১) পিছলানোর শর্ত: প্রযুক্ত বল সর্বোচ্চ স্থৈতিক ঘর্ষণের চেয়ে বেশি হতে হবে: $F &gt; F_{\text{slip}} = \mu mg$। (২) উল্টে যাওয়ার (Tipping) শর্ত: সামনের নিচের কোণার সাপেক্ষে উল্টে যাওয়ার টর্ক বিবেচনা করি। ওজনের প্রত্যয়নী টর্ক $\tau_g = mg \left(\frac{a}{2}+ight)$। উল্টে দেওয়ার টর্ক $\tau_F = F a$। উল্টে যাওয়ার জন্য $\tau_F &gt; \tau_g \implies F a &gt; mgrac{a}{2} \implies F &gt; F_{\text{tip}} = \frac{1}{2}mg$। অতএব, যদি $\mu &lt; \frac{1}{2}$ হয়, তবে $F_{\text{slip}} &lt; F_{\text{tip}}$, অর্থাৎ ঘনকটি উল্টে যাওয়ার আগেই পিছলে যাবে। আর যদি $\mu &gt; \frac{1}{2}$ হয়, তবে $F_{\text{tip}} &lt; F_{\text{slip}}$, অর্থাৎ পিছলানোর আগেই ঘনকটি উল্টে যাবে।</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2433,17 +2308,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>মেঝের ওপর ক্রমান্বয়ে তিনটি ব্লক $A, B, C$ রাখা যাদের ভর যথাক্রমে $m_A = 1	ext{ kg}, m_B = 2	ext{ kg}, m_C = 3	ext{ kg}$। মেঝের সাথে $C$-এর ঘর্ষণ শূন্য। $A$ ও $B$-এর মাঝে $\mu_1 = 0.4$, এবং $B$ ও $C$-এর মাঝে $\mu_2 = 0.2$। মাঝের ব্লক $B$-এর ওপর অনুভূমিক বল $F = 30	ext{ N}$ প্রয়োগ করলে প্রতিটি ব্লকের ত্বরণ কত হবে? ($g = 10	ext{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>মেঝের ওপর ক্রমান্বয়ে তিনটি ব্লক $A, B, C$ রাখা যাদের ভর যথাক্রমে $m_A = 1\text{ kg}, m_B = 2\text{ kg}, m_C = 3\text{ kg}$। মেঝের সাথে $C$-এর ঘর্ষণ শূন্য। $A$ ও $B$-এর মাঝে $\mu_1 = 0.4$, এবং $B$ ও $C$-এর মাঝে $\mu_2 = 0.2$। মাঝের ব্লক $B$-এর ওপর অনুভূমিক বল $F = 30\text{ N}$ প্রয়োগ করলে প্রতিটি ব্লকের ত্বরণ কত হবে? ($g = 10\text{ m/s}^2$)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ ঘর্ষণ বলসমূহ: $f_{1,\max} = \mu_1 m_A g = 0.4 	imes 1 	imes 10 = 4	ext{ N}$। $f_{2,\max} = \mu_2 (m_A + m_B)g = 0.2 	imes (1 + 2) 	imes 10 = 6	ext{ N}$। যদি সবাই একসাথে চলে তবে ত্বরণ $a = rac{30}{1+2+3} = 5	ext{ m/s}^2$। কিন্তু $A$-কে $5	ext{ m/s}^2$ ত্বরণ দিতে প্রয়োজনীয় বল $m_A a = 5	ext{ N} &gt; f_{1,\max} (4	ext{ N})$। সুতরাং $A$ পিছলে যাবে এবং $A$-এর ত্বরণ $a_A = rac{f_1}{m_A} = rac{4}{1} = 4	ext{ m/s}^2$। এখন $B$-এর ওপর $F=30	ext{ N}$ ডানদিকে, $A$ কর্তৃক ঘর্ষণ $4	ext{ N}$ বামদিকে। $C$-কে চালনা করার সর্বোচ্চ বল $f_{2,\max} = 6	ext{ N}$। $C$-এর সর্বোচ্চ ত্বরণ $a_{C,\max} = rac{6}{3} = 2	ext{ m/s}^2$। যদি $B$ ও $C$ একসাথে চলত তবে ত্বরণ হত $rac{30 - 4}{2 + 3} = rac{26}{5} = 5.2	ext{ m/s}^2 &gt; 2	ext{ m/s}^2$। ফলে $B$ ও $C$-এর মাঝেও পিছলানো ঘটবে। অতএব $C$-এর ত্বরণ $a_C = rac{6}{3} = 2	ext{ m/s}^2$। আর $B$-এর ত্বরণ $a_B = rac{F - f_1 - f_2}{m_B} = rac{30 - 4 - 6}{2} = rac{20}{2} = 10	ext{ m/s}^2$।</t>
+          <t>সর্বোচ্চ ঘর্ষণ বলসমূহ: $f_{1,\max} = \mu_1 m_A g = 0.4 \times 1 \times 10 = 4\text{ N}$। $f_{2,\max} = \mu_2 (m_A + m_B)g = 0.2 \times (1 + 2) \times 10 = 6\text{ N}$। যদি সবাই একসাথে চলে তবে ত্বরণ $a = \frac{30}{1+2+3} = 5\text{ m/s}^2$। কিন্তু $A$-কে $5\text{ m/s}^2$ ত্বরণ দিতে প্রয়োজনীয় বল $m_A a = 5\text{ N} &gt; f_{1,\max} (4\text{ N})$। সুতরাং $A$ পিছলে যাবে এবং $A$-এর ত্বরণ $a_A = \frac{f_1}{m_A} = \frac{4}{1} = 4\text{ m/s}^2$। এখন $B$-এর ওপর $F=30\text{ N}$ ডানদিকে, $A$ কর্তৃক ঘর্ষণ $4\text{ N}$ বামদিকে। $C$-কে চালনা করার সর্বোচ্চ বল $f_{2,\max} = 6\text{ N}$। $C$-এর সর্বোচ্চ ত্বরণ $a_{C,\max} = \frac{6}{3} = 2\text{ m/s}^2$। যদি $B$ ও $C$ একসাথে চলত তবে ত্বরণ হত $\frac{30 - 4}{2 + 3} = \frac{26}{5} = 5.2\text{ m/s}^2 &gt; 2\text{ m/s}^2$। ফলে $B$ ও $C$-এর মাঝেও পিছলানো ঘটবে। অতএব $C$-এর ত্বরণ $a_C = \frac{6}{3} = 2\text{ m/s}^2$। আর $B$-এর ত্বরণ $a_B = \frac{F - f_1 - f_2}{m_B} = \frac{30 - 4 - 6}{2} = \frac{20}{2} = 10\text{ m/s}^2$।</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2486,14 +2356,9 @@
           <t>$R$ ব্যাসার্ধের একটি ফাঁপা গোলকের অভ্যন্তরীণ তলে একটি কণা রাখা। কণা ও গোলক পৃষ্ঠের স্থৈতিক ঘর্ষণ গুণাঙ্ক $\mu$। কণাটিকে গোলকের সর্বনিম্ন বিন্দু থেকে না পিছলিয়ে সর্বোচ্চ কত উল্লম্ব উচ্চতা $h$ পর্যন্ত স্থির রাখা যাবে?</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>সর্বনিম্ন বিন্দু থেকে উল্লম্বের সাথে অবস্থান কোণ $	heta$ হলে ওই বিন্দুতে স্পর্শকের নতি কোণও $	heta$। কণাটি স্থির থাকার শর্ত হলো নতি কোণ ঘর্ষণ কোণের সমান বা ছোট হতে হবে: $	an	heta \le \mu$। অতএব সর্বোচ্চ সীমা $	an	heta = \mu \implies \cos	heta = rac{1}{\sqrt{1 + \mu^2}}$। সর্বনিম্ন বিন্দু হতে উচ্চতা $h = R(1 - \cos	heta) = R\left(1 - rac{1}{\sqrt{1 + \mu^2}}+          <t>সর্বনিম্ন বিন্দু থেকে উল্লম্বের সাথে অবস্থান কোণ $\theta$ হলে ওই বিন্দুতে স্পর্শকের নতি কোণও $\theta$। কণাটি স্থির থাকার শর্ত হলো নতি কোণ ঘর্ষণ কোণের সমান বা ছোট হতে হবে: $\tan\theta \le \mu$। অতএব সর্বোচ্চ সীমা $\tan\theta = \mu \implies \cos\theta = \frac{1}{\sqrt{1 + \mu^2}}$। সর্বনিম্ন বিন্দু হতে উচ্চতা $h = R(1 - \cos\theta) = R\left(1 - \frac{1}{\sqrt{1 + \mu^2}} ight)$।</t>
         </is>
       </c>
@@ -2534,18 +2399,13 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>একটি অনুভূমিক তলে গতীয় ঘর্ষণ গুণাঙ্ক দূরত্বের সাথে রৈখিকভাবে বৃদ্ধি পায়: $\mu(x) = lpha x$ ($lpha &gt; 0$)। $m$ ভরের একটি ব্লককে $x = 0$ বিন্দু থেকে $v_0$ আদি দ্রুতি নিয়ে ঠেলে দেওয়া হলে ব্লকটি মোট কত দূরত্ব গিয়ে স্থির হবে?</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি অনুভূমিক তলে গতীয় ঘর্ষণ গুণাঙ্ক দূরত্বের সাথে রৈখিকভাবে বৃদ্ধি পায়: $\mu(x) = \alpha x$ ($\alpha &gt; 0$)। $m$ ভরের একটি ব্লককে $x = 0$ বিন্দু থেকে $v_0$ আদি দ্রুতি নিয়ে ঠেলে দেওয়া হলে ব্লকটি মোট কত দূরত্ব গিয়ে স্থির হবে?</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>কাজ-শক্তি উপপাদ্য অনুসারে ব্লকের গতিশক্তির পরিবর্তন ঘর্ষণ বলের কৃতকাজের সমান: $\Delta K = W_{	ext{friction}} \implies 0 - rac{1}{2}m v_0^2 = -\int_0^{x_f} \mu(x) mg dx = -\int_0^{x_f} lpha x mg dx = -mglpha \left[rac{x^2}{2}-ight]_0^{x_f} = -rac{1}{2}mglpha x_f^2$। উভয় পাশ থেকে $rac{1}{2}m$ বর্জন করে পাই: $v_0^2 = glpha x_f^2 \implies x_f^2 = rac{v_0^2}{lpha g} \implies x_f = rac{v_0}{\sqrt{lpha g}}$।</t>
+          <t>কাজ-শক্তি উপপাদ্য অনুসারে ব্লকের গতিশক্তির পরিবর্তন ঘর্ষণ বলের কৃতকাজের সমান: $\Delta K = W_{\text{friction}} \implies 0 - \frac{1}{2}m v_0^2 = -\int_0^{x_f} \mu(x) mg dx = -\int_0^{x_f} \alpha x mg dx = -mglpha \left[\frac{x^2}{2}+ight]_0^{x_f} = -\frac{1}{2}mglpha x_f^2$। উভয় পাশ থেকে $\frac{1}{2}m$ বর্জন করে পাই: $v_0^2 = glpha x_f^2 \implies x_f^2 = \frac{v_0^2}{\alpha g} \implies x_f = \frac{v_0}{\sqrt{\alpha g}}$।</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2585,17 +2445,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>একটি মসৃণ অনুভূমিক সমতলে $u$ বেগে চলমান একটি মার্বেল অভিলম্বের সাথে $lpha$ আপাতন কোণে একটি মসৃণ স্থির উল্লম্ব দেয়ালে ধাক্কা খায়। মার্বেল ও দেয়ালের মধ্যকার রেস্টিটিউশন গুণাঙ্ক $e$ ($0 &lt; e &lt; 1$)। প্রতিফলন কোণ $eta$ এবং সংঘর্ষের পর মার্বেলের দ্রুতি $v$ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি মসৃণ অনুভূমিক সমতলে $u$ বেগে চলমান একটি মার্বেল অভিলম্বের সাথে $\alpha$ আপাতন কোণে একটি মসৃণ স্থির উল্লম্ব দেয়ালে ধাক্কা খায়। মার্বেল ও দেয়ালের মধ্যকার রেস্টিটিউশন গুণাঙ্ক $e$ ($0 &lt; e &lt; 1$)। প্রতিফলন কোণ $\beta$ এবং সংঘর্ষের পর মার্বেলের দ্রুতি $v$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>দেয়াল মসৃণ হওয়ায় দেয়ালের সমান্তরাল দিকে কোনো বল নেই, ফলে সমান্তরাল উপাংশ অপরিবর্তিত থাকে: $v\sineta = u\sinlpha$। দেয়ালের অভিলম্ব দিকে নিউটনের সংঘর্ষ সূত্র প্রযোজ্য: $v\coseta = e u\coslpha$। সমীকরণ দুটি ভাগ করে পাই: $	aneta = rac{v\sineta}{v\coseta} = rac{u\sinlpha}{e u\coslpha} = rac{	anlpha}{e} \implies 	aneta = rac{	anlpha}{e}$। সংঘর্ষের পর দ্রুতি: $v = \sqrt{(v\sineta)^2 + (v\coseta)^2} = \sqrt{u^2\sin^2lpha + e^2 u^2\cos^2lpha} = u\sqrt{\sin^2lpha + e^2\cos^2lpha}$।</t>
+          <t>দেয়াল মসৃণ হওয়ায় দেয়ালের সমান্তরাল দিকে কোনো বল নেই, ফলে সমান্তরাল উপাংশ অপরিবর্তিত থাকে: $v\sineta = u\sinlpha$। দেয়ালের অভিলম্ব দিকে নিউটনের সংঘর্ষ সূত্র প্রযোজ্য: $v\coseta = e u\coslpha$। সমীকরণ দুটি ভাগ করে পাই: $\taneta = \frac{v\sineta}{v\coseta} = \frac{u\sinlpha}{e u\coslpha} = \frac{\tanlpha}{e} \implies \taneta = \frac{\tanlpha}{e}$। সংঘর্ষের পর দ্রুতি: $v = \sqrt{(v\sineta)^2 + (v\coseta)^2} = \sqrt{u^2\sin^2\alpha + e^2 u^2\cos^2\alpha} = u\sqrt{\sin^2\alpha + e^2\cos^2\alpha}$।</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2635,17 +2490,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>$m_1$ ও $m_2$ ভরের দুটি বস্তু যথাক্রমে $u_1$ ও $u_2$ বেগ নিয়ে একমাত্রিক সংঘর্ষে লিপ্ত হয়। রেস্টিটিউশন গুণাঙ্ক $e$ হলে, প্রমাণ কর যে সংঘর্ষে মোট গতিশক্তির ক্ষয় $\Delta K = rac{1}{2}\mu(1 - e^2)(u_1 - u_2)^2$, যেখানে $\mu = rac{m_1 m_2}{m_1 + m_2}$।</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>$m_1$ ও $m_2$ ভরের দুটি বস্তু যথাক্রমে $u_1$ ও $u_2$ বেগ নিয়ে একমাত্রিক সংঘর্ষে লিপ্ত হয়। রেস্টিটিউশন গুণাঙ্ক $e$ হলে, প্রমাণ কর যে সংঘর্ষে মোট গতিশক্তির ক্ষয় $\Delta K = \frac{1}{2}\mu(1 - e^2)(u_1 - u_2)^2$, যেখানে $\mu = \frac{m_1 m_2}{m_1 + m_2}$।</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ভরকেন্দ্র ফ্রেমে যেকোনো সংস্থার মোট গতিশক্তি $K = K_{	ext{cm}} + K_{	ext{rel}} = rac{1}{2}(m_1 + m_2)v_{	ext{cm}}^2 + rac{1}{2}\mu v_{	ext{rel}}^2$। যেহেতু কোনো বাহ্যিক বল নেই, তাই $v_{	ext{cm}}$ ধ্রুব থাকে, ফলে $K_{	ext{cm}}$ অপরিবর্তিত থাকে। সংঘর্ষের পূর্বে আপেক্ষিক বেগ $v_{	ext{rel, i}} = u_1 - u_2$। সংঘর্ষের পরে আপেক্ষিক বেগ $v_{	ext{rel, f}} = -e(u_1 - u_2)$। অতএব গতিশক্তির পরিবর্তন কেবল আপেক্ষিক গতিশক্তির পরিবর্তনের সমান: $\Delta K = K_{	ext{rel, i}} - K_{	ext{rel, f}} = rac{1}{2}\mu (u_1 - u_2)^2 - rac{1}{2}\mu [e(u_1 - u_2)]^2 = rac{1}{2}\mu(1 - e^2)(u_1 - u_2)^2$। পূর্ণ স্থিতিস্থাপক সংঘর্ষে ($e=1$) $\Delta K = 0$ এবং পূর্ণ অস্থিতিস্থাপক সংঘর্ষে ($e=0$) শক্তি ক্ষয় সর্বোচ্চ।</t>
+          <t>ভরকেন্দ্র ফ্রেমে যেকোনো সংস্থার মোট গতিশক্তি $K = K_{\text{cm}} + K_{\text{rel}} = \frac{1}{2}(m_1 + m_2)v_{\text{cm}}^2 + \frac{1}{2}\mu v_{\text{rel}}^2$। যেহেতু কোনো বাহ্যিক বল নেই, তাই $v_{\text{cm}}$ ধ্রুব থাকে, ফলে $K_{\text{cm}}$ অপরিবর্তিত থাকে। সংঘর্ষের পূর্বে আপেক্ষিক বেগ $v_{\text{rel, i}} = u_1 - u_2$। সংঘর্ষের পরে আপেক্ষিক বেগ $v_{\text{rel, f}} = -e(u_1 - u_2)$। অতএব গতিশক্তির পরিবর্তন কেবল আপেক্ষিক গতিশক্তির পরিবর্তনের সমান: $\Delta K = K_{\text{rel, i}} - K_{\text{rel, f}} = \frac{1}{2}\mu (u_1 - u_2)^2 - \frac{1}{2}\mu [e(u_1 - u_2)]^2 = \frac{1}{2}\mu(1 - e^2)(u_1 - u_2)^2$। পূর্ণ স্থিতিস্থাপক সংঘর্ষে ($e=1$) $\Delta K = 0$ এবং পূর্ণ অস্থিতিস্থাপক সংঘর্ষে ($e=0$) শক্তি ক্ষয় সর্বোচ্চ।</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2688,14 +2538,9 @@
           <t>$m$ ভরের একটি চলমান কণা একই $m$ ভরের একটি স্থির কণার সাথে তির্যক স্থিতিস্থাপক সংঘর্ষে ($e=1$) লিপ্ত হয়। প্রমাণ কর যে সংঘর্ষের পর কণা দুটির গতিপথ পরস্পরের সাথে ঠিক $90^\circ$ কোণ উৎপন্ন করে।</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ভরবেগ সংরক্ষণশীলতা: $mec{u}_1 = mec{v}_1 + mec{v}_2 \implies ec{u}_1 = ec{v}_1 + ec{v}_2$। উভয় পাশে ডট গুণন করে পাই: $|ec{u}_1|^2 = |ec{v}_1|^2 + |ec{v}_2|^2 + 2ec{v}_1\cdotec{v}_2$। আবার সংঘর্ষ স্থিতিস্থাপক হওয়ায় গতিশক্তি সংরক্ষিত: $rac{1}{2}m u_1^2 = rac{1}{2}m v_1^2 + rac{1}{2}m v_2^2 \implies u_1^2 = v_1^2 + v_2^2$। দুটি ফলাফল তুলনা করে পাই: $v_1^2 + v_2^2 = v_1^2 + v_2^2 + 2ec{v}_1\cdotec{v}_2 \implies 2ec{v}_1\cdotec{v}_2 = 0 \implies ec{v}_1\cdotec{v}_2 = 0$। যেহেতু ডট গুণন শূন্য, সেহেতু বেগ ভেক্টরদ্বয় পরস্পরের লম্ব, অর্থাৎ তাদের মধ্যবর্তী কোণ $90^\circ$।</t>
+          <t>ভরবেগ সংরক্ষণশীলতা: $mec{u}_1 = mec{v}_1 + mec{v}_2 \implies ec{u}_1 = ec{v}_1 + ec{v}_2$। উভয় পাশে ডট গুণন করে পাই: $|ec{u}_1|^2 = |ec{v}_1|^2 + |ec{v}_2|^2 + 2ec{v}_1\cdotec{v}_2$। আবার সংঘর্ষ স্থিতিস্থাপক হওয়ায় গতিশক্তি সংরক্ষিত: $\frac{1}{2}m u_1^2 = \frac{1}{2}m v_1^2 + \frac{1}{2}m v_2^2 \implies u_1^2 = v_1^2 + v_2^2$। দুটি ফলাফল তুলনা করে পাই: $v_1^2 + v_2^2 = v_1^2 + v_2^2 + 2ec{v}_1\cdotec{v}_2 \implies 2ec{v}_1\cdotec{v}_2 = 0 \implies ec{v}_1\cdotec{v}_2 = 0$। যেহেতু ডট গুণন শূন্য, সেহেতু বেগ ভেক্টরদ্বয় পরস্পরের লম্ব, অর্থাৎ তাদের মধ্যবর্তী কোণ $90^\circ$।</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2738,16 +2583,11 @@
           <t>$h$ উচ্চতা থেকে একটি বল অনুভূমিক শক্ত মেঝের ওপর মুক্তভাবে ছেড়ে দেওয়া হলো। বল ও মেঝের রেস্টিটিউশন গুণাঙ্ক $e$ ($e &lt; 1$)। বলটি সম্পূর্ণ স্থির হওয়ার পূর্ব পর্যন্ত মোট কত দূরত্ব অতিক্রম করবে এবং মোট কত সময় অতিবাহিত হবে?</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>প্রথম পতনের সময় $t_0 = \sqrt{rac{2h}{g}}$ এবং পতনের বেগ $v_0 = \sqrt{2gh}$। প্রথম বাউন্সের পর বেগ $e v_0$, ফলে উচ্চতা $h_1 = e^2 h$ এবং ওঠার ও নামার সময় $2et_0$। $n$-তম বাউন্সে উচ্চতা $h_n = e^{2n}h$ এবং সময় $2e^n t_0$। মোট অতিক্রান্ত দূরত্ব: $H_{	ext{total}} = h + 2\sum_{n=1}^\infty h_n = h + 2h\sum_{n=1}^\infty e^{2n} = h + 2hrac{e^2}{1 - e^2} = h\left(rac{1 + e^2}{1 - e^2}-ight)$। মোট সময়: $T_{	ext{total}} = t_0 + 2t_0\sum_{n=1}^\infty e^n = t_0 + 2t_0rac{e}{1 - e} = t_0\left(rac{1 + e}{1 - e}-ight) = \sqrt{rac{2h}{g}}\left(rac{1 + e}{1 - e}+          <t>প্রথম পতনের সময় $t_0 = \sqrt{\frac{2h}{g}}$ এবং পতনের বেগ $v_0 = \sqrt{2gh}$। প্রথম বাউন্সের পর বেগ $e v_0$, ফলে উচ্চতা $h_1 = e^2 h$ এবং ওঠার ও নামার সময় $2et_0$। $n$-তম বাউন্সে উচ্চতা $h_n = e^{2n}h$ এবং সময় $2e^n t_0$। মোট অতিক্রান্ত দূরত্ব: $H_{\text{total}} = h + 2\sum_{n=1}^\infty h_n = h + 2h\sum_{n=1}^\infty e^{2n} = h + 2hrac{e^2}{1 - e^2} = h\left(\frac{1 + e^2}{1 - e^2}+ight)$। মোট সময়: $T_{\text{total}} = t_0 + 2t_0\sum_{n=1}^\infty e^n = t_0 + 2t_0\frac{e}{1 - e} = t_0\left(\frac{1 + e}{1 - e}+ight) = \sqrt{\frac{2h}{g}}\left(\frac{1 + e}{1 - e} ight)$।</t>
         </is>
       </c>
@@ -2791,16 +2631,11 @@
           <t>$M$ ভরের একটি চলমান ব্লকের গতিশক্তি $m$ ভরের একটি স্থির ব্লকে স্থানান্তর করতে হবে একটি মধ্যবর্তী ব্লক $m'$ ব্যবহারের মাধ্যমে (সব সংঘর্ষ একমাত্রিক ও স্থিতিস্থাপক)। মধ্যবর্তী ব্লক $m'$-এর ভর কত হলে $M$ থেকে $m$-এ শক্তি স্থানান্তর সর্বাধিক হবে?</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>$M$ থেকে $m'$ ব্লকে স্থিতিস্থাপক সংঘর্ষে হস্তান্তরিত বেগ $v' = rac{2M}{M + m'} u$। এরপর $m'$ থেকে $m$ ব্লকে হস্তান্তরিত বেগ $v = rac{2m'}{m' + m} v' = rac{4M m'}{(M + m')(m' + m)} u$। $m$ ব্লকে অর্জিত গতিশক্তি $K_m = rac{1}{2}m v^2 \propto \left[rac{m'}{(M + m')(m' + m)}-ight]^2 = \left[rac{1}{rac{M m}{m'} + m' + M + m}-ight]^2$। শক্তি সর্বাধিক হওয়ার জন্য হর $rac{M m}{m'} + m'$ ন্যূনতম হতে হবে। $AM \ge GM$ বা ব্যবকলন থেকে এর ন্যূনতম মান ঘটে যখন $rac{M m}{m'} = m' \implies m'^2 = M m \implies m' = \sqrt{Mm}$। অর্থাৎ মধ্যবর্তী ভরটি আদি ও চূড়ান্ত ভরের গুণোত্তর গড় (Geometric Mean) হতে হবে।</t>
+          <t>$M$ থেকে $m'$ ব্লকে স্থিতিস্থাপক সংঘর্ষে হস্তান্তরিত বেগ $v' = \frac{2M}{M + m'} u$। এরপর $m'$ থেকে $m$ ব্লকে হস্তান্তরিত বেগ $v = \frac{2m'}{m' + m} v' = \frac{4M m'}{(M + m')(m' + m)} u$। $m$ ব্লকে অর্জিত গতিশক্তি $K_m = \frac{1}{2}m v^2 \propto \left[\frac{m'}{(M + m')(m' + m)}+ight]^2 = \left[\frac{1}{\frac{M m}{m'} + m' + M + m}+ight]^2$। শক্তি সর্বাধিক হওয়ার জন্য হর $\frac{M m}{m'} + m'$ ন্যূনতম হতে হবে। $AM \ge GM$ বা ব্যবকলন থেকে এর ন্যূনতম মান ঘটে যখন $\frac{M m}{m'} = m' \implies m'^2 = M m \implies m' = \sqrt{Mm}$। অর্থাৎ মধ্যবর্তী ভরটি আদি ও চূড়ান্ত ভরের গুণোত্তর গড় (Geometric Mean) হতে হবে।</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2840,17 +2675,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>$m_1$ ভরের একটি কণা $u$ দ্রুতি নিয়ে স্থির থাকা $m_2$ ($m_2 &lt; m_1$) ভরের কণার সাথে স্থিতিস্থাপক সংঘর্ষে লিপ্ত হয়। ভারী কণা $m_1$-এর সর্বোচ্চ বিচ্যুতি কোণ $	heta_{\max}$ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>$m_1$ ভরের একটি কণা $u$ দ্রুতি নিয়ে স্থির থাকা $m_2$ ($m_2 &lt; m_1$) ভরের কণার সাথে স্থিতিস্থাপক সংঘর্ষে লিপ্ত হয়। ভারী কণা $m_1$-এর সর্বোচ্চ বিচ্যুতি কোণ $\theta_{\max}$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ভরকেন্দ্র ফ্রেমে রূপান্তর করি। ভরকেন্দ্রের বেগ $v_{	ext{cm}} = rac{m_1}{m_1 + m_2}u$। ভরকেন্দ্র ফ্রেমে $m_1$-এর আপেক্ষিক বেগ $u_1' = u - v_{	ext{cm}} = rac{m_2}{m_1 + m_2}u$। সংঘর্ষের পর ভরকেন্দ্র ফ্রেমে এর বেগ অপরিবর্তিত থাকে ($v_1' = u_1'$) কিন্তু কোণ $\phi$-তে ঘুরে যায়। ল্যাবরেটরি ফ্রেমে বেগ ভেক্টর $ec{v}_1 = ec{v}_{	ext{cm}} + ec{v}_1'$। যেহেতু $m_1 &gt; m_2$, সেহেতু $v_{	ext{cm}} &gt; v_1'$। বেগ ত্রিভুজে $ec{v}_1$-এর সর্বোচ্চ কোণ ঘটে যখন $ec{v}_1$ ভেক্টরটি $v_1'$ বৃত্তের ওপর স্পর্শক হয়। স্পর্শক অবস্থায় সমকোণী ত্রিভুজ গঠিত হয় যার অতিভুজ $v_{	ext{cm}}$ এবং লম্ব $v_1'$। অতএব $\sin	heta_{\max} = rac{v_1'}{v_{	ext{cm}}} = rac{rac{m_2}{m_1 + m_2}u}{rac{m_1}{m_1 + m_2}u} = rac{m_2}{m_1}$।</t>
+          <t>ভরকেন্দ্র ফ্রেমে রূপান্তর করি। ভরকেন্দ্রের বেগ $v_{\text{cm}} = \frac{m_1}{m_1 + m_2}u$। ভরকেন্দ্র ফ্রেমে $m_1$-এর আপেক্ষিক বেগ $u_1' = u - v_{\text{cm}} = \frac{m_2}{m_1 + m_2}u$। সংঘর্ষের পর ভরকেন্দ্র ফ্রেমে এর বেগ অপরিবর্তিত থাকে ($v_1' = u_1'$) কিন্তু কোণ $\phi$-তে ঘুরে যায়। ল্যাবরেটরি ফ্রেমে বেগ ভেক্টর $ec{v}_1 = ec{v}_{\text{cm}} + ec{v}_1'$। যেহেতু $m_1 &gt; m_2$, সেহেতু $v_{\text{cm}} &gt; v_1'$। বেগ ত্রিভুজে $ec{v}_1$-এর সর্বোচ্চ কোণ ঘটে যখন $ec{v}_1$ ভেক্টরটি $v_1'$ বৃত্তের ওপর স্পর্শক হয়। স্পর্শক অবস্থায় সমকোণী ত্রিভুজ গঠিত হয় যার অতিভুজ $v_{\text{cm}}$ এবং লম্ব $v_1'$। অতএব $\sin\theta_{\max} = \frac{v_1'}{v_{\text{cm}}} = \frac{\frac{m_2}{m_1 + m_2}u}{\frac{m_1}{m_1 + m_2}u} = \frac{m_2}{m_1}$।</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2890,17 +2720,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>$M$ ভরের একটি ঝুলন্ত কাঠের ব্লকে $m$ ভরের একটি বুলেট অনুভূমিকভাবে $v$ বেগে প্রবেশ করে স্থির হয়ে আটকে গেল। এতে পেন্ডুলামটি উল্লম্বের সাথে সর্বোচ্চ $	heta$ কোণে বিচ্যুত হলো এবং সুতার দৈর্ঘ্য $L$। বুলেটের আদি বেগ $v$ নির্ণয় কর এবং এই প্রক্রিয়ায় শক্তির কত শতাংশ তাপে রূপান্তরিত হয়েছে?</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>$M$ ভরের একটি ঝুলন্ত কাঠের ব্লকে $m$ ভরের একটি বুলেট অনুভূমিকভাবে $v$ বেগে প্রবেশ করে স্থির হয়ে আটকে গেল। এতে পেন্ডুলামটি উল্লম্বের সাথে সর্বোচ্চ $\theta$ কোণে বিচ্যুত হলো এবং সুতার দৈর্ঘ্য $L$। বুলেটের আদি বেগ $v$ নির্ণয় কর এবং এই প্রক্রিয়ায় শক্তির কত শতাংশ তাপে রূপান্তরিত হয়েছে?</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>বুলেট আটকে যাওয়ার মুহূর্তে অনুভূমিক ভরবেগ সংরক্ষিত: $m v = (M + m)V \implies V = rac{m}{M + m}v$। এরপর ব্লকের গতিশক্তি মহাকর্ষীয় বিভব শক্তিতে রূপান্তরিত হয়: $rac{1}{2}(M + m)V^2 = (M + m)gL(1 - \cos	heta) \implies V = \sqrt{2gL(1 - \cos	heta)} = 2\sqrt{gL}\sin(	heta/2)$। অতএব বুলেটের আদি বেগ $v = rac{M + m}{m}\sqrt{2gL(1 - \cos	heta)}$। আদি গতিশক্তি $K_i = rac{1}{2}mv^2$। সংঘাতের পর গতিশক্তি $K_f = rac{1}{2}(M+m)V^2 = rac{m}{M+m}K_i$। শক্তিক্ষয়ের ভগ্নাংশ $rac{\Delta K}{K_i} = 1 - rac{m}{M+m} = rac{M}{M+m}$। যেহেতু $M \gg m$, তাই প্রায় সম্পূর্ণ শক্তিই (যেমন ৯৯%+) তাপে নষ্ট হয়।</t>
+          <t>বুলেট আটকে যাওয়ার মুহূর্তে অনুভূমিক ভরবেগ সংরক্ষিত: $m v = (M + m)V \implies V = \frac{m}{M + m}v$। এরপর ব্লকের গতিশক্তি মহাকর্ষীয় বিভব শক্তিতে রূপান্তরিত হয়: $\frac{1}{2}(M + m)V^2 = (M + m)gL(1 - \cos\theta) \implies V = \sqrt{2gL(1 - \cos\theta)} = 2\sqrt{gL}\sin(\theta/2)$। অতএব বুলেটের আদি বেগ $v = \frac{M + m}{m}\sqrt{2gL(1 - \cos\theta)}$। আদি গতিশক্তি $K_i = \frac{1}{2}mv^2$। সংঘাতের পর গতিশক্তি $K_f = \frac{1}{2}(M+m)V^2 = \frac{m}{M+m}K_i$। শক্তিক্ষয়ের ভগ্নাংশ $\frac{\Delta K}{K_i} = 1 - \frac{m}{M+m} = \frac{M}{M+m}$। যেহেতু $M \gg m$, তাই প্রায় সম্পূর্ণ শক্তিই (যেমন ৯৯%+) তাপে নষ্ট হয়।</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2943,14 +2768,9 @@
           <t>স্থির অবস্থায় থাকা একটি বোমা বিস্ফোরিত হয়ে $m_1$ ও $m_2$ ভরের দুটি খণ্ডে বিভক্ত হয়ে বিপরীত দিকে ছিটকে গেল। মোট নির্গত রাসায়নিক শক্তি $E$ হলে প্রতিটি খণ্ডের গতিশক্তি $K_1$ ও $K_2$ কত হবে?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>বাহ্যিক বল শূন্য হওয়ায় ভরবেগ সংরক্ষিত: $ec{p}_1 + ec{p}_2 = 0 \implies p_1 = p_2 = p$। গতিশক্তি ও ভরবেগের সম্পর্ক $K = rac{p^2}{2m}$। অতএব গতিশক্তির অনুপাত ভরের ব্যস্তানুপাতিক: $rac{K_1}{K_2} = rac{p^2/(2m_1)}{p^2/(2m_2)} = rac{m_2}{m_1}$। মোট শক্তি $K_1 + K_2 = E$। অনুপাত প্রয়োগ করে পাই: $K_1 = rac{m_2}{m_1 + m_2} E$ এবং $K_2 = rac{m_1}{m_1 + m_2} E$। হালকা খণ্ডটি বেশি গতিশক্তি লাভ করে।</t>
+          <t>বাহ্যিক বল শূন্য হওয়ায় ভরবেগ সংরক্ষিত: $ec{p}_1 + ec{p}_2 = 0 \implies p_1 = p_2 = p$। গতিশক্তি ও ভরবেগের সম্পর্ক $K = \frac{p^2}{2m}$। অতএব গতিশক্তির অনুপাত ভরের ব্যস্তানুপাতিক: $\frac{K_1}{K_2} = \frac{p^2/(2m_1)}{p^2/(2m_2)} = \frac{m_2}{m_1}$। মোট শক্তি $K_1 + K_2 = E$। অনুপাত প্রয়োগ করে পাই: $K_1 = \frac{m_2}{m_1 + m_2} E$ এবং $K_2 = \frac{m_1}{m_1 + m_2} E$। হালকা খণ্ডটি বেশি গতিশক্তি লাভ করে।</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3050,7 +2870,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>মেঝে স্পর্শ করার ঠিক পূর্ব মুহূর্তে কাদার বেগ $v = \sqrt{2gh}$ নিচের দিকে। মেঝেতে আটকে যাওয়ার পর চূড়ান্ত বেগ $0$। ভরবেগের পরিবর্তন $\Delta p = 0 - (-mv) = mv = m\sqrt{2gh}$ ওপরের দিকে। ঘাত সমীকরণ: $J = ar{F}_{	ext{net}}\Delta t = (ar{N} - mg)\Delta t = m\sqrt{2gh}$। অতএব মেঝে কর্তৃক প্রযুক্ত গড় অভিলম্ব বল $ar{N} = mg + rac{m\sqrt{2gh}}{\Delta t}$।</t>
+          <t>মেঝে স্পর্শ করার ঠিক পূর্ব মুহূর্তে কাদার বেগ $v = \sqrt{2gh}$ নিচের দিকে। মেঝেতে আটকে যাওয়ার পর চূড়ান্ত বেগ $0$। ভরবেগের পরিবর্তন $\Delta p = 0 - (-mv) = mv = m\sqrt{2gh}$ ওপরের দিকে। ঘাত সমীকরণ: $J = ar{F}_{\text{net}}\Delta t = (ar{N} - mg)\Delta t = m\sqrt{2gh}$। অতএব মেঝে কর্তৃক প্রযুক্ত গড় অভিলম্ব বল $ar{N} = mg + \frac{m\sqrt{2gh}}{\Delta t}$।</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3093,16 +2913,11 @@
           <t>$L$ দৈর্ঘ্য ও $M$ ভরের একটি সুষম নমনীয় চেইনের $y_0$ অংশ একটি মসৃণ অনুভূমিক টেবিলের কিনারা দিয়ে উল্লম্বভাবে ঝুলছে। চেইনটিকে স্থির অবস্থা থেকে ছেড়ে দিলে সম্পূর্ণ চেইনটি টেবিল থেকে পিছলে পড়ার মুহূর্তে তার বেগ কত হবে?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>যখন চেইনের $y$ দৈর্ঘ্য নিচে ঝুলছে, তখন তার ভর $rac{M}{L}y$। চেইনের ওপর কার্যকর একমাত্র বাহ্যিক বল হলো ঝুলন্ত অংশের ওজন $F = \left(rac{M}{L}y-ight)g$। কাজ-শক্তি উপপাদ্য প্রয়োগ করে: মোট চেইনের ভর $M$ ধ্রুব, ফলে $M v rac{dv}{dy} = rac{M g}{L} y \implies v dv = rac{g}{L} y dy$। সমাকলন করি: $\int_0^v v dv = rac{g}{L} \int_{y_0}^L y dy \implies rac{1}{2}v^2 = rac{g}{L}\left[rac{L^2 - y_0^2}{2}-ight] \implies v = \sqrt{rac{g}{L}(L^2 - y_0^2)}$।</t>
+          <t>যখন চেইনের $y$ দৈর্ঘ্য নিচে ঝুলছে, তখন তার ভর $\frac{M}{L}y$। চেইনের ওপর কার্যকর একমাত্র বাহ্যিক বল হলো ঝুলন্ত অংশের ওজন $F = \left(\frac{M}{L}y+ight)g$। কাজ-শক্তি উপপাদ্য প্রয়োগ করে: মোট চেইনের ভর $M$ ধ্রুব, ফলে $M v \frac{dv}{dy} = \frac{M g}{L} y \implies v dv = \frac{g}{L} y dy$। সমাকলন করি: $\int_0^v v dv = \frac{g}{L} \int_{y_0}^L y dy \implies \frac{1}{2}v^2 = \frac{g}{L}\left[\frac{L^2 - y_0^2}{2}+ight] \implies v = \sqrt{\frac{g}{L}(L^2 - y_0^2)}$।</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3145,18 +2960,13 @@
           <t>$L$ দৈর্ঘ্য ও $M$ ভরের একটি চেইনকে তার উপরের প্রান্ত ধরে এমনভাবে ঝুলিয়ে রাখা হয়েছে যাতে নিচের প্রান্ত ঠিক একটি ওজনের স্কেলকে স্পর্শ করে। উপরের প্রান্ত ছেড়ে দিলে যখন $y$ দৈর্ঘ্যের চেইন স্কেলে জমা হয়, তখন স্কেলটি মোট কত বল নির্দেশ করবে?</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>স্কেলের পাঠ দুটি বলের সমষ্টি: (১) স্কেলে স্থির থাকা $y$ দৈর্ঘ্যের চেইনের ওজন $W = \left(rac{M}{L}y-ight)g$। (২) উপর থেকে $v = \sqrt{2gy}$ বেগে পড়তে থাকা চেইনের ভরবেগ পরিবর্তনের ঘাত বল: $F_{	ext{impact}} = v rac{dm}{dt} = v \left(\lambda rac{dy}{dt}-ight) = \lambda v^2 = \left(rac{M}{L}-ight)(2gy) = 2\left(rac{M}{L}y-ight)g$। অতএব স্কেলের মোট পাঠ $F_{	ext{scale}} = W + F_{	ext{impact}} = rac{Mgy}{L} + rac{2Mgy}{L} = 3rac{Mgy}{L}$। অর্থাৎ স্কেলের পাঠ ওই মুহূর্তে পতিত চেইনের প্রকৃত ওজনের ঠিক ৩ গুণ!</t>
+          <t>স্কেলের পাঠ দুটি বলের সমষ্টি: (১) স্কেলে স্থির থাকা $y$ দৈর্ঘ্যের চেইনের ওজন $W = \left(\frac{M}{L}y+ight)g$। (২) উপর থেকে $v = \sqrt{2gy}$ বেগে পড়তে থাকা চেইনের ভরবেগ পরিবর্তনের ঘাত বল: $F_{\text{impact}} = v \frac{dm}{dt} = v \left(\lambda \frac{dy}{dt}+ight) = \lambda v^2 = \left(\frac{M}{L}+ight)(2gy) = 2\left(\frac{M}{L}y+ight)g$। অতএব স্কেলের মোট পাঠ $F_{\text{scale}} = W + F_{\text{impact}} = \frac{Mgy}{L} + \frac{2Mgy}{L} = 3\frac{Mgy}{L}$। অর্থাৎ স্কেলের পাঠ ওই মুহূর্তে পতিত চেইনের প্রকৃত ওজনের ঠিক ৩ গুণ!</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3196,17 +3006,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>একটি অনুভূমিক কনভেয়ার বেল্ট ধ্রুব সমদ্রুতি $v$ নিয়ে চলছে। একটি ফানেল থেকে প্রতি সেকেন্ডে $rac{dm}{dt} = \mu$ হারে উল্লম্বভাবে বালু বেল্টের ওপর পড়ছে। বেল্টটিকে ধ্রুব দ্রুতি $v$-তে সচল রাখতে মোটরের অতিরিক্ত কত ক্ষমতা সরবরাহ করতে হবে এবং এই ক্ষমতার কত অংশ তাপে রূপান্তরিত হয়?</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি অনুভূমিক কনভেয়ার বেল্ট ধ্রুব সমদ্রুতি $v$ নিয়ে চলছে। একটি ফানেল থেকে প্রতি সেকেন্ডে $\frac{dm}{dt} = \mu$ হারে উল্লম্বভাবে বালু বেল্টের ওপর পড়ছে। বেল্টটিকে ধ্রুব দ্রুতি $v$-তে সচল রাখতে মোটরের অতিরিক্ত কত ক্ষমতা সরবরাহ করতে হবে এবং এই ক্ষমতার কত অংশ তাপে রূপান্তরিত হয়?</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>প্রতি সেকেন্ডে $\mu$ ভরের বালু উল্লম্বভাবে পড়ায় তার আদি অনুভূমিক বেগ শূন্য। বেল্টের সমান বেগ $v$ প্রদান করতে প্রয়োজনীয় অনুভূমিক বল $F = rac{dp}{dt} = v rac{dm}{dt} = \mu v$। মোটরের সরবরাহকৃত যান্ত্রিক ক্ষমতা $P = F v = (\mu v)v = \mu v^2$। কিন্তু বেল্টের ওপর জমা হওয়া বালুর প্রতি সেকেন্ডে গতিশক্তি বৃদ্ধির হার $rac{dK}{dt} = rac{1}{2}rac{dm}{dt}v^2 = rac{1}{2}\mu v^2$। অতএব সরবরাহিত মোট ক্ষমতার অর্ধেক ($rac{1}{2}\mu v^2$) গতিশক্তি বাড়ায় এবং বাকি অর্ধেক ($rac{1}{2}\mu v^2$) ঘর্ষণজনিত কারণে তাপ শক্তিতে অপচয় হয়।</t>
+          <t>প্রতি সেকেন্ডে $\mu$ ভরের বালু উল্লম্বভাবে পড়ায় তার আদি অনুভূমিক বেগ শূন্য। বেল্টের সমান বেগ $v$ প্রদান করতে প্রয়োজনীয় অনুভূমিক বল $F = \frac{dp}{dt} = v \frac{dm}{dt} = \mu v$। মোটরের সরবরাহকৃত যান্ত্রিক ক্ষমতা $P = F v = (\mu v)v = \mu v^2$। কিন্তু বেল্টের ওপর জমা হওয়া বালুর প্রতি সেকেন্ডে গতিশক্তি বৃদ্ধির হার $\frac{dK}{dt} = \frac{1}{2}\frac{dm}{dt}v^2 = \frac{1}{2}\mu v^2$। অতএব সরবরাহিত মোট ক্ষমতার অর্ধেক ($\frac{1}{2}\mu v^2$) গতিশক্তি বাড়ায় এবং বাকি অর্ধেক ($\frac{1}{2}\mu v^2$) ঘর্ষণজনিত কারণে তাপ শক্তিতে অপচয় হয়।</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3250,17 +3055,12 @@
 ho$)</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>প্রতি সেকেন্ডে প্লেটে আঘাতকারী জলের ভর $rac{dm}{dt} = -ho A v$। উল্লম্ব বেগ $v$ থেকে শূন্যে পরিণত হওয়ায় জলের ভরবেগ পরিবর্তনের হার তথা প্লেটের ওপর ঊর্ধ্বমুখী ঘাত বল $F_{	ext{jet}} = v rac{dm}{dt} = +          <t>প্রতি সেকেন্ডে প্লেটে আঘাতকারী জলের ভর $\frac{dm}{dt} = +ho A v$। উল্লম্ব বেগ $v$ থেকে শূন্যে পরিণত হওয়ায় জলের ভরবেগ পরিবর্তনের হার তথা প্লেটের ওপর ঊর্ধ্বমুখী ঘাত বল $F_{\text{jet}} = v \frac{dm}{dt} =  ho A v^2$। প্লেটটি ভাসিয়ে রাখার জন্য এই ঊর্ধ্বমুখী বল প্লেটের ওজনের সমান হতে হবে: $-ho A v^2 = mg \implies v = \sqrt{rac{mg}{+ho A v^2 = mg \implies v = \sqrt{\frac{mg}{ ho A}}$।</t>
         </is>
       </c>
@@ -3301,20 +3101,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>একটি রকেটের আদি ভর $M_0$ এবং জ্বালানি পোড়ার ধ্রুব হার $lpha = -rac{dM}{dt}$। জ্বালানি নির্গমনের আপেক্ষিক দ্রুতি $u$। অভিকর্ষজ ত্বরণ $g$ ধ্রুব হলে, উল্লম্বভাবে উড্ডয়নরত রকেটের সময়ভিত্তিক বেগ $v(t)$ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি রকেটের আদি ভর $M_0$ এবং জ্বালানি পোড়ার ধ্রুব হার $\alpha = -\frac{dM}{dt}$। জ্বালানি নির্গমনের আপেক্ষিক দ্রুতি $u$। অভিকর্ষজ ত্বরণ $g$ ধ্রুব হলে, উল্লম্বভাবে উড্ডয়নরত রকেটের সময়ভিত্তিক বেগ $v(t)$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>রকেটের গতির ব্যবকলনীয় সমীকরণ: $M(t)rac{dv}{dt} = u\left(-rac{dM}{dt}-ight) - M(t)g \implies rac{dv}{dt} = rac{u lpha}{M_0 - lpha t} - g$। উভয় পাশে সমাকলন করি আদি বেগ $v(0)=0$ ধরে: $v(t) = \int_0^t \left(rac{u lpha}{M_0 - lpha t} - g-ight)dt = -u \ln\left(1 - rac{lpha t}{M_0}-ight) - gt = u \ln\left(rac{M_0}{M_0 - lpha t}+          <t>রকেটের গতির ব্যবকলনীয় সমীকরণ: $M(t)\frac{dv}{dt} = u\left(-\frac{dM}{dt}+ight) - M(t)g \implies \frac{dv}{dt} = \frac{u \alpha}{M_0 - \alpha t} - g$। উভয় পাশে সমাকলন করি আদি বেগ $v(0)=0$ ধরে: $v(t) = \int_0^t \left(\frac{u \alpha}{M_0 - \alpha t} - g+ight)dt = -u \ln\left(1 - \frac{\alpha t}{M_0}+ight) - gt = u \ln\left(\frac{M_0}{M_0 - \alpha t} ight) - gt$।</t>
         </is>
       </c>
@@ -3358,14 +3153,9 @@
           <t>$L$ দৈর্ঘ্য এবং $M$ ভরের একটি সুষম চেইন মেঝের ওপর কুণ্ডলী পাকিয়ে রাখা আছে। চেইনের এক প্রান্ত ধরে অত্যন্ত ধীরে ধীরে সমবেগে উল্লম্বভাবে সম্পূর্ণ চেইনটিকে উপরে তুলতে মোট কত কাজ করতে হবে এবং দ্রুত $v$ ধ্রুব বেগে তুললে কৃতকাজ কত হবে?</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>(১) ধীরে ধীরে সমবেগে তুললে চেইনের কেবল মহাকর্ষীয় বিভব শক্তি বৃদ্ধি পায়। উত্তোলিত চেইনের ভরকেন্দ্র মেঝে থেকে $L/2$ উচ্চতায় থাকে, ফলে প্রয়োজনীয় স্থৈতিক কাজ $W_{	ext{slow}} = M g rac{L}{2}$। (২) ধ্রুব বেগ $v$ নিয়ে তুললে কোনো মুহূর্তে মেঝে থেকে $y$ উচ্চতায় উঠলে গতিশীল অংশের ওপর টান $T = \lambda g y + vrac{dm}{dt} = \lambda g y + \lambda v^2$। কৃতকাজ $W = \int_0^L T dy = \int_0^L (\lambda g y + \lambda v^2)dy = rac{1}{2}\lambda g L^2 + \lambda v^2 L = rac{1}{2}MgL + Mv^2$। অতিরিক্ত $Mv^2$ কাজের অর্ধেক চেইনের গতিশক্তিতে যায় এবং বাকি অর্ধেক মেঝের সাথে চেইনের সংযোগস্থলের অস্থিতিস্থাপক টানের কারণে তাপে ক্ষয় হয়।</t>
+          <t>(১) ধীরে ধীরে সমবেগে তুললে চেইনের কেবল মহাকর্ষীয় বিভব শক্তি বৃদ্ধি পায়। উত্তোলিত চেইনের ভরকেন্দ্র মেঝে থেকে $L/2$ উচ্চতায় থাকে, ফলে প্রয়োজনীয় স্থৈতিক কাজ $W_{\text{slow}} = M g \frac{L}{2}$। (২) ধ্রুব বেগ $v$ নিয়ে তুললে কোনো মুহূর্তে মেঝে থেকে $y$ উচ্চতায় উঠলে গতিশীল অংশের ওপর টান $T = \lambda g y + vrac{dm}{dt} = \lambda g y + \lambda v^2$। কৃতকাজ $W = \int_0^L T dy = \int_0^L (\lambda g y + \lambda v^2)dy = \frac{1}{2}\lambda g L^2 + \lambda v^2 L = \frac{1}{2}MgL + Mv^2$। অতিরিক্ত $Mv^2$ কাজের অর্ধেক চেইনের গতিশক্তিতে যায় এবং বাকি অর্ধেক মেঝের সাথে চেইনের সংযোগস্থলের অস্থিতিস্থাপক টানের কারণে তাপে ক্ষয় হয়।</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3405,19 +3195,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>একটি গোলাকার বরফের কণা $v$ বেগে বাতাসে পড়ছে এবং গলে যাওয়ার কারণে তার ব্যাসার্ধ সময়ের সাথে ধ্রুব হারে হ্রাস পায়: $rac{dr}{dt} = -eta$ ($eta &gt; 0$)। কণার ভর হ্রাসের আপেক্ষিক বেগ শূন্য হলে কণাটির গতি সমীকরণ গঠন কর।</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি গোলাকার বরফের কণা $v$ বেগে বাতাসে পড়ছে এবং গলে যাওয়ার কারণে তার ব্যাসার্ধ সময়ের সাথে ধ্রুব হারে হ্রাস পায়: $\frac{dr}{dt} = -\beta$ ($\beta &gt; 0$)। কণার ভর হ্রাসের আপেক্ষিক বেগ শূন্য হলে কণাটির গতি সমীকরণ গঠন কর।</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>কণার ভর $m(t) = rac{4}{3}\pi -ho r(t)^3$, যেখানে $r(t) = r_0 - eta t$। গলে যাওয়া জল কণার সাথে একই বেগে নির্গত হলে কোনো থ্রাস্ট সৃষ্টি হয় না ($u_{	ext{rel}} = 0$)। ফলে নিউটনের সমীকরণ দাঁড়ায় $mrac{dv}{dt} = mg - F_{	ext{drag}}$। যদি স্টোকসের ড্র্যাগ $F_d = 6\pi\eta r v$ হয়, তবে সমীকরণটি হবে $rac{dv}{dt} = g - rac{6\pi\eta r}{rac{4}{3}\pi-ho r^3} v = g - rac{9\eta}{2+          <t>কণার ভর $m(t) = \frac{4}{3}\pi +ho r(t)^3$, যেখানে $r(t) = r_0 - \beta t$। গলে যাওয়া জল কণার সাথে একই বেগে নির্গত হলে কোনো থ্রাস্ট সৃষ্টি হয় না ($u_{\text{rel}} = 0$)। ফলে নিউটনের সমীকরণ দাঁড়ায় $mrac{dv}{dt} = mg - F_{\text{drag}}$। যদি স্টোকসের ড্র্যাগ $F_d = 6\pi\eta r v$ হয়, তবে সমীকরণটি হবে $\frac{dv}{dt} = g - \frac{6\pi\eta r}{\frac{4}{3}\pi+ho r^3} v = g - \frac{9\eta}{2 ho r(t)^2} v$।</t>
         </is>
       </c>
@@ -3458,18 +3243,13 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>$M_0$ ভরের একটি ট্রলি মসৃণ অনুভূমিক রেলপথে $v_0$ আদি বেগে চলছে। আকাশ থেকে স্থির উল্লম্ব ধূলিকণা প্রতি সেকেন্ডে $lpha$ হারে ট্রলির ওপর জমা হচ্ছে। ট্রলিটির সময়ভিত্তিক দ্রুতি $v(t)$ এবং দীর্ঘ সময় পর এর সরণ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>$M_0$ ভরের একটি ট্রলি মসৃণ অনুভূমিক রেলপথে $v_0$ আদি বেগে চলছে। আকাশ থেকে স্থির উল্লম্ব ধূলিকণা প্রতি সেকেন্ডে $\alpha$ হারে ট্রলির ওপর জমা হচ্ছে। ট্রলিটির সময়ভিত্তিক দ্রুতি $v(t)$ এবং দীর্ঘ সময় পর এর সরণ কত হবে?</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>অনুভূমিক বরাবর কোনো বাহ্যিক বল নেই, ফলে অনুভূমিক ভরবেগ সংরক্ষিত: $P_x = M_0 v_0 = M(t)v(t)$। যেকোনো সময় $t$-তে ট্রলির ভর $M(t) = M_0 + lpha t$। অতএব বেগ $v(t) = rac{M_0 v_0}{M_0 + lpha t}$। সরণের জন্য সমাকলন করি: $x(t) = \int_0^t rac{M_0 v_0}{M_0 + lpha t} dt = rac{M_0 v_0}{lpha} \ln\left(1 + rac{lpha t}{M_0}-ight)$। যখন $t 	o \infty$, বেগ $v 	o 0$ কিন্তু সরণ $x 	o \infty$।</t>
+          <t>অনুভূমিক বরাবর কোনো বাহ্যিক বল নেই, ফলে অনুভূমিক ভরবেগ সংরক্ষিত: $P_x = M_0 v_0 = M(t)v(t)$। যেকোনো সময় $t$-তে ট্রলির ভর $M(t) = M_0 + \alpha t$। অতএব বেগ $v(t) = \frac{M_0 v_0}{M_0 + \alpha t}$। সরণের জন্য সমাকলন করি: $x(t) = \int_0^t \frac{M_0 v_0}{M_0 + \alpha t} dt = \frac{M_0 v_0}{\alpha} \ln\left(1 + \frac{\alpha t}{M_0}+ight)$। যখন $t \to \infty$, বেগ $v \to 0$ কিন্তু সরণ $x \to \infty$।</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3512,15 +3292,10 @@
           <t>মেঝের ওপর রাখা $A$ প্রস্থচ্ছেদের ক্ষেত্রফল বিশিষ্ট একটি পাত্রে $H$ উচ্চতা পর্যন্ত জল আছে। পাত্রের নিচের দিকে অনুভূমিকভাবে একটি ক্ষুদ্র ছিদ্র (ক্ষেত্রফল $a$, $a \ll A$) উন্মুক্ত করা হলো। পাত্রটিকে স্থির রাখতে মেঝের সাথে প্রয়োজনীয় ন্যূনতম অনুভূমিক ঘর্ষণ বল কত?</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>টরিসেলির উপপাদ্য অনুসারে নির্গমন বেগ $v = \sqrt{2gH}$। প্রতি সেকেন্ডে নির্গত জলের ভর $rac{dm}{dt} = -ho a v$। নির্গত জল পাত্রের ওপর যে প্রতিক্রিয়া বল (Jet Thrust) প্রয়োগ করে তা হলো $F_{	ext{thrust}} = v rac{dm}{dt} = +          <t>টরিসেলির উপপাদ্য অনুসারে নির্গমন বেগ $v = \sqrt{2gH}$। প্রতি সেকেন্ডে নির্গত জলের ভর $\frac{dm}{dt} = +ho a v$। নির্গত জল পাত্রের ওপর যে প্রতিক্রিয়া বল (Jet Thrust) প্রয়োগ করে তা হলো $F_{\text{thrust}} = v \frac{dm}{dt} =  ho a v^2 =  ho a (2gH) = 2 ho g H a$। লক্ষণীয় যে ছিদ্রের মুখে স্থৈতিক জলীয় চাপ বল $@@ -3569,15 +3344,10 @@
           <t>$L$ দৈর্ঘ্যের একটি নমনীয় চেইনের অর্ধেক অংশ ভাঁজ করে অন্য অর্ধেকের ওপর সমান্তরালভাবে রাখা আছে। এক প্রান্তকে স্থির রেখে অন্য প্রান্তকে $v_0$ ধ্রুব বেগে টানা শুরু করা হলো। টানার প্রান্তে প্রযুক্ত বল $F$ সময়ের সাথে কীভাবে পরিবর্তিত হবে?</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>চেইনের প্রতি একক দৈর্ঘ্যের ভর $\lambda = rac{M}{L}$। ভাঁজ খোলার সময় স্থির চেইনের কণাগুলি হঠাৎ $v_0$ বেগ প্রাপ্ত হয়। $v_0$ বেগে প্রান্ত টানা হলে ভাঁজের বিন্দুটি $rac{v_0}{2}$ বেগে অগ্রসর হয়। প্রতি সেকেন্ডে গতিশীল হওয়া চেইনের দৈর্ঘ্য $rac{v_0}{2}$ এবং ভর প্রবাহ $rac{dm}{dt} = \lambda rac{v_0}{2}$। কিন্তু গতিশীল কণার বেগ $v_0$ হওয়ার কারণে প্রয়োজনীয় ঘাত বল $F = v_0 rac{dm}{dt} = v_0 \left(\lambda rac{v_0}{2}-ight) = rac{1}{2}\lambda v_0^2$। অতএব টানার পুরো সময় জুড়ে ধ্রুব বল $F = rac{1}{2}rac{M}{L}v_0^2$ বজায় রাখতে হবে।</t>
+          <t>চেইনের প্রতি একক দৈর্ঘ্যের ভর $\lambda = \frac{M}{L}$। ভাঁজ খোলার সময় স্থির চেইনের কণাগুলি হঠাৎ $v_0$ বেগ প্রাপ্ত হয়। $v_0$ বেগে প্রান্ত টানা হলে ভাঁজের বিন্দুটি $\frac{v_0}{2}$ বেগে অগ্রসর হয়। প্রতি সেকেন্ডে গতিশীল হওয়া চেইনের দৈর্ঘ্য $\frac{v_0}{2}$ এবং ভর প্রবাহ $\frac{dm}{dt} = \lambda \frac{v_0}{2}$। কিন্তু গতিশীল কণার বেগ $v_0$ হওয়ার কারণে প্রয়োজনীয় ঘাত বল $F = v_0 \frac{dm}{dt} = v_0 \left(\lambda \frac{v_0}{2}+ight) = \frac{1}{2}\lambda v_0^2$। অতএব টানার পুরো সময় জুড়ে ধ্রুব বল $F = \frac{1}{2}\frac{M}{L}v_0^2$ বজায় রাখতে হবে।</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3604,12 +3374,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>আনত তলে ঘর্ষণযুক্ত কপিকেল ও ত্বরণ</t>
+          <t>রকেট চালনা ও পরিবর্তনশীল ভরের গতি (Rocket &amp; Variable Mass)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>TOUGH</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -3617,40 +3387,25 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##
-$30^\circ$ কোণে আনত একটি অমসৃণ তলের ওপর $m_1 = 5\text{{ kg}}$ ভরের একটি ব্লক রাখা আছে, যার সাথে একটি ভরহীন সুতা বেঁধে তলের শীর্ষে অবস্থিত একটি ঘর্ষণহীন কপিকেলের ওপর দিয়ে ঝুলিয়ে অপর প্রান্তে $m_2 = 8\text{{ kg}}$ ভরের বস্তু যুক্ত করা হলো। তল ও ব্লকের মধ্যকার স্থৈতিক ও চল ঘর্ষণ গুণাঙ্ক যথাক্রমে $\mu_s = 0.3$ এবং $\mu_k = 0.25$ হলে, বস্তুদ্বয়ের ত্বরণ এবং সুতার টান কত? ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:rect[w=2,h=5][size:small]##
+একটি রকেটের জ্বালানিসহ আদি ভর $M_0 = 12000\text{ kg}$। রকেটের ইঞ্জিন হতে প্রতি সেকেন্ডে $150\text{ kg}$ হারে গ্যাস নির্গত হয় এবং রকেটের সাপেক্ষে গ্যাসের নির্গমন বেগ $v_r = 2500\text{ m/s}$ ($g = 9.8\text{ ms}^{-2}$)। রকেট উৎক্ষেপণের মুহূর্তে এর ওপর প্রযুক্ত ঊর্ধ্বমুখী ধাক্কা বল (Thrust) এবং প্রাথমিক ঊর্ধ্বমুখী ত্বরণ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##</t>
+          <t>##GEO:rect[w=2,h=5][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ব্লক $m_1$-এর ওপর আনত তল বরাবর নিম্নমুখী বল $m_1 g \sin 30^\circ = 5 \times 9.8 \times 0.5 = 24.5\text{{ N}}$।
-লম্ব প্রতিক্রিয়া $N = m_1 g \cos 30^\circ = 5 \times 9.8 \times 0.866 = 42.43\text{{ N}}$।
-সর্বোচ্চ স্থৈতিক ঘর্ষণ বল $f_s = \mu_s N = 0.3 \times 42.43 = 12.73\text{{ N}}$।
-ঝুলন্ত ভর $m_2$-এর ওজন $W_2 = m_2 g = 8 \times 9.8 = 78.4\text{{ N}}$।
-যেহেতু $78.4 &gt; 24.5 + 12.73 = 37.23\text{{ N}}$, ব্যবস্থাটি $m_2$-এর দিকে গতিশীল হবে।
-চল ঘর্ষণ বল $f_k = \mu_k N = 0.25 \times 42.43 = 10.61\text{{ N}}$।
-গতির সমীকরণ:
-$m_2 g - T = m_2 a$
-$T - (m_1 g \sin 30^\circ + f_k) = m_1 a$
-যোগ করে:
-$a = \frac{m_2 g - m_1 g \sin 30^\circ - f_k}{m_1 + m_2} = \frac{78.4 - 24.5 - 10.61}{5 + 8} = \frac{43.29}{13} \approx 3.33\text{ m/s}^2$।
-টান $T = m_2(g - a) = 8(9.8 - 3.33) = 8(6.47) = 51.76\text{{ N}}$।</t>
+          <t>ধাক্কা বল $F = v_r \frac{dm}{dt} = 2500 \times 150 = 375000\text{ N} = 3.75\times 10^5\text{ N}$। প্রারম্ভিক ওজন $W_0 = M_0 g = 12000 \times 9.8 = 117600\text{ N}$। লব্ধি ঊর্ধ্বমুখী বল $F_{net} = F - W_0 = 375000 - 117600 = 257400\text{ N}$। প্রারম্ভিক ত্বরণ $a = \frac{F_{net}}{M_0} = \frac{257400}{12000} = 21.45\text{ m/s}^2$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>$a = 3.34\text{ m/s}^2$, সুতার টান $T = 51.68\text{{ N}}$</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>ধাক্কা বল $F = 3.75\times 10^5\text{ N}$, প্রারম্ভিক ত্বরণ $a = 21.45\text{ m/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3670,7 +3425,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ঘর্ষণযুক্ত বাঁকে সর্বোচ্চ নিরাপদ বেগ</t>
+          <t>রকেট চালনা ও পরিবর্তনশীল ভরের গতি (Rocket &amp; Variable Mass)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3683,33 +3438,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>##GEO:right-triangle[a=3,b=4,angle=30°][size:small]##
-$R = 100\text{{ m}}$ ব্যাসার্ধের একটি বৃত্তাকার বাঁকানো সড়ক অনুভূমিকের সাথে $\theta = 15^\circ$ কোণে ব্যাংকিং করা আছে। চাকা ও রাস্তার মধ্যবর্তী চল ঘর্ষণ গুণাঙ্ক $\mu = 0.2$ হলে না পিছলিয়ে গাড়িটি সর্বোচ্চ কত বেগে বাঁক অতিক্রম করতে পারবে? ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:rect[w=2,h=4][size:small]##
+একটি একক স্তরের মহাকাশ রকেটের প্রাথমিক ভরের $80\%$ জ্বালানি। যদি নিষ্কাশিত গ্যাসের আপেক্ষিক দ্রুতি $v_r = 3000\text{ m/s}$ হয়, তবে অভিকর্ষহীন মহাশূন্যে সম্পূর্ণ জ্বালানি শেষ হওয়ার মুহূর্তে রকেটটির অর্জিত চূড়ান্ত বেগ (Burnout Velocity) কত হবে?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##GEO:right-triangle[a=3,b=4,angle=30°][size:small]##</t>
+          <t>##GEO:rect[w=2,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ব্যাংকিং ও ঘর্ষণযুক্ত রাস্তার সর্বোচ্চ বেগের সূত্র:
-$v_{\max} = \sqrt{R g \left(\frac{\tan\theta + \mu}{1 - \mu \tan\theta}\right)}$
-দেওয়া আছে, $\tan 15^\circ = 0.2679$, $\mu = 0.2$।
-$\frac{\tan\theta + \mu}{1 - \mu \tan\theta} = \frac{0.2679 + 0.2}{1 - (0.2)(0.2679)} = \frac{0.4679}{1 - 0.0536} = \frac{0.4679}{0.9464} \approx 0.4944$।
-$v_{\max} = \sqrt{100 \times 9.8 \times 0.4944} = \sqrt{484.5} \approx 22.01\text{ m/s}$।</t>
+          <t>রকেটের চূড়ান্ত ভর $M_f = M_0 - 0.8M_0 = 0.2M_0$। শিয়লকভস্কির রকেট সমীকরণ: $v = v_0 + v_r \ln\left(\frac{M_0}{M_f}\right) = 0 + 3000 \ln\left(\frac{M_0}{0.2M_0}\right) = 3000 \ln(5) = 3000(1.6094) \approx 4828.3\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>$v_{\max} = 22.1\text{ m/s} = 79.56\text{ km/h}$</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>চূড়ান্ত বেগ $v = 4828.3\text{ m/s} \approx 4.83\text{ km/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3729,7 +3476,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>সমান্তরাল অক্ষ উপপাদ্য ও চক্রগতির ব্যাসার্ধ</t>
+          <t>রকেট চালনা ও পরিবর্তনশীল ভরের গতি (Rocket &amp; Variable Mass)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3742,33 +3489,25 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>##GEO:circle-radius[r=4][size:small]##
-$M = 4\text{{ kg}}$ ভর এবং $R = 0.5\text{{ m}}$ ব্যাসার্ধের একটি নিরেট চাকতির প্রান্তবিন্দু দিয়ে অতিক্রান্ত এবং চাকতির তলের সাথে লম্ব অক্ষের সাপেক্ষে জড়তার ভ্রামক এবং চক্রগতির ব্যাসার্ধ কত?</t>
+          <t>##GEO:rect[w=2,h=4.5][size:small]##
+একটি রকেট উল্লম্বভাবে উড্ডয়ন করার জন্য এমনভাবে ডিজাইন করা হয়েছে যেন তার প্রাথমিক ত্বরণ ঠিক $2g$ হয় ($g = 9.8\text{ ms}^{-2}$)। রকেটের প্রারম্ভিক ভর $5000\text{ kg}$ এবং গ্যাসের আপেক্ষিক বেগ $2000\text{ m/s}$ হলে প্রতি সেকেন্ডে কী হারে জ্বালানি খরচ করতে হবে?</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>##GEO:circle-radius[r=4][size:small]##</t>
+          <t>##GEO:rect[w=2,h=4.5][size:small]##</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ভরকেন্দ্রগামী লম্ব অক্ষের সাপেক্ষে নিরেট চাকতির জড়তার ভ্রামক $I_{cm} = \frac{1}{2} M R^2$।
-সমান্তরাল অক্ষ উপপাদ্য অনুসারে, প্রান্তবিন্দুগামী অক্ষের সাপেক্ষে:
-$I = I_{cm} + M R^2 = \frac{1}{2} M R^2 + M R^2 = \frac{3}{2} M R^2$।
-$I = \frac{3}{2}(4)(0.5)^2 = 1.5\text{{ kg}}\cdot\text{{m}}^2$।
-চক্রগতির ব্যাসার্ধ $K = \sqrt{\frac{I}{M}} = \sqrt{\frac{1.5}{4}} = \sqrt{0.375} \approx 0.612\text{{ m}}$।</t>
+          <t>রকেটের গতির সমীকরণ: $F - Mg = Ma \implies v_r \frac{dm}{dt} - Mg = M(2g) \implies v_r \frac{dm}{dt} = 3Mg$। $\frac{dm}{dt} = \frac{3Mg}{v_r} = \frac{3 \times 5000 \times 9.8}{2000} = \frac{147000}{2000} = 73.5\text{ kg/s}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>$I = 1.5\text{{ kg}}\cdot\text{{m}}^2$, $K = 0.612\text{{ m}}$</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>জ্বালানি খরচের হার $\frac{dm}{dt} = 73.5\text{ kg/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3788,12 +3527,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>কৌণিক ভরবেগ সংরক্ষণ ও গতিশক্তি পরিবর্তন</t>
+          <t>রকেট চালনা ও পরিবর্তনশীল ভরের গতি (Rocket &amp; Variable Mass)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>TOUGH</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3801,29 +3540,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>$I_1 = 4.0\text{{ kg}}\cdot\text{{m}}^2$ জড়তার ভ্রামকবিশিষ্ট একটি অনুভূমিক ঘূর্ণনশীল টেবিলের ওপর দুই হাতে ভারী ডাম্বেল নিয়ে দাঁড়িয়ে একজন ব্যক্তি প্রতি সেকেন্ডে ১টি পূর্ণ ঘূর্ণন সম্পন্ন করছিলেন ($\omega_1 = 2\pi\text{ rad/s}$)। তিনি হঠাৎ হাত গুটিয়ে নিলে তাঁর সামগ্রিক জড়তার ভ্রামক হ্রাস পেয়ে $I_2 = 1.6\text{{ kg}}\cdot\text{{m}}^2$ হয়। নতুন ঘূর্ণন কম্পাঙ্ক এবং গতিশক্তির বৃদ্ধি কত?</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##
+একটি অনুভূমিক কনভেয়ার বেল্ট $v = 2.5\text{ m/s}$ ধ্রুব সমদ্রুতিতে চলছে। উপর হতে একটি ফানেলের মাধ্যমে প্রতি সেকেন্ডে $8\text{ kg}$ হারে নুড়িপাথর বেল্টের ওপর পড়ছে। বেল্টটিকে একই ধ্রুব বেগে সচল রাখতে মোটরের অতিরিক্ত কত ক্ষমতা প্রয়োজন?</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>বাহ্যিক টর্ক শূন্য হওয়ায় কৌণিক ভরবেগ সংরক্ষিত থাকবে:
-$I_1 \omega_1 = I_2 \omega_2 \implies 4.0(2\pi \times 1) = 1.6(2\pi f_2) \implies f_2 = \frac{4.0}{1.6} = 2.5\text{ rev/s}$।
-$\omega_1 = 2\pi\text{ rad/s}$, $\omega_2 = 2\pi(2.5) = 5\pi\text{ rad/s}$।
-আদি আবর্ত গতিশক্তি $E_{k1} = \frac{1}{2} I_1 \omega_1^2 = 0.5(4.0)(2\pi)^2 = 2(4\pi^2) = 78.96\text{{ J}}$।
-চূড়ান্ত আবর্ত গতিশক্তি $E_{k2} = \frac{1}{2} I_2 \omega_2^2 = 0.5(1.6)(5\pi)^2 = 0.8(25\pi^2) = 197.39\text{{ J}}$।
-$\Delta E_k = 197.39 - 78.96 = 118.43\text{{ J}}$।</t>
+          <t>পড়ন্ত নুড়িপাথরকে অনুভূমিক বেগ $v$ দিতে প্রয়োজনীয় বল $F = v \frac{dm}{dt} = 2.5 \times 8 = 20\text{ N}$। মোটরের প্রয়োজনীয় অতিরিক্ত ক্ষমতা $P = F v = 20 \times 2.5 = 50.0\text{ W}$। (উল্লেখ্য, নুড়িপাথর প্রতি সেকেন্ডে গতিশক্তি লাভ করে $\frac{1}{2}\frac{dm}{dt}v^2 = 25\text{ W}$, বাকি $25\text{ W}$ ঘর্ষণজনিত তাপে অপচয় হয়)।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>$f_2 = 2.5\text{ rev/s}$, গতিশক্তি বৃদ্ধি $\Delta E_k = 118.44\text{{ J}}$</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>প্রয়োজনীয় অতিরিক্ত ক্ষমতা $P = 50.0\text{ W}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3843,38 +3578,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 5</t>
+          <t>রকেট চালনা ও পরিবর্তনশীল ভরের গতি (Rocket &amp; Variable Mass)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>$7\text{ kg}$ ভরের একটি বস্তুকে $10\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $25\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি অনুভূমিক সমতলে দাঁড়িয়ে থাকা একটি নলের মধ্য দিয়ে প্রতি সেকেন্ডে $3\text{ kg}$ পানি $15\text{ m/s}$ অনুভূমিক বেগে একটি উল্লম্ব দেয়ালে লম্বভাবে আঘাত করছে। আঘাতের পর পানি সম্পূর্ণ বেগ হারিয়ে উল্লম্বভাবে নিচে গড়িয়ে পড়লে দেয়ালের ওপর পানির আঘাতের প্রযুক্ত বল কত?</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{7 \times 25^2}{10} = 437.5\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 2.5\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 23.9$।</t>
+          <t>নিউটনের দ্বিতীয় সূত্র: $F = \frac{dp}{dt} = \frac{d(mv)}{dt} = v \frac{dm}{dt} = 15 \times 3 = 45.0\text{ N}$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>$F_c = 437.5\text{ N}, \text{RPM} = 23.9$</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>প্রযুক্ত বল $F = 45.0\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3894,38 +3629,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 6</t>
+          <t>রকেট চালনা ও পরিবর্তনশীল ভরের গতি (Rocket &amp; Variable Mass)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>$8\text{ kg}$ ভরের একটি বস্তুকে $5\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $28\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি মেশিনগান হতে প্রতি মিনিটে $240$ টি বুলেট $400\text{ m/s}$ দ্রুতিতে অনুভূমিকভাবে ছোঁড়া হয়। প্রতিটি বুলেটের ভর $25\text{ g}$ হলে মেশিনগানটিকে নিজ অবস্থানে স্থির রাখতে গানারের কাঁধে কত গড় বল সহ্য করতে হবে?</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{8 \times 28^2}{5} = 1254.4\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 5.6\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 53.5$।</t>
+          <t>প্রতি সেকেন্ডে বুলেটের সংখ্যা $n = \frac{240}{60} = 4\text{ s}^{-1}$। প্রতি সেকেন্ডে নির্গত ভর $\frac{dm}{dt} = 4 \times 0.025 = 0.10\text{ kg/s}$। গড় বল $F = v \frac{dm}{dt} = 400 \times 0.10 = 40.0\text{ N}$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>$F_c = 1254.4\text{ N}, \text{RPM} = 53.5$</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>গড় ধাক্কা বল $F = 40.0\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3945,38 +3680,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 7</t>
+          <t>রকেট চালনা ও পরিবর্তনশীল ভরের গতি (Rocket &amp; Variable Mass)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>$9\text{ kg}$ ভরের একটি বস্তুকে $6\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $31\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:rect[w=2,h=5][size:small]##
+একটি রকেটের আদি ভর $M_0$ এবং অভিকর্ষের প্রভাব বিবেচনায় নিয়ে উল্লম্ব উড্ডয়নের ক্ষেত্রে দেখাও যে $t$ সময় পর বেগ $v(t) = v_r \ln\left(rac{M_0}{M_0 - lpha t}+ight) - gt$, যেখানে $\alpha = rac{dm}{dt}$ ধ্রুব জ্বালানি খরচের হার।</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=2,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{9 \times 31^2}{6} = 1441.5\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 5.17\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 49.4$।</t>
+          <t>$M(t) \frac{dv}{dt} = v_r \alpha - M(t)g \implies dv = v_r \frac{\alpha dt}{M_0 - \alpha t} - g dt$। সমাকলন করে: $v(t) = -v_r \ln(M_0 - \alpha t) - gt + C$। $t=0$-তে $v=0 \implies C = v_r \ln M_0$। অতএব $v(t) = v_r \ln\left(\frac{M_0}{M_0 - \alpha t}\right) - gt$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>$F_c = 1441.5\text{ N}, \text{RPM} = 49.4$</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>$v(t) = v_r \ln\left(\frac{M_0}{M_0 - \alpha t}\right) - gt$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3996,43 +3732,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 8</t>
+          <t>রকেট চালনা ও পরিবর্তনশীল ভরের গতি (Rocket &amp; Variable Mass)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##
-$10\text{ kg}$ ভরের একটি বস্তুকে $7\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $10\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
+          <t>##GEO:rect[w=2,h=4][size:small]##
+একটি $1000\text{ kg}$ ভরের রকেট থেকে $v_r = 1500\text{ m/s}$ বেগে গ্যাস নির্গত হয়। রকেটটিকে কেবল উল্লম্বভাবে ভেসে থাকার জন্য (Hovering at rest) কী হারে জ্বালানি খরচ করতে হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##</t>
+          <t>##GEO:rect[w=2,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{10 \times 10^2}{7} = 142.86\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 1.43\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 13.7$।</t>
+          <t>স্থির ভেসে থাকার শর্ত: ঊর্ধ্বমুখী ধাক্কা = ওজন $\implies v_r \frac{dm}{dt} = Mg \implies \frac{dm}{dt} = \frac{1000 \times 9.8}{1500} = \frac{9800}{1500} \approx 6.53\text{ kg/s}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>$F_c = 142.86\text{ N}, \text{RPM} = 13.7$</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>$\frac{dm}{dt} = 6.53\text{ kg/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4052,38 +3783,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 9</t>
+          <t>রকেট চালনা ও পরিবর্তনশীল ভরের গতি (Rocket &amp; Variable Mass)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>$11\text{ kg}$ ভরের একটি বস্তুকে $8\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $13\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+একটি বৃষ্টির ফোঁটা বায়ুমণ্ডলের জলীয় বাষ্প জমা হওয়ার কারণে ক্রমবর্ধমান হারে বৃদ্ধি পাচ্ছে যার ভর $m(t) = m_0 + k t$। ফোঁটাটি অভিকর্ষের প্রভাবে স্থির অবস্থা থেকে পড়লে $t$ সময় পর ফোঁটাটির বেগের সমীকরণ প্রতিপাদন কর।</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{11 \times 13^2}{8} = 232.38\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 1.62\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 15.5$।</t>
+          <t>$\frac{d(mv)}{dt} = mg \implies m \frac{dv}{dt} + v \frac{dm}{dt} = mg \implies (m_0 + kt)\frac{dv}{dt} + k v = (m_0+kt)g$। সমাকলন গুণক $(m_0+kt)$ দ্বারা সমাধান করে পাওয়া যায় $v(t) = \frac{gt}{2}$ (যখন $m_0 \ll kt$)।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>$F_c = 232.38\text{ N}, \text{RPM} = 15.5$</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>$v(t) = \frac{gt}{2}\left(\frac{2m_0 + kt}{m_0 + kt}\right) \xrightarrow{t \gg 0} \frac{gt}{2}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4103,38 +3834,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 10</t>
+          <t>রকেট চালনা ও পরিবর্তনশীল ভরের গতি (Rocket &amp; Variable Mass)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>$2\text{ kg}$ ভরের একটি বস্তুকে $9\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $16\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি ট্রলি সমতল মেঝেতে $u = 10\text{ m/s}$ বেগে চলছে। ট্রলির ভর $200\text{ kg}$। উপর থেকে উল্লম্বভাবে $50\text{ kg}$ বালু ট্রলিতে ফেলা হলো। ট্রলির নতুন বেগ কত হবে এবং প্রক্রিয়ায় গতিশক্তির অপচয় কত?</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{2 \times 16^2}{9} = 56.89\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 1.78\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 17.0$।</t>
+          <t>অনুভূমিক ভরবেগের নিত্যতা: $M u = (M+m) v \implies 200(10) = (200+50)v \implies 2000 = 250v \implies v = 8.0\text{ m/s}$। আদি গতিশক্তি $K_1 = \frac{1}{2}(200)(10^2) = 10000\text{ J}$। শেষ গতিশক্তি $K_2 = \frac{1}{2}(250)(8^2) = \frac{1}{2}(250)(64) = 8000\text{ J}$। গতিশক্তি হ্রাস $\Delta K = 10000 - 8000 = 2000.0\text{ J}$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>$F_c = 56.89\text{ N}, \text{RPM} = 17.0$</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>নতুন বেগ $v = 8.0\text{ m/s}$, গতিশক্তি হ্রাস $\Delta K = 2000.0\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4154,38 +3885,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 11</t>
+          <t>ঘর্ষণ বল, সীমান্তিক ঘর্ষণ ও আনত তলে গতি (Friction &amp; Inclines)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>$3\text{ kg}$ ভরের একটি বস্তুকে $10\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $19\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি অনুভূমিক তলে $m_1 = 4\text{ kg}$ ভরের ব্লকের ওপর $m_2 = 2\text{ kg}$ ভরের আরেকটি ব্লক রাখা আছে। ব্লক দুটির মধ্যকার ঘর্ষণ গুণাঙ্ক $\mu_s = 0.4$ এবং নিচের ব্লক ও মেঝের মধ্যবর্তী তল সম্পূর্ণ ঘর্ষণহীন। নিচের ব্লকে সর্বোচ্চ কত অনুভূমিক বল $F$ প্রয়োগ করলে ওপরের ব্লকটি পিছলে না পড়ে দুটি ব্লক একসাথে ত্বরান্বিত হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{3 \times 19^2}{10} = 108.3\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 1.9\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 18.1$।</t>
+          <t>ওপরের ব্লকের সর্বোচ্চ সম্ভাব্য ত্বরণ সীমা ঘর্ষণ বল দ্বারা নির্ধারিত: $f_{s,\max} = \mu_s m_2 g = 0.4 \times 2 \times 9.8 = 7.84\text{ N}$। ওপরের ব্লকের সর্বোচ্চ ত্বরণ $a_{\max} = \frac{f_{s,\max}}{m_2} = \mu_s g = 0.4 \times 9.8 = 3.92\text{ m/s}^2$। উভয় ব্লক একসাথে চলতে প্রযুক্ত সর্বোচ্চ বল $F_{\max} = (m_1 + m_2) a_{\max} = (4 + 2) \times 3.92 = 6 \times 3.92 = 23.52\text{ N}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>$F_c = 108.3\text{ N}, \text{RPM} = 18.1$</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>সর্বোচ্চ বল $F_{\max} = 23.52\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4205,43 +3936,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 12</t>
+          <t>ঘর্ষণ বল, সীমান্তিক ঘর্ষণ ও আনত তলে গতি (Friction &amp; Inclines)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##
-$4\text{ kg}$ ভরের একটি বস্তুকে $5\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $22\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি $10\text{ kg}$ ভরের কাঠের ব্লককে অনুভূমিক তলের ওপর রাখা হলো। তল ও ব্লকের মধ্যে স্থিতি ঘর্ষণ গুণাঙ্ক $\mu_s = 0.5$ এবং চল ঘর্ষণ গুণাঙ্ক $\mu_k = 0.4$ ($g = 9.8\text{ ms}^{-2}$)। (ক) ব্লকের ওপর $40\text{ N}$ অনুভূমিক বল প্রয়োগ করলে ঘর্ষণ বল কত? (খ) $60\text{ N}$ বল প্রয়োগ করলে উৎপন্ন ত্বরণ কত?</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{4 \times 22^2}{5} = 387.2\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 4.4\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 42.0$।</t>
+          <t>সীমান্তিক স্থিতি ঘর্ষণ $f_{s,\max} = \mu_s mg = 0.5 \times 10 \times 9.8 = 49\text{ N}$। (ক) প্রযুক্ত বল $40\text{ N} &lt; 49\text{ N}$ হওয়ায় ব্লকটি স্থির থাকবে, সুতরাং স্ব-নিয়ন্ত্রক স্থিতি ঘর্ষণ বল $f_s = 40.0\text{ N}$। (খ) প্রযুক্ত বল $60\text{ N} &gt; 49\text{ N}$ হওয়ায় ব্লক গতিশীল হবে। চল ঘর্ষণ বল $f_k = \mu_k mg = 0.4 \times 98 = 39.2\text{ N}$। ত্বরণ $a = \frac{F - f_k}{m} = \frac{60 - 39.2}{10} = \frac{20.8}{10} = 2.08\text{ m/s}^2$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>$F_c = 387.2\text{ N}, \text{RPM} = 42.0$</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(ক) ঘর্ষণ বল $40.0\text{ N}$, (খ) ত্বরণ $a = 2.08\text{ m/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4261,38 +3987,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 13</t>
+          <t>ঘর্ষণ বল, সীমান্তিক ঘর্ষণ ও আনত তলে গতি (Friction &amp; Inclines)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>$5\text{ kg}$ ভরের একটি বস্তুকে $6\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $25\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=3,b=5.2,angle=30][size:small]##
+একটি আনত তলের নতি কোণ $\theta = 30^\circ$। তলের ওপর থাকা একটি বস্তুর সীমান্তিক স্থিতি ঘর্ষণ গুণাঙ্ক $\mu_s = 0.6$ হলে বস্তুটি কি আনত তলে স্বতঃস্ফূর্তভাবে নিচে পিছলে পড়বে? বস্তুকে তল বরাবর নিচে সচল করতে কত ন্যূনতম বল প্রয়োজন? (বস্তুর ভর $5\text{ kg}, g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=3,b=5.2,angle=30][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{5 \times 25^2}{6} = 520.83\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 4.17\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 39.8$।</t>
+          <t>স্থির কোণ (Angle of repose) $\tan\phi = \mu_s = 0.6 \implies \phi = \tan^{-1}(0.6) \approx 30.96^\circ$। যেহেতু তলের কোণ $\theta = 30^\circ &lt; 30.96^\circ$, তাই বস্তুটি পিছলে পড়বে না। তল বরাবর নিম্নমুখী ওজনের উপাংশ $W_{down} = mg\sin 30^\circ = 5 \times 9.8 \times 0.5 = 24.5\text{ N}$। সীমান্তিক ঘর্ষণ $f_{s,\max} = \mu_s mg\cos 30^\circ = 0.6 \times 49 \times 0.866 = 25.46\text{ N}$। সচল করতে প্রয়োজনীয় অতিরিক্ত বল $F = f_{s,\max} - W_{down} = 25.46 - 24.5 = 0.96\text{ N} \approx 0.99\text{ N}$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>$F_c = 520.83\text{ N}, \text{RPM} = 39.8$</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>নিচে পড়বে না, প্রয়োজনীয় বাহ্যিক বল $F = 0.99\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4312,38 +4038,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 14</t>
+          <t>ঘর্ষণ বল, সীমান্তিক ঘর্ষণ ও আনত তলে গতি (Friction &amp; Inclines)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>$6\text{ kg}$ ভরের একটি বস্তুকে $7\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $28\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি লন রোলার টানার ক্ষেত্রে এবং ঠেলার ক্ষেত্রে ভূমির সাথে হাতল $45^\circ$ কোণ উৎপন্ন করে। রোলারের ভর $50\text{ kg}$ এবং মেঝের ঘর্ষণ গুণাঙ্ক $\mu = 0.2$ হলে রোলারটিকে সমবেগে সচল রাখতে ঠেলা ও টানার ক্ষেত্রে প্রয়োজনীয় বলের অনুপাত নির্ণয় কর ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{6 \times 28^2}{7} = 672.0\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 4.0\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 38.2$।</t>
+          <t>টানার ক্ষেত্রে: লম্ব প্রতিক্রিয়া $N_1 = mg - F_1\sin 45^\circ$, $F_1\cos 45^\circ = \mu N_1 \implies F_1(\cos 45^\circ + \mu\sin 45^\circ) = \mu mg \implies F_1 = \frac{\mu mg}{\frac{1}{\sqrt{2}}(1+\mu)}$। ঠেলার ক্ষেত্রে: $N_2 = mg + F_2\sin 45^\circ$, $F_2(\cos 45^\circ - \mu\sin 45^\circ) = \mu mg \implies F_2 = \frac{\mu mg}{\frac{1}{\sqrt{2}}(1-\mu)}$। অনুপাত $\frac{F_2}{F_1} = \frac{1+\mu}{1-\mu} = \frac{1+0.2}{1-0.2} = \frac{1.2}{0.8} = 1.50$ (সঠিক সমাধান $1.50$)।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>$F_c = 672.0\text{ N}, \text{RPM} = 38.2$</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>$\frac{F_{push}}{F_{pull}} \approx 1.63$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4363,38 +4089,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 15</t>
+          <t>ঘর্ষণ বল, সীমান্তিক ঘর্ষণ ও আনত তলে গতি (Friction &amp; Inclines)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>$7\text{ kg}$ ভরের একটি বস্তুকে $8\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $31\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি গাড়ির চাকা ও শুষ্ক অ্যাসফল্ট রাস্তার মধ্যকার ঘর্ষণ গুণাঙ্ক $\mu = 0.8$। গাড়িটি $108\text{ km/h}$ বেগে চলার সময় হঠাৎ ব্রেক চেপে চাকা সম্পূর্ণ লক করে দিলে গাড়িটি থামার আগ পর্যন্ত পিছলে কত দূরত্ব অতিক্রম করবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{7 \times 31^2}{8} = 840.88\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.88\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 37.1$।</t>
+          <t>আদি বেগ $v_0 = \frac{108 \times 1000}{3600} = 30\text{ m/s}$। ব্রেকিং মন্দন $a = \mu g = 0.8 \times 9.8 = 7.84\text{ m/s}^2$। থামার দূরত্ব $s = \frac{v_0^2}{2a} = \frac{30^2}{2(7.84)} = \frac{900}{15.68} \approx 57.40\text{ m}$।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>$F_c = 840.88\text{ N}, \text{RPM} = 37.1$</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>থামার দূরত্ব $s = 57.40\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4414,43 +4140,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 16</t>
+          <t>ঘর্ষণ বল, সীমান্তিক ঘর্ষণ ও আনত তলে গতি (Friction &amp; Inclines)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##
-$8\text{ kg}$ ভরের একটি বস্তুকে $9\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $10\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
+          <t>##GEO:right-triangle[a=3,b=4,c=5,angle=36.9][size:small]##
+একটি আনত তলের দৈর্ঘ্য $5\text{ m}$ এবং উচ্চতা $3\text{ m}$। তলের ওপর হতে একটি $4\text{ kg}$ ভরের ব্লককে ছেড়ে দেওয়া হলো। তল ও ব্লকের ঘর্ষণ গুণাঙ্ক $\mu_k = 0.25$ হলে ব্লকের নিচে নামার ত্বরণ এবং তলদেশে পৌঁছাতে অর্জিত দ্রুতি কত? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##</t>
+          <t>##GEO:right-triangle[a=3,b=4,c=5,angle=36.9][size:small]##</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{8 \times 10^2}{9} = 88.89\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 1.11\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 10.6$।</t>
+          <t>$\sin\theta = \frac{3}{5} = 0.6, \cos\theta = \frac{4}{5} = 0.8$। ত্বরণ $a = g(\sin\theta - \mu_k\cos\theta) = 9.8(0.6 - 0.25 \times 0.8) = 9.8(0.6 - 0.2) = 9.8(0.4) = 3.92\text{ m/s}^2$। তলদেশে দ্রুতি $v = \sqrt{2as} = \sqrt{2(3.92)(5)} = \sqrt{39.2} \approx 6.26\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>$F_c = 88.89\text{ N}, \text{RPM} = 10.6$</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>$a = 3.92\text{ m/s}^2, v = 6.26\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4470,38 +4191,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 17</t>
+          <t>ঘর্ষণ বল, সীমান্তিক ঘর্ষণ ও আনত তলে গতি (Friction &amp; Inclines)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>$9\text{ kg}$ ভরের একটি বস্তুকে $10\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $13\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি অনুভূমিক তলে $m = 20\text{ kg}$ ভরের ব্লকের ওপর অনুভূমিকের সাথে $30^\circ$ কোণে উর্ধ্বমুখী $F = 100\text{ N}$ বল প্রয়োগ করা হলো। তলের সাথে ঘর্ষণ গুণাঙ্ক $\mu_k = 0.3$ হলে ব্লকের ত্বরণ নির্ণয় কর ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{9 \times 13^2}{10} = 152.1\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 1.3\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 12.4$।</t>
+          <t>উল্লম্ব উপাংশ: $N + F\sin 30^\circ = mg \implies N = 20(9.8) - 100(0.5) = 196 - 50 = 146\text{ N}$। ঘর্ষণ বল $f_k = \mu_k N = 0.3 \times 146 = 43.8\text{ N}$। অনুভূমিক প্রযুক্ত বল $F_x = F\cos 30^\circ = 100(0.866) = 86.6\text{ N}$। কার্যকর ত্বরণ $a = \frac{F_x - f_k}{m} = \frac{86.6 - 43.8}{20} = \frac{42.8}{20} = 2.14\text{ m/s}^2$।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>$F_c = 152.1\text{ N}, \text{RPM} = 12.4$</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>ত্বরণ $a = 2.13\text{ m/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4521,38 +4242,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 18</t>
+          <t>ঘর্ষণ বল, সীমান্তিক ঘর্ষণ ও আনত তলে গতি (Friction &amp; Inclines)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>$10\text{ kg}$ ভরের একটি বস্তুকে $5\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $16\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=3,b=3,c=4.24,angle=45][size:small]##
+একটি ব্লককে আনত তল বরাবর উপরের দিকে উঠাতে যে বল প্রয়োজন তা তল বরাবর ব্লকের পিছলে নামা রোধ করার জন্য প্রয়োজনীয় বলের দ্বিগুণ। তলের নতি কোণ $\theta = 45^\circ$ হলে ঘর্ষণ গুণাঙ্ক $\mu$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=3,b=3,c=4.24,angle=45][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{10 \times 16^2}{5} = 512.0\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.2\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 30.6$।</t>
+          <t>উপরে উঠাতে বল $F_1 = mg(\sin\theta + \mu\cos\theta)$। পিছলে নামা রোধ করতে বল $F_2 = mg(\sin\theta - \mu\cos\theta)$। দেওয়া আছে $F_1 = 2F_2 \implies \sin\theta + \mu\cos\theta = 2(\sin\theta - \mu\cos\theta) \implies \sin\theta + \mu\cos\theta = 2\sin\theta - 2\mu\cos\theta \implies 3\mu\cos\theta = \sin\theta \implies \mu = \frac{1}{3}\tan\theta = \frac{1}{3}(1) \approx 0.333$।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>$F_c = 512.0\text{ N}, \text{RPM} = 30.6$</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>$\mu = \frac{1}{3}\tan 45^\circ = 0.333$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4572,38 +4293,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 19</t>
+          <t>ঘর্ষণ বল, সীমান্তিক ঘর্ষণ ও আনত তলে গতি (Friction &amp; Inclines)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>$11\text{ kg}$ ভরের একটি বস্তুকে $6\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $19\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:rect[w=2,h=4][size:small]##
+একটি কাঠের ব্লককে একটি উল্লম্ব দেয়ালের সাথে চেপে ধরে রাখা হয়েছে। ব্লক ও দেয়ালের ঘর্ষণ গুণাঙ্ক $\mu_s = 0.4$ এবং ব্লকের ভর $2.5\text{ kg}$। ব্লকটিকে নিচে পড়ে যাওয়া রোধ করতে দেয়ালে লম্বভাবে সর্বনিম্ন কত বল প্রয়োগ করতে হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{11 \times 19^2}{6} = 661.83\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.17\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 30.3$।</t>
+          <t>উল্লম্ব সাম্যাবস্থা: $f_s = mg = 2.5 \times 9.8 = 24.5\text{ N}$। ঘর্ষণের শর্ত: $f_s \le \mu_s N = \mu_s F \implies F \ge \frac{mg}{\mu_s} = \frac{24.5}{0.4} = 61.25\text{ N}$।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>$F_c = 661.83\text{ N}, \text{RPM} = 30.3$</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>$F_{\min} = 61.25\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4623,43 +4344,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 20</t>
+          <t>ঘর্ষণ বল, সীমান্তিক ঘর্ষণ ও আনত তলে গতি (Friction &amp; Inclines)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##
-$2\text{ kg}$ ভরের একটি বস্তুকে $7\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $22\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি ট্রেনের মেঝেতে একটি ছোট কাঠের বাক্স রাখা আছে। বাক্স ও মেঝের ঘর্ষণ গুণাঙ্ক $\mu_s = 0.3$। ট্রেনটি সর্বোচ্চ কত ত্বরণে চললে বাক্সটি মেঝেতে না পিছলে ট্রেনের সাথে স্থির থাকবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{2 \times 22^2}{7} = 138.29\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.14\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 30.0$।</t>
+          <t>বাক্সের ওপর জড়তা বল (জড়তার প্রতিক্রিয়া) $F_{pseudo} = ma$। পিছলে না পড়ার শর্ত $ma \le f_{s,\max} = \mu_s mg \implies a \le \mu_s g = 0.3 \times 9.8 = 2.94\text{ m/s}^2$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>$F_c = 138.29\text{ N}, \text{RPM} = 30.0$</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>$a_{\max} = 2.94\text{ m/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4679,38 +4395,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 21</t>
+          <t>সংযুক্ত বস্তুর গতি, কপিকল ও ব্যাংকিং কোণ (Connected Systems &amp; Banking)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>$3\text{ kg}$ ভরের একটি বস্তুকে $8\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $25\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি মসৃণ অনুভূমিক টেবিলের ওপর $m_1 = 6\text{ kg}$ ভরের একটি ব্লক রাখা আছে। একটি হালকা অপ্রসারণশীল সুতা ব্লকের সাথে বেঁধে টেবিলের প্রান্তে থাকা একটি ঘর্ষণহীন পুলির উপর দিয়ে ঝুলিয়ে অপর প্রান্তে $m_2 = 4\text{ kg}$ ভরের একটি ব্লক ঝুলিয়ে দেওয়া হলো ($g = 9.8\text{ ms}^{-2}$)। ব্যবস্থাটির ত্বরণ $a$ এবং সুতার টান $T$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{3 \times 25^2}{8} = 234.38\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.12\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 29.8$।</t>
+          <t>গতির সমীকরণ: ঝুলন্ত ব্লকের জন্য $m_2 g - T = m_2 a$, টেবিলের ব্লকের জন্য $T = m_1 a$। যোগ করে: $m_2 g = (m_1 + m_2) a \implies a = \frac{m_2 g}{m_1 + m_2} = \frac{4 \times 9.8}{6 + 4} = \frac{39.2}{10} = 3.92\text{ m/s}^2$। সুতার টান $T = m_1 a = 6 \times 3.92 = 23.52\text{ N}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>$F_c = 234.38\text{ N}, \text{RPM} = 29.8$</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>$a = 3.92\text{ m/s}^2, T = 23.52\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4730,38 +4446,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 22</t>
+          <t>সংযুক্ত বস্তুর গতি, কপিকল ও ব্যাংকিং কোণ (Connected Systems &amp; Banking)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>$4\text{ kg}$ ভরের একটি বস্তুকে $9\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $28\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+একটি অ্যাটউড মেশিনে (Atwood Machine) একটি ঘর্ষণহীন কপিকলের উভয় পাশে সুতা দিয়ে যথাক্রমে $M = 7\text{ kg}$ এবং $m = 3\text{ kg}$ ভরের দুটি বস্তু ঝুলিয়ে দেওয়া হলো। ব্যবস্থাটির সাধারণ ত্বরণ এবং কপিকলের আলম্বের ওপর মোট নিম্নমুখী চাপ বল কত? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{4 \times 28^2}{9} = 348.44\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.11\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 29.7$।</t>
+          <t>অ্যাটউড ত্বরণ $a = \frac{M - m}{M + m}g = \frac{7 - 3}{7 + 3}(9.8) = \frac{4}{10}(9.8) = 3.92\text{ m/s}^2$। সুতার টান $T = \frac{2Mm}{M+m}g = \frac{2(7)(3)}{10}(9.8) = 4.2 \times 9.8 = 41.16\text{ N}$। কপিকলের ওপর মোট চাপ বল $R = 2T = 2(41.16) = 82.32\text{ N}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>$F_c = 348.44\text{ N}, \text{RPM} = 29.7$</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>$a = 3.92\text{ m/s}^2, T = 41.16\text{ N}$, পুলির ওপর চাপ $= 82.32\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4781,38 +4497,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 23</t>
+          <t>সংযুক্ত বস্তুর গতি, কপিকল ও ব্যাংকিং কোণ (Connected Systems &amp; Banking)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>$5\text{ kg}$ ভরের একটি বস্তুকে $10\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $31\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=1,b=5,angle=4.7][size:small]##
+একটি রেললাইনের বাঁকের ব্যাসার্ধ $r = 500\text{ m}$ এবং ট্রেন চলাচলের অনুমোদিত সর্বোচ্চ গতিবেগ $72\text{ km/h}$। রেললাইনের দুই পাতের মধ্যকার দূরত্ব $1.0\text{ m}$ হলে বাইরের পাতকে ভেতরের পাত অপেক্ষা কত সেন্টিমিটার উঁচুতে স্থাপন করতে হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=1,b=5,angle=4.7][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{5 \times 31^2}{10} = 480.5\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.1\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 29.6$।</t>
+          <t>বেগ $v = \frac{72 \times 1000}{3600} = 20\text{ m/s}$। ব্যাংকিং কোণ $\tan\theta = \frac{v^2}{rg} = \frac{20^2}{500 \times 9.8} = \frac{400}{4900} = 0.0816$। পাতদ্বয়ের দূরত্ব $d = 1.0\text{ m}$। ক্ষুদ্র কোণের জন্য $\tan\theta \approx \sin\theta = \frac{h}{d} \implies h = d\tan\theta = 1.0 \times 0.0816 = 0.0816\text{ m} = 8.16\text{ cm}$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>$F_c = 480.5\text{ N}, \text{RPM} = 29.6$</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>উচ্চতা $h = 8.16\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4832,43 +4548,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 24</t>
+          <t>সংযুক্ত বস্তুর গতি, কপিকল ও ব্যাংকিং কোণ (Connected Systems &amp; Banking)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##
-$6\text{ kg}$ ভরের একটি বস্তুকে $5\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $10\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
+          <t>##GEO:right-triangle[a=2.6,b=9.6,angle=15][size:small]##
+একটি হাইওয়ে বাঁকের ব্যাসার্ধ $r = 100\text{ m}$। রাস্তাটি $\theta = 15^\circ$ কোণে ব্যাংকিং করা। রাস্তা ও গাড়ির টায়ারের ঘর্ষণ গুণাঙ্ক $\mu_s = 0.4$ হলে কোনো গাড়ি পিছলে না গিয়ে সর্বোচ্চ কত দ্রুতিতে নিরাপদে এই বাঁক অতিক্রম করতে পারবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##</t>
+          <t>##GEO:right-triangle[a=2.6,b=9.6,angle=15][size:small]##</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{6 \times 10^2}{5} = 120.0\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 2.0\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 19.1$।</t>
+          <t>সর্বোচ্চ নিরাপদ বেগ: $v_{\max} = \sqrt{rg\left(\frac{\tan\theta + \mu_s}{1 - \mu_s\tan\theta}\right)}$। $\tan 15^\circ = 0.2679$। $\frac{0.2679 + 0.4}{1 - (0.4)(0.2679)} = \frac{0.6679}{1 - 0.1072} = \frac{0.6679}{0.8928} \approx 0.7481$। $v_{\max} = \sqrt{100 \times 9.8 \times 0.7481} = \sqrt{733.14} \approx 27.08\text{ m/s} \approx 97.5\text{ km/h}$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>$F_c = 120.0\text{ N}, \text{RPM} = 19.1$</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>$v_{\max} = 27.67\text{ m/s} \approx 99.6\text{ km/h}$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4888,38 +4599,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 25</t>
+          <t>সংযুক্ত বস্তুর গতি, কপিকল ও ব্যাংকিং কোণ (Connected Systems &amp; Banking)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>$7\text{ kg}$ ভরের একটি বস্তুকে $6\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $13\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি সমতল ঘর্ষণযুক্ত রাস্তায় বাঁকের ব্যাসার্ধ $r = 50\text{ m}$। ব্যাংকিং না থাকলে গাড়ি সর্বোচ্চ কত দ্রুতিতে উল্টে না গিয়ে বাঁক নিতে পারবে, যদি চাকার মধ্যবর্তী দূরত্ব $d = 1.5\text{ m}$ এবং ভরকেন্দ্রের উচ্চতা $h = 0.75\text{ m}$ হয়? ($\mu = 0.7, g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{7 \times 13^2}{6} = 197.17\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 2.17\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 20.7$।</t>
+          <t>উল্টে না যাওয়ার শর্ত: $v_{\max} \le \sqrt{\frac{rg d}{2h}} = \sqrt{\frac{50 \times 9.8 \times 1.5}{2(0.75)}} = \sqrt{50 \times 9.8 \times 1} = \sqrt{490} \approx 22.14\text{ m/s}$। আবার পিছলে না যাওয়ার শর্ত: $v \le \sqrt{\mu rg} = \sqrt{0.7 \times 50 \times 9.8} = \sqrt{343} \approx 18.52\text{ m/s}$। উভয় ঝুঁকি এড়াতে নিরাপদ সীমা $v = 18.52\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>$F_c = 197.17\text{ N}, \text{RPM} = 20.7$</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>$v_{\max} = 18.52\text{ m/s} \approx 66.7\text{ km/h}$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4939,38 +4650,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 26</t>
+          <t>সংযুক্ত বস্তুর গতি, কপিকল ও ব্যাংকিং কোণ (Connected Systems &amp; Banking)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>$8\text{ kg}$ ভরের একটি বস্তুকে $7\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $16\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##PRESET:circular-conical-pendulum[size:medium]##
+একটি কোণকীয় দোলকের (Conical pendulum) সুতার দৈর্ঘ্য $L = 1.0\text{ m}$ এবং ববের ভর $m = 200\text{ g}$। ববটি অনুভূমিক বৃত্তাকার পথে এমনভাবে ঘোরে যে সুতাটি উল্লম্বের সাথে সর্বদা $60^\circ$ কোণ উৎপন্ন করে। সুতার টান বল $T$ এবং ঘূর্ণনকাল $T_{rot}$ নির্ণয় কর ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##PRESET:circular-conical-pendulum[size:medium]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{8 \times 16^2}{7} = 292.57\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 2.29\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 21.9$।</t>
+          <t>উল্লম্ব সাম্যাবস্থা: $T\cos 60^\circ = mg \implies T(0.5) = 0.2 \times 9.8 = 1.96 \implies T = 3.92\text{ N}$। ব্যাসার্ধ $r = L\sin 60^\circ$। কেন্দ্রমুখী বল $T\sin 60^\circ = m\omega^2 r = m\omega^2 L\sin 60^\circ \implies \omega^2 = \frac{T}{mL} = \frac{g}{L\cos 60^\circ} = \frac{9.8}{0.5} = 19.6$। $\omega = \sqrt{19.6} \approx 4.427\text{ rad/s}$। পর্যায়কাল $T_{rot} = \frac{2\pi}{\omega} = \frac{2\pi}{4.427} \approx 1.42\text{ s}$।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>$F_c = 292.57\text{ N}, \text{RPM} = 21.9$</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>সুতার টান $T = 3.92\text{ N}$, ঘূর্ণনকাল $T_{rot} = 1.42\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4990,38 +4701,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 27</t>
+          <t>সংযুক্ত বস্তুর গতি, কপিকল ও ব্যাংকিং কোণ (Connected Systems &amp; Banking)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>$9\text{ kg}$ ভরের একটি বস্তুকে $8\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $19\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=1,b=9.8,angle=5.8][size:small]##
+একটি বৃত্তাকার বাঁকে সাইকেল আরোহী $18\text{ km/h}$ দ্রুতিতে বাঁক নেওয়ার সময় উল্টে যাওয়া রোধ করতে উল্লম্বের সাথে কত কোণে হেলে পড়বেন, যদি বাঁকের ব্যাসার্ধ $25\text{ m}$ হয়? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=1,b=9.8,angle=5.8][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{9 \times 19^2}{8} = 406.12\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 2.38\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 22.7$।</t>
+          <t>বেগ $v = \frac{18 \times 1000}{3600} = 5\text{ m/s}$। ব্যাংকিং কোণ $\tan\theta = \frac{v^2}{rg} = \frac{5^2}{25 \times 9.8} = \frac{25}{245} \approx 0.102 \implies \theta = \tan^{-1}(0.102) \approx 5.82^\circ$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>$F_c = 406.12\text{ N}, \text{RPM} = 22.7$</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>$\theta = 5.82^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5041,43 +4752,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 28</t>
+          <t>সংযুক্ত বস্তুর গতি, কপিকল ও ব্যাংকিং কোণ (Connected Systems &amp; Banking)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##
-$10\text{ kg}$ ভরের একটি বস্তুকে $9\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $22\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
+          <t>##GEO:circle[r=3][size:small]##
+একটি উল্লম্ব সমতলে $R = 1.5\text{ m}$ দৈর্ঘ্যের একটি হালকা রডের একপ্রান্তে $m = 2\text{ kg}$ ভরের বস্তু বেঁধে বৃত্তাকার পথে ঘোরানো হচ্ছে। রডের ক্ষেত্রে শীর্ষবিন্দুতে সর্বনিম্ন কত দ্রুতি থাকলে বৃত্তটি সম্পূর্ণ হবে? (সুতা ও রডের পার্থক্যের ব্যাখ্যাসহ)।</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##</t>
+          <t>##GEO:circle[r=3][size:small]##</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{10 \times 22^2}{9} = 537.78\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 2.44\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 23.3$।</t>
+          <t>রড সংকুচিত হতে পারে না (দৃঢ় বস্তু), তাই শীর্ষবিন্দুতে বেগ শূন্য ($v=0$) হলেও রড কুঁকড়ে যাবে না। সুতার ক্ষেত্রে টান বল শূন্য হতে পারে না বলে সুতার জন্য শীর্ষবিন্দুতে ন্যূনতম বেগ $v = \sqrt{g R} = \sqrt{9.8 \times 1.5} \approx 3.83\text{ m/s}$ আবশ্যক।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>$F_c = 537.78\text{ N}, \text{RPM} = 23.3$</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>রডের জন্য $v_{\min} = 0$, সুতার জন্য $v_{\min} = \sqrt{g R} = 3.83\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5097,38 +4803,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 29</t>
+          <t>সংযুক্ত বস্তুর গতি, কপিকল ও ব্যাংকিং কোণ (Connected Systems &amp; Banking)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>$11\text{ kg}$ ভরের একটি বস্তুকে $10\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $25\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+দুটি ব্লক $m_1 = 3\text{ kg}$ এবং $m_2 = 2\text{ kg}$ অনুভূমিক ঘর্ষণহীন তলে পরস্পর সংস্পর্শে রাখা আছে। $m_1$ ব্লকের ওপর অনুভূমিক $F = 20\text{ N}$ বল প্রয়োগ করা হলে উভয় ব্লকের ত্বরণ এবং ব্লকদ্বয়ের মধ্যবর্তী পারস্পরিক স্পর্শ প্রতিক্রিয়া বল (Contact force) কত?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{11 \times 25^2}{10} = 687.5\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 2.5\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 23.9$।</t>
+          <t>সাধারণ ত্বরণ $a = \frac{F}{m_1 + m_2} = \frac{20}{3 + 2} = 4.0\text{ m/s}^2$। ব্লক $m_2$-এর গতির জন্য একমাত্র বল স্পর্শ প্রতিক্রিয়া $N_c$: $N_c = m_2 a = 2 \times 4.0 = 8.0\text{ N}$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>$F_c = 687.5\text{ N}, \text{RPM} = 23.9$</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>ত্বরণ $a = 4.0\text{ m/s}^2$, প্রতিক্রিয়া বল $N_c = 8.0\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5148,38 +4854,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 30</t>
+          <t>সংযুক্ত বস্তুর গতি, কপিকল ও ব্যাংকিং কোণ (Connected Systems &amp; Banking)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>$2\text{ kg}$ ভরের একটি বস্তুকে $5\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $28\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=3,b=5.2,angle=30][size:small]##
+একটি মসৃণ আনত তলে একটি কপিকলের সাহায্যে $m_1 = 5\text{ kg}$ ভরের ব্লককে তল বরাবর রেখে এবং অপর প্রান্তে $m_2 = 5\text{ kg}$ ভরের ব্লককে উল্লম্বভাবে ঝুলিয়ে দেওয়া হলো। তলের নতি কোণ $\theta = 30^\circ$ হলে ব্যবস্থাটির ত্বরণ কত? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=3,b=5.2,angle=30][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{2 \times 28^2}{5} = 313.6\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 5.6\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 53.5$।</t>
+          <t>ঝুলন্ত ভর $m_2$ নিচে নামলে: $m_2 g - T = m_2 a$। আনত তলে ব্লক $m_1$ উপরে উঠলে: $T - m_1 g\sin 30^\circ = m_1 a$। যোগ করে: $m_2 g - m_1 g\sin 30^\circ = (m_1 + m_2)a \implies 5(9.8) - 5(9.8)(0.5) = (5+5)a \implies 49 - 24.5 = 10a \implies 24.5 = 10a \implies a = 2.45\text{ m/s}^2$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>$F_c = 313.6\text{ N}, \text{RPM} = 53.5$</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>$a = 2.45\text{ m/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5199,38 +4905,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 31</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>$3\text{ kg}$ ভরের একটি বস্তুকে $6\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $31\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি $M = 4\text{ kg}$ ভর এবং $R = 0.5\text{ m}$ ব্যাসার্ধের নিরেট বেলন (Solid Cylinder) তার অক্ষের সাপেক্ষে $30\text{ rad/s}$ কৌণিক বেগে ঘুরছে। বেলনটির ঘূর্ণন গতিশক্তি এবং কৌণিক ভরবেগ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{3 \times 31^2}{6} = 480.5\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 5.17\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 49.4$।</t>
+          <t>জড়তার ভ্রামক $I = \frac{1}{2}M R^2 = \frac{1}{2}(4)(0.5^2) = 2(0.25) = 0.5\text{ kg}\cdot\text{m}^2$। ঘূর্ণন গতিশক্তি $K_{rot} = \frac{1}{2}I\omega^2 = \frac{1}{2}(0.5)(30^2) = 0.25(900) = 225.0\text{ J}$। কৌণিক ভরবেগ $L = I\omega = 0.5 \times 30 = 15.0\text{ kg}\cdot\text{m}^2/\text{s}$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>$F_c = 480.5\text{ N}, \text{RPM} = 49.4$</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>$K_{rot} = 225.0\text{ J}, L = 15.0\text{ kg}\cdot\text{m}^2/\text{s}$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5250,43 +4956,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 32</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##
-$4\text{ kg}$ ভরের একটি বস্তুকে $7\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $10\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি চাকা স্থির অবস্থা থেকে সমকৌণিক ত্বরণ নিয়ে ঘুরে $10\text{ সেকেন্ডে}$ $50\text{ বার}$ সম্পূর্ণ আবর্তন সম্পন্ন করে। চাকাটির কৌণিক ত্বরণ $\alpha$ এবং $10\text{ s}$ শেষে কৌণিক বেগ কত?</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{4 \times 10^2}{7} = 57.14\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 1.43\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 13.7$।</t>
+          <t>মোট কৌণিক সরণ $\theta = 50 \times 2\pi = 100\pi\text{ rad}$। $\theta = \frac{1}{2}\alpha t^2 \implies 100\pi = \frac{1}{2}\alpha(100) = 50\alpha \implies \alpha = 2\pi \approx 6.283\text{ rad/s}^2$। শেষ কৌণিক বেগ $\omega = \alpha t = 2\pi(10) = 20\pi \approx 62.83\text{ rad/s}$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>$F_c = 57.14\text{ N}, \text{RPM} = 13.7$</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>$\alpha = 6.28\text{ rad/s}^2, \omega = 62.83\text{ rad/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5306,38 +5007,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 33</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>$5\text{ kg}$ ভরের একটি বস্তুকে $8\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $13\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=3,b=4,angle=37][size:small]##
+একটি নিরেট গোলক ($I = \frac{2}{5}M R^2$), একটি ফাঁপা গোলক ($I = \frac{2}{3}M R^2$) এবং একটি নিরেট চাকতি ($I = \frac{1}{2}M R^2$) একই সাথে একটি আনত তলের শীর্ষ হতে বিনা পিছলে গড়িয়ে (Roll without slipping) পড়লে কোনটি সর্বপ্রথম তলদেশে পৌঁছাবে? গাণিতিক ত্বরণ নির্ণয়পূর্বক প্রমাণ কর।</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=3,b=4,angle=37][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{5 \times 13^2}{8} = 105.62\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 1.62\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 15.5$।</t>
+          <t>বিনা পিছলে গড়ানোর রৈখিক ত্বরণ $a = \frac{g\sin\theta}{1 + \frac{I}{MR^2}}$। নিরেট গোলকের জন্য $a_1 = \frac{g\sin\theta}{1 + 2/5} = \frac{5}{7}g\sin\theta \approx 0.714 g\sin\theta$। নিরেট চাকতির জন্য $a_2 = \frac{g\sin\theta}{1 + 1/2} = \frac{2}{3}g\sin\theta \approx 0.667 g\sin\theta$। ফাঁপা গোলকের জন্য $a_3 = \frac{g\sin\theta}{1 + 2/3} = \frac{3}{5}g\sin\theta = 0.600 g\sin\theta$। যেহেতু $a_1 &gt; a_2 &gt; a_3$, তাই নিরেট গোলক সবচেয়ে কম সময়ে প্রথম পৌঁছাবে।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>$F_c = 105.62\text{ N}, \text{RPM} = 15.5$</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>নিরেট গোলক সর্বপ্রথম পৌঁছাবে ($a_{solid} &gt; a_{disc} &gt; a_{hollow}$)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5357,38 +5058,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 34</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>$6\text{ kg}$ ভরের একটি বস্তুকে $9\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $16\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ঘূর্ণায়মান অনুভূমিক গোল টেবিলের ওপর একজন স্কেটার হাত প্রসারিত করে $2\text{ rev/s}$ বেগে ঘুরছেন। এ অবস্থায় তার জড়তার ভ্রামক $I_1 = 4.0\text{ kg}\cdot	ext{m}^2$। স্কেটার হাত গুটিয়ে নিলে তার জড়তার ভ্রামক হ্রাস পেয়ে $I_2 = 1.6\text{ kg}\cdot	ext{m}^2$ হয়। স্কেটারের নতুন ঘূর্ণন বেগ এবং গতিশক্তির শতকরা পরিবর্তন কত?</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{6 \times 16^2}{9} = 170.67\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 1.78\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 17.0$।</t>
+          <t>বাহ্যিক টর্ক শূন্য থাকায় কৌণিক ভরবেগ সংরক্ষিত: $I_1 \omega_1 = I_2 \omega_2 \implies 4.0(2) = 1.6 \omega_2 \implies \omega_2 = \frac{8}{1.6} = 5.0\text{ rev/s}$। আদি গতিশক্তি $K_1 = \frac{1}{2}I_1\omega_1^2 = \frac{1}{2}(4)(2^2) = 8$ (আপেক্ষিক একক)। শেষ গতিশক্তি $K_2 = \frac{1}{2}I_2\omega_2^2 = \frac{1}{2}(1.6)(5^2) = 20$। গতিশক্তির অনুপাত $\frac{K_2}{K_1} = \frac{20}{8} = 2.5$। শতকরা বৃদ্ধি $= (2.5 - 1) \times 100\% = 150\%$ (স্কেটারের পেশিজ শক্তি গতিশক্তিতে রূপান্তর হয়েছে)।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>$F_c = 170.67\text{ N}, \text{RPM} = 17.0$</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>নতুন বেগ $\omega_2 = 5.0\text{ rev/s}$, গতিশক্তি বৃদ্ধি $150\%$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5408,38 +5109,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 35</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>$7\text{ kg}$ ভরের একটি বস্তুকে $10\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $19\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=0.5][size:small]##
+একটি $M = 2\text{ kg}$ ভর এবং $L = 1.2\text{ m}$ দৈর্ঘ্যের সুষম সরু দণ্ডের একপ্রান্তগামী লম্ব অক্ষের সাপেক্ষে জড়তার ভ্রামক এবং চক্রগতির ব্যাসার্ধ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=0.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{7 \times 19^2}{10} = 252.7\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 1.9\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 18.1$।</t>
+          <t>একপ্রান্তগামী অক্ষের সাপেক্ষে জড়তার ভ্রামক $I = \frac{1}{3}M L^2 = \frac{1}{3}(2)(1.2^2) = \frac{2}{3}(1.44) = 0.96\text{ kg}\cdot\text{m}^2$। চক্রগতির ব্যাসার্ধ $K = \frac{L}{\sqrt{3}} = \frac{1.2}{\sqrt{3}} \approx 0.693\text{ m}$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>$F_c = 252.7\text{ N}, \text{RPM} = 18.1$</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>$I = 0.96\text{ kg}\cdot\text{m}^2, K = 0.693\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5459,43 +5160,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 36</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##
-$8\text{ kg}$ ভরের একটি বস্তুকে $5\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $22\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
+          <t>##GEO:circle[r=2][size:small]##
+একটি নিরেট চাকতির ভর $5\text{ kg}$ এবং ব্যাসার্ধ $0.4\text{ m}$। চাকতির পরিধিতে একটি স্পর্শকীয় বল $F = 20\text{ N}$ প্রয়োগ করা হলে উৎপন্ন কৌণিক ত্বরণ $\alpha$ কত?</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##</t>
+          <t>##GEO:circle[r=2][size:small]##</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{8 \times 22^2}{5} = 774.4\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 4.4\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 42.0$।</t>
+          <t>প্রযুক্ত টর্ক $\tau = F R = 20 \times 0.4 = 8.0\text{ N}\cdot\text{m}$। কেন্দ্রগামী অক্ষের সাপেক্ষে চাকতির জড়তার ভ্রামক $I = \frac{1}{2}M R^2 = \frac{1}{2}(5)(0.4^2) = 2.5(0.16) = 0.4\text{ kg}\cdot\text{m}^2$। কৌণিক ত্বরণ $\alpha = \frac{\tau}{I} = \frac{8.0}{0.4} = 20.0\text{ rad/s}^2$।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>$F_c = 774.4\text{ N}, \text{RPM} = 42.0$</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>$\alpha = 20.0\text{ rad/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5515,38 +5211,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 37</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>$9\text{ kg}$ ভরের একটি বস্তুকে $6\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $25\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি $200\text{ kg}$ ভরের ফ্লাইহুইল $360\text{ rpm}$ বেগে ঘুরছে। এর চক্রগতির ব্যাসার্ধ $K = 0.6\text{ m}$। একটি ব্রেক প্রয়োগ করে চাকাটিকে $15\text{ সেকেন্ডে}$ সম্পূর্ণ থামাতে কী পরিমাণ ধ্রুব ব্রেকিং টর্ক প্রয়োগ করতে হবে?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{9 \times 25^2}{6} = 937.5\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 4.17\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 39.8$।</t>
+          <t>আদি কৌণিক বেগ $\omega_0 = \frac{2\pi \times 360}{60} = 12\pi \approx 37.70\text{ rad/s}$। মন্দন $\alpha = \frac{\omega_0}{t} = \frac{12\pi}{15} = 0.8\pi \approx 2.513\text{ rad/s}^2$। জড়তার ভ্রামক $I = M K^2 = 200(0.6^2) = 200(0.36) = 72\text{ kg}\cdot\text{m}^2$। ব্রেকিং টর্ক $\tau = I\alpha = 72 \times 0.8\pi = 57.6\pi \approx 180.96\text{ N}\cdot\text{m}$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>$F_c = 937.5\text{ N}, \text{RPM} = 39.8$</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>$\tau = 180.96\text{ N}\cdot\text{m}$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5566,38 +5262,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 38</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>$10\text{ kg}$ ভরের একটি বস্তুকে $7\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $28\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+একটি বৃত্তাকার রিং (হুপ) এবং একটি নিরেট গোলকের ভর ও ব্যাসার্ধ সমান। উভয়ে একই রৈখিক দ্রুতি $v = 10\text{ m/s}$ নিয়ে অনুভূমিক মেঝের ওপর গড়িয়ে চললে তাদের মোট গতিশক্তির (রৈখিক + ঘূর্ণন) অনুপাত নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{10 \times 28^2}{7} = 1120.0\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 4.0\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 38.2$।</t>
+          <t>গড়ানো গতিশক্তি $K = \frac{1}{2}M v^2\left(1 + \frac{I}{MR^2}\right)$। রিংয়ের জন্য $I = MR^2 \implies K_{ring} = \frac{1}{2}M v^2(1+1) = M v^2$। নিরেট গোলকের জন্য $I = \frac{2}{5}MR^2 \implies K_{sphere} = \frac{1}{2}M v^2(1 + 2/5) = \frac{7}{10}M v^2$। অনুপাত $\frac{K_{ring}}{K_{sphere}} = \frac{1}{7/10} = \frac{10}{7} \approx 1.43$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>$F_c = 1120.0\text{ N}, \text{RPM} = 38.2$</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>$\frac{K_{ring}}{K_{sphere}} = \frac{10}{7} \approx 1.43$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5617,38 +5313,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 39</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>$11\text{ kg}$ ভরের একটি বস্তুকে $8\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $31\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:circle[r=2.2][size:small]##
+একটি সমান্তরাল অক্ষ উপপাদ্য (Parallel axis theorem) প্রয়োগ কর: $M$ ভর এবং $R$ ব্যাসার্ধের একটি নিরেট চাকতির তলের সাথে লম্ব এবং পরিধির ওপর অবস্থিত কোনো স্পর্শকীয় অক্ষের সাপেক্ষে জড়তার ভ্রামক কত?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.2][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{11 \times 31^2}{8} = 1321.38\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.88\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 37.1$।</t>
+          <t>ভরকেন্দ্রগামী অক্ষের সাপেক্ষে $I_{cm} = \frac{1}{2}M R^2$। পরিধির অক্ষের দূরত্ব $d = R$। সমান্তরাল অক্ষ উপপাদ্য: $I = I_{cm} + M d^2 = \frac{1}{2}M R^2 + M R^2 = \frac{3}{2}M R^2$।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>$F_c = 1321.38\text{ N}, \text{RPM} = 37.1$</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>$I = \frac{3}{2}M R^2$</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5668,43 +5364,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 40</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##
-$2\text{ kg}$ ভরের একটি বস্তুকে $9\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $10\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
+          <t>##GEO:circle[r=2.2][size:small]##
+একটি লম্ব অক্ষ উপপাদ্য (Perpendicular axis theorem) প্রয়োগ কর: $M$ ভর এবং $R$ ব্যাসার্ধের একটি পাতলা বৃত্তাকার চাকতির ব্যাসের সাপেক্ষে জড়তার ভ্রামক নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##</t>
+          <t>##GEO:circle[r=2.2][size:small]##</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{2 \times 10^2}{9} = 22.22\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 1.11\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 10.6$।</t>
+          <t>চাকতির তলের ওপর দুটি পরস্পর লম্ব ব্যাস $x$ ও $y$। সমমিতির কারণে $I_x = I_y = I_d$। তলের লম্ব কেন্দ্রগামী অক্ষের সাপেক্ষে $I_z = \frac{1}{2}MR^2$। লম্ব অক্ষ উপপাদ্য: $I_z = I_x + I_y = 2I_d \implies 2I_d = \frac{1}{2}MR^2 \implies I_d = \frac{1}{4}MR^2$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>$F_c = 22.22\text{ N}, \text{RPM} = 10.6$</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>$I_{diameter} = \frac{1}{4}M R^2$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5724,38 +5415,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 41</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>$3\text{ kg}$ ভরের একটি বস্তুকে $10\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $13\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি কণার ভর $m$ এবং তা $xy$-তলে $y = 3	ext{ m}$ সরলরেখা বরাবর $v = 4	ext{ m/s}$ সমদ্রুতিতে চলছে। মূলবিন্দুর সাপেক্ষে কণাটির কৌণিক ভরবেগের মান নির্ণয় কর ($m = 2	ext{ kg}$)।</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{3 \times 13^2}{10} = 50.7\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 1.3\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 12.4$।</t>
+          <t>কৌণিক ভরবেগ $L = |\vec{r} \times \vec{p}| = m v r_{\perp}$ যেখানে $r_{\perp}$ হলো গতিপথের ওপর মূলবিন্দু হতে লম্ব দূরত্ব। এখানে $r_{\perp} = y = 3\text{ m}$। $L = 2 \times 4 \times 3 = 24.0\text{ kg}\cdot\text{m}^2/\text{s}$। দূরত্ব বা সময়ের ওপর এটি নির্ভর করে না, সর্বদা ধ্রুব থাকে।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>$F_c = 50.7\text{ N}, \text{RPM} = 12.4$</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>$L = 24.0\text{ kg}\cdot\text{m}^2/\text{s}$ (ধ্রুব)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5775,38 +5466,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 42</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>$4\text{ kg}$ ভরের একটি বস্তুকে $5\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $16\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+একটি ঘূর্ণনশীল চাকার ওপর প্রযুক্ত টর্ক $	au(t) = (4t + 2)	ext{ N}\cdot	ext{m}$। চাকাটির জড়তার ভ্রামক $I = 2	ext{ kg}\cdot	ext{m}^2$ হলে প্রথম $3	ext{ সেকেন্ডে}$ চাকার কৌণিক ভরবেগের পরিবর্তন $\Delta L$ এবং অর্জিত কৌণিক বেগ কত? (স্থির অবস্থা হতে শুরু)।</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{4 \times 16^2}{5} = 204.8\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.2\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 30.6$।</t>
+          <t>কৌণিক ভরবেগের পরিবর্তন (কৌণিক ঘাত): $\Delta L = \int_0^3 \tau dt = \int_0^3 (4t+2)dt = [2t^2 + 2t]_0^3 = 2(9) + 2(3) = 18 + 6 = 24.0\text{ N}\cdot\text{m}\cdot\text{s}$। কৌণিক বেগ $\omega = \frac{\Delta L}{I} = \frac{24.0}{2} = 12.0\text{ rad/s}$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>$F_c = 204.8\text{ N}, \text{RPM} = 30.6$</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>$\Delta L = 24.0\text{ N}\cdot\text{m}\cdot\text{s}, \omega = 12.0\text{ rad/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5826,38 +5517,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 43</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>$5\text{ kg}$ ভরের একটি বস্তুকে $6\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $19\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি গোলকের ভর $M$ এবং ব্যাসার্ধ $R$। গোলকটি অনুভূমিক মেঝেতে পিছলে না গিয়ে $v_{cm}$ সমদ্রুতিতে গড়িয়ে চললে এর ঘূর্ণন গতিশক্তি এবং রৈখিক গতিশক্তির শতকরা অনুপাত কত?</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{5 \times 19^2}{6} = 300.83\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.17\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 30.3$।</t>
+          <t>রৈখিক গতিশক্তি $K_{trans} = \frac{1}{2}M v_{cm}^2$। ঘূর্ণন গতিশক্তি $K_{rot} = \frac{1}{2}I\omega^2 = \frac{1}{2}\left(\frac{2}{5}MR^2\right)\left(\frac{v_{cm}}{R}\right)^2 = \frac{1}{5}M v_{cm}^2$। অনুপাত $\frac{K_{rot}}{K_{trans}} = \frac{1/5}{1/2} = \frac{2}{5} = 0.40 = 40\%$। মোট শক্তিতে অনুপাত $\frac{K_{rot}}{K_{total}} = \frac{2/5}{1 + 2/5} = \frac{2}{7} \approx 28.57\%$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>$F_c = 300.83\text{ N}, \text{RPM} = 30.3$</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>ঘূর্ণন গতিশক্তি রৈখিক গতিশক্তির $40\%$ (মোট গতিশক্তির $28.57\%$)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5877,43 +5568,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 44</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##
-$6\text{ kg}$ ভরের একটি বস্তুকে $7\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $22\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি নিরেট চোঙের ভর $10	ext{ kg}$ এবং ব্যাসার্ধ $0.2	ext{ m}$। চোঙটির গায়ে পেঁচানো সুতা টেনে $30	ext{ N}$ বল প্রয়োগ করা হলো। চোঙটি মসৃণ অনুভূমিক মেঝের ওপর থাকলে এর ভরকেন্দ্রের রৈখিক ত্বরণ এবং কৌণিক ত্বরণ কত?</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{6 \times 22^2}{7} = 414.86\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.14\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 30.0$।</t>
+          <t>মেঝে মসৃণ হওয়ায় কেবল প্রযুক্ত বল কাজ করে: ভরকেন্দ্রের ত্বরণ $a_{cm} = \frac{F}{M} = \frac{30}{10} = 3.0\text{ m/s}^2$। কেন্দ্রগামী অক্ষ সাপেক্ষে টর্ক $\tau = F R = 30 \times 0.2 = 6.0\text{ N}\cdot\text{m}$। জড়তার ভ্রামক $I = \frac{1}{2}MR^2 = \frac{1}{2}(10)(0.04) = 0.2\text{ kg}\cdot\text{m}^2$। কৌণিক ত্বরণ $\alpha = \frac{\tau}{I} = \frac{6.0}{0.2} = 30.0\text{ rad/s}^2$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>$F_c = 414.86\text{ N}, \text{RPM} = 30.0$</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>$a = 3.0\text{ m/s}^2, \alpha = 30.0\text{ rad/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5933,38 +5619,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 45</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>$7\text{ kg}$ ভরের একটি বস্তুকে $8\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $25\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=0.5][size:small]##
+একটি সুষম দণ্ডের দৈর্ঘ্য $L$ এবং ভর $M$। দণ্ডটিকে একপ্রান্তে কব্জা (Hinge) দিয়ে উল্লম্বভাবে ঝুলিয়ে দেওয়া হয়েছে। দণ্ডটিকে অনুভূমিক অবস্থান পর্যন্ত তুলে ছেড়ে দিলে সর্বনিম্ন বিন্দু অতিক্রমের মুহূর্তে দণ্ডের মুক্ত প্রান্তের রৈখিক বেগ কত হবে? ($g = 9.8	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=0.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{7 \times 25^2}{8} = 546.88\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.12\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 29.8$।</t>
+          <t>ভরকেন্দ্রের উচ্চতা হ্রাস $h = L/2$। বিভব শক্তি হ্রাস $= Mg(L/2)$। একপ্রান্ত সাপেক্ষে দণ্ডের ঘূর্ণন গতিশক্তি $K = \frac{1}{2}I\omega^2 = \frac{1}{2}\left(\frac{1}{3}ML^2\right)\omega^2 = \frac{1}{6}ML^2\omega^2$। শক্তির নিত্যতা: $\frac{1}{6}ML^2\omega^2 = \frac{1}{2}MgL \implies \omega^2 = \frac{3g}{L} \implies \omega = \sqrt{\frac{3g}{L}}$। মুক্ত প্রান্তের রৈখিক বেগ $v = \omega L = \sqrt{\frac{3g}{L}} \times L = \sqrt{3gL}$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>$F_c = 546.88\text{ N}, \text{RPM} = 29.8$</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>$v = \sqrt{3g L}$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5984,38 +5670,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 46</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>$8\text{ kg}$ ভরের একটি বস্তুকে $9\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $28\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+একটি ফ্যানের ব্লেডগুলোর জড়তার ভ্রামক $I = 0.2	ext{ kg}\cdot	ext{m}^2$। সুইচ অন করার পর মোটর $1.6	ext{ N}\cdot	ext{m}$ ধ্রুব টর্ক প্রয়োগ করে। ফ্যানটি কত সেকেন্ডে তার পূর্ণ কার্যনির্বাহী দ্রুতি $600	ext{ rpm}$-এ পৌঁছাবে?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{8 \times 28^2}{9} = 696.89\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.11\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 29.7$।</t>
+          <t>চূড়ান্ত কৌণিক বেগ $\omega = \frac{2\pi \times 600}{60} = 20\pi \approx 62.83\text{ rad/s}$। কৌণিক ত্বরণ $\alpha = \frac{\tau}{I} = \frac{1.6}{0.2} = 8.0\text{ rad/s}^2$। সময় $t = \frac{\omega}{\alpha} = \frac{20\pi}{8} = 2.5\pi \approx 7.85\text{ s}$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>$F_c = 696.89\text{ N}, \text{RPM} = 29.7$</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>সময় $t = 7.85\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6035,38 +5721,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 47</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>$9\text{ kg}$ ভরের একটি বস্তুকে $10\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $31\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি গোলক একটি ফাঁপা গোলকের অভ্যন্তরে তলদেশে সাম্যাবস্থায় রাখা আছে। গোলকটিকে সামান্য আন্দোলিত করলে এর দোলনকাল কত হবে? (বৃহৎ গোলকের ব্যাসার্ধ $R$, ক্ষুদ্র নিরেট গোলকের ব্যাসার্ধ $r$)।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{9 \times 31^2}{10} = 864.9\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 3.1\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 29.6$।</t>
+          <t>বিনা পিছলে রোলিং দোলনের ক্ষেত্রে কার্যকর কার্যকর দৈর্ঘ্য $L_{eff} = \frac{7}{5}(R-r)$। অতএব কৌণিক কম্পাঙ্ক $\omega = \sqrt{\frac{5g}{7(R-r)}}$ এবং দোলনকাল $T = 2\pi\sqrt{\frac{7(R-r)}{5g}}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>$F_c = 864.9\text{ N}, \text{RPM} = 29.6$</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>$T = 2\pi\sqrt{\frac{7(R-r)}{5g}}$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6086,43 +5772,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 48</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##
-$10\text{ kg}$ ভরের একটি বস্তুকে $5\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $10\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
+          <t>##PRESET:vector-cross[size:medium]##
+একটি কণার ভরবেগ $ec{p} = 2t\hat{i} + 3\hat{j} - 4t^2\hat{k}$ কেজি মিটার/সেকেন্ড। $t = 2	ext{ s}$ মুহূর্তে কণাটির ওপর প্রযুক্ত বল এবং আদি অবস্থান $ec{r} = (1, 0, -2)	ext{ m}$ সাপেক্ষে প্রযুক্ত টর্ক নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>##PRESET:pulley-single[size:medium]##</t>
+          <t>##PRESET:vector-cross[size:medium]##</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{10 \times 10^2}{5} = 200.0\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 2.0\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 19.1$।</t>
+          <t>বল $\vec{F} = \frac{d\vec{p}}{dt} = 2\hat{i} - 8t\hat{k}$। $t = 2$-এ $\vec{F} = 2\hat{i} - 16\hat{k}\text{ N}$। টর্ক $\vec{\tau} = \vec{r} \times \vec{F} = \begin{vmatrix} \hat{i} &amp; \hat{j} &amp; \hat{k} \\ 1 &amp; 0 &amp; -2 \\ 2 &amp; 0 &amp; -16 \end{vmatrix} = \hat{i}(0) - \hat{j}(-16 - (-4)) + \hat{k}(0) = -(-12)\hat{j} = 12\hat{j}\text{ N}\cdot\text{m}$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>$F_c = 200.0\text{ N}, \text{RPM} = 19.1$</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>$\vec{F} = 2\hat{i} - 16\hat{k}\text{ N}, \vec{\tau} = 0\hat{i} + 12\hat{j} + 0\hat{k}\text{ N}\cdot\text{m}$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6142,38 +5823,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 49</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>$11\text{ kg}$ ভরের একটি বস্তুকে $6\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $13\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+একটি চাকতির চক্রগতির ব্যাসার্ধ $K = 0.25	ext{ m}$ এবং ভর $8	ext{ kg}$। চাকতির পরিধিতে একটি $12	ext{ N}$ বল স্পর্শকীয়ভাবে প্রযুক্ত হলে $4	ext{ সেকেন্ডে}$ সম্পন্ন ঘূর্ণন সংখ্যা কত?</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{11 \times 13^2}{6} = 309.83\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 2.17\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 20.7$।</t>
+          <t>জড়তার ভ্রামক $I = M K^2 = 8(0.25^2) = 8(0.0625) = 0.5\text{ kg}\cdot\text{m}^2$। ব্যাসার্ধ $R = \sqrt{2}K = \sqrt{2}(0.25) \approx 0.3536\text{ m}$। টর্ক $\tau = F R = 12(0.3536) = 4.243\text{ N}\cdot\text{m}$। $\alpha = \frac{\tau}{I} = \frac{4.243}{0.5} = 8.485\text{ rad/s}^2$। কৌণিক সরণ $\theta = \frac{1}{2}\alpha t^2 = 0.5(8.485)(16) = 67.88\text{ rad}$। ঘূর্ণন সংখ্যা $N = \frac{\theta}{2\pi} = \frac{67.88}{6.283} \approx 10.8\text{ বার}$।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>$F_c = 309.83\text{ N}, \text{RPM} = 20.7$</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>$N \approx 15.28\text{ বার}$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6193,38 +5874,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>রৈখিক ও কৌণিক বলবিদ্যার সমন্বিত সমস্যা 50</t>
+          <t>ঘূর্ণন গতিবিদ্যা, জড়তার ভ্রামক ও কৌণিক ভরবেগ (Rotational Dynamics)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>$2\text{ kg}$ ভরের একটি বস্তুকে $7\text{ m}$ দীর্ঘ সুতার একপ্রান্তে বেঁধে অনুভূমিক তলে বৃত্তাকার পথে $16\text{ m/s}$ দ্রুতিতে ঘোরানো হচ্ছে। সুতাটির কেন্দ্রমুখী টান বল এবং প্রতি মিনিটে ঘূর্ণন সংখ্যা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি গাড়ি $1200	ext{ kg}$ ভরের। এটি $20	ext{ m/s}$ বেগে চলার সময় হঠাৎ চালক ব্রেক চেপে $4	ext{ সেকেন্ডে}$ গাড়িটিকে থামিয়ে দিলেন। চাকার সাথে মেঝের ঘর্ষণের ফলে উৎপন্ন মোট তাপশক্তি ক্যালরিতে কত? ($1	ext{ cal} = 4.2	ext{ J}$)।</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>কেন্দ্রমুখী বল $F_c = \frac{m v^2}{r} = \frac{2 \times 16^2}{7} = 73.14\text{ N}$।
-কৌণিক বেগ $\omega = \frac{v}{r} = 2.29\text{ rad/s}$। $\text{RPM} = \frac{\omega \times 60}{2\pi} = 21.9$।</t>
+          <t>আদি গতিশক্তি $K = \frac{1}{2}m v^2 = \frac{1}{2}(1200)(20^2) = 600(400) = 240000\text{ J}$। ঘর্ষণে সম্পূর্ণ গতিশক্তি তাপে রূপান্তরিত হয়: $H = \frac{W}{J} = \frac{240000}{4.2} \approx 57142.86\text{ cal} \approx 57.14\text{ kcal}$।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>$F_c = 73.14\text{ N}, \text{RPM} = 21.9$</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>$H = 57142.86\text{ cal} \approx 57.14\text{ kcal}$</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
